--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="# ##0.00;-# ##0.00;—"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;—"/>
   </numFmts>
   <fonts count="13">
     <font>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I100"/>
+  <dimension ref="B1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1131,11 +1131,11 @@
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Первая декада, старая управленка</t>
+          <t xml:space="preserve">    Наличными</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>29748144</v>
+        <v>31243030</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
@@ -1144,18 +1144,18 @@
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>способа оплаты в выгрузке старой программы нет</t>
+          <t>01–10.08: 6 949 630; 11–31.08: 24 293 400</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Наличными</t>
+          <t xml:space="preserve">    Безналичными (эквайринг)</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>24293400</v>
+        <v>64563454</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
@@ -1164,104 +1164,106 @@
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>новая управленка, 11–31.08</t>
+          <t>01–10.08: 22 798 514; 11–31.08: 41 764 940</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Безналичными (эквайринг)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>41764940</v>
-      </c>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>новая управленка, 11–31.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C40" s="12">
-        <f>SUM(C37:C39)</f>
-        <v/>
-      </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="C39" s="12">
+        <f>SUM(C37:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="B43" s="5" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>6135792.28</v>
+      </c>
+      <c r="D43" s="7">
+        <f>C43/2</f>
+        <v/>
+      </c>
+      <c r="E43" s="7">
+        <f>C43/2</f>
+        <v/>
+      </c>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>6135792.28</v>
+        <v>12490831.85</v>
       </c>
       <c r="D44" s="7">
         <f>C44/2</f>
@@ -1279,11 +1281,11 @@
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Зарплата по банку</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>12490831.85</v>
+        <v>141281.46</v>
       </c>
       <c r="D45" s="7">
         <f>C45/2</f>
@@ -1301,11 +1303,11 @@
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>141281.46</v>
+        <v>373487.16</v>
       </c>
       <c r="D46" s="7">
         <f>C46/2</f>
@@ -1323,11 +1325,11 @@
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Алименты (удержание из зарплаты)</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>373487.16</v>
+        <v>38726.66</v>
       </c>
       <c r="D47" s="7">
         <f>C47/2</f>
@@ -1343,60 +1345,54 @@
       <c r="I47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Алименты (удержание из зарплаты)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>38726.66</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D48" s="19">
         <f>C48/2</f>
         <v/>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="19">
         <f>C48/2</f>
         <v/>
       </c>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D49" s="19">
-        <f>C49/2</f>
-        <v/>
-      </c>
-      <c r="E49" s="19">
-        <f>C49/2</f>
-        <v/>
-      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>39819623</v>
+      </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
@@ -1407,11 +1403,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>39819623</v>
+        <v>4527900</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
@@ -1423,11 +1419,11 @@
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>4527900</v>
+        <v>3298432.06</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
@@ -1439,11 +1435,11 @@
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>3298432.06</v>
+        <v>2887658</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
@@ -1455,11 +1451,11 @@
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>2887658</v>
+        <v>2250790.16</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
@@ -1471,11 +1467,11 @@
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>2250790.16</v>
+        <v>827352.65</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
@@ -1487,11 +1483,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>827352.65</v>
+        <v>515528</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1503,11 +1499,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>515528</v>
+        <v>376950</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1519,11 +1515,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>376950</v>
+        <v>345200</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1535,11 +1531,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>345200</v>
+        <v>582359.62</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1549,14 +1545,12 @@
       <c r="I59" s="8" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>582359.62</v>
-      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
@@ -1565,12 +1559,14 @@
       <c r="I60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>4692500</v>
+      </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
@@ -1581,11 +1577,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>4692500</v>
+        <v>2505800</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1597,11 +1593,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>2505800</v>
+        <v>1155000</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1613,11 +1609,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>1155000</v>
+        <v>878789.77</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1629,11 +1625,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            ЗП Заведягин ОН</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>878789.77</v>
+        <v>570005</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1645,11 +1641,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ЗП Заведягин ОН</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>570005</v>
+        <v>516000</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1661,11 +1657,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>516000</v>
+        <v>435435</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1677,11 +1673,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>435435</v>
+        <v>337440</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1693,11 +1689,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>337440</v>
+        <v>330000</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1709,11 +1705,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>330000</v>
+        <v>320000</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1725,11 +1721,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>320000</v>
+        <v>2621284.79</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1739,156 +1735,163 @@
       <c r="I71" s="8" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>2621284.79</v>
-      </c>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
-      <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="8" t="n"/>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ</t>
+        </is>
+      </c>
+      <c r="C72" s="15">
+        <f>SUM(C43:C48)</f>
+        <v/>
+      </c>
+      <c r="D72" s="15">
+        <f>SUM(D43:D48)</f>
+        <v/>
+      </c>
+      <c r="E72" s="15">
+        <f>SUM(E43:E48)</f>
+        <v/>
+      </c>
+      <c r="F72" s="16" t="n"/>
+      <c r="G72" s="16" t="n"/>
+      <c r="H72" s="16" t="n"/>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ</t>
-        </is>
-      </c>
-      <c r="C73" s="15">
-        <f>SUM(C44:C49)</f>
-        <v/>
-      </c>
-      <c r="D73" s="15">
-        <f>SUM(D44:D49)</f>
-        <v/>
-      </c>
-      <c r="E73" s="15">
-        <f>SUM(E44:E49)</f>
-        <v/>
-      </c>
-      <c r="F73" s="16" t="n"/>
-      <c r="G73" s="16" t="n"/>
-      <c r="H73" s="16" t="n"/>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="21" t="inlineStr">
+      <c r="B73" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C74" s="22" t="n">
+      <c r="C73" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="B76" s="3" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="B77" s="5" t="inlineStr">
+    <row r="76" ht="26" customHeight="1">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>1. Личная выручка (свои операции)</t>
+        </is>
+      </c>
+      <c r="C77" s="7">
+        <f>D77+E77</f>
+        <v/>
+      </c>
+      <c r="D77" s="7">
+        <f>D34</f>
+        <v/>
+      </c>
+      <c r="E77" s="7">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>1. Личная выручка (свои операции)</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C78" s="7">
-        <f>D78+E78</f>
+        <f>F34</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>D34</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="E78" s="7">
-        <f>E34</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
+      <c r="I78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C79" s="7">
-        <f>F34</f>
+        <f>H34</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>F34/2</f>
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="E79" s="7">
-        <f>F34/2</f>
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="F79" s="8" t="n"/>
@@ -1899,19 +1902,19 @@
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>4. Половина прочих доходов</t>
         </is>
       </c>
       <c r="C80" s="7">
-        <f>H34</f>
+        <f>G34</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>H34/2</f>
+        <f>G34/2</f>
         <v/>
       </c>
       <c r="E80" s="7">
-        <f>H34/2</f>
+        <f>G34/2</f>
         <v/>
       </c>
       <c r="F80" s="8" t="n"/>
@@ -1922,41 +1925,45 @@
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
-        </is>
-      </c>
-      <c r="C81" s="7">
-        <f>G34</f>
-        <v/>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>396337.24</v>
       </c>
       <c r="D81" s="7">
-        <f>G34/2</f>
+        <f>C81/2</f>
         <v/>
       </c>
       <c r="E81" s="7">
-        <f>G34/2</f>
+        <f>C81/2</f>
         <v/>
       </c>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
-      <c r="I81" s="8" t="n"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="n">
-        <v>396337.24</v>
-      </c>
-      <c r="D82" s="7">
-        <f>C82/2</f>
-        <v/>
-      </c>
-      <c r="E82" s="7">
-        <f>C82/2</f>
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C82" s="24">
+        <f>-C72</f>
+        <v/>
+      </c>
+      <c r="D82" s="24">
+        <f>-D72</f>
+        <v/>
+      </c>
+      <c r="E82" s="24">
+        <f>-E72</f>
         <v/>
       </c>
       <c r="F82" s="8" t="n"/>
@@ -1964,272 +1971,261 @@
       <c r="H82" s="8" t="n"/>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>начислены банком на остатки</t>
+          <t>итог блока «Расходы», пополам</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C83" s="24">
-        <f>-C73</f>
-        <v/>
-      </c>
-      <c r="D83" s="24">
-        <f>-D73</f>
-        <v/>
-      </c>
-      <c r="E83" s="24">
-        <f>-E73</f>
-        <v/>
-      </c>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>итог блока «Расходы», пополам</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C84" s="15">
-        <f>SUM(C78:C83)</f>
-        <v/>
-      </c>
-      <c r="D84" s="15">
-        <f>SUM(D78:D83)</f>
-        <v/>
-      </c>
-      <c r="E84" s="15">
-        <f>SUM(E78:E83)</f>
-        <v/>
-      </c>
-      <c r="F84" s="16" t="n"/>
-      <c r="G84" s="16" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="B86" s="3" t="inlineStr">
+      <c r="C83" s="15">
+        <f>SUM(C77:C82)</f>
+        <v/>
+      </c>
+      <c r="D83" s="15">
+        <f>SUM(D77:D82)</f>
+        <v/>
+      </c>
+      <c r="E83" s="15">
+        <f>SUM(E77:E82)</f>
+        <v/>
+      </c>
+      <c r="F83" s="16" t="n"/>
+      <c r="G83" s="16" t="n"/>
+      <c r="H83" s="16" t="n"/>
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="inlineStr"/>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="B87" s="5" t="inlineStr">
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Доход за месяц</t>
+        </is>
+      </c>
+      <c r="C87" s="7">
+        <f>C83</f>
+        <v/>
+      </c>
+      <c r="D87" s="7">
+        <f>D83</f>
+        <v/>
+      </c>
+      <c r="E87" s="7">
+        <f>E83</f>
+        <v/>
+      </c>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Доход за месяц</t>
+          <t>Остаток с прошлого месяца</t>
         </is>
       </c>
       <c r="C88" s="7">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="D88" s="7">
-        <f>D84</f>
-        <v/>
-      </c>
-      <c r="E88" s="7">
-        <f>E84</f>
-        <v/>
+        <f>D88+E88</f>
+        <v/>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C89" s="7">
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C89" s="24">
         <f>D89+E89</f>
         <v/>
       </c>
-      <c r="D89" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>45275972.21</v>
+      <c r="D89" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E89" s="24" t="n">
+        <v>-5882353</v>
       </c>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>ручной ввод бухгалтерии</t>
+          <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C90" s="24">
-        <f>D90+E90</f>
-        <v/>
-      </c>
-      <c r="D90" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E90" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="F90" s="8" t="n"/>
-      <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>начислено с НДФЛ</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C91" s="15">
-        <f>SUM(C88:C90)</f>
-        <v/>
-      </c>
-      <c r="D91" s="15">
-        <f>SUM(D88:D90)</f>
-        <v/>
-      </c>
-      <c r="E91" s="15">
-        <f>SUM(E88:E90)</f>
-        <v/>
-      </c>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="16" t="n"/>
-      <c r="H91" s="16" t="n"/>
-      <c r="I91" s="16" t="n"/>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="B93" s="3" t="inlineStr">
+      <c r="C90" s="15">
+        <f>SUM(C87:C89)</f>
+        <v/>
+      </c>
+      <c r="D90" s="15">
+        <f>SUM(D87:D89)</f>
+        <v/>
+      </c>
+      <c r="E90" s="15">
+        <f>SUM(E87:E89)</f>
+        <v/>
+      </c>
+      <c r="F90" s="16" t="n"/>
+      <c r="G90" s="16" t="n"/>
+      <c r="H90" s="16" t="n"/>
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="B94" s="5" t="inlineStr">
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — лимит</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t>Кредитная линия — выбрано</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>30000000</v>
+        <v>27545367</v>
       </c>
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
-      <c r="I95" s="8" t="n"/>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>долг на дату отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>27545367</v>
+        <v>2454633</v>
       </c>
       <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>долг на дату отчёта</t>
-        </is>
-      </c>
+      <c r="I96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Проценты по депозитам за месяц</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>2454633</v>
+        <v>396337.24</v>
       </c>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
@@ -2241,52 +2237,36 @@
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="n">
-        <v>396337.24</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n"/>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="n"/>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>373487.16</v>
+      </c>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="n"/>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>373487.16</v>
-      </c>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I99"/>
+  <dimension ref="B1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1100,13 +1100,13 @@
         <v>13054662.21</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>75249046.11</v>
+        <v>77250611.63</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>271238.64</v>
+        <v>261238.64</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>3050755.58</v>
+        <v>2960140.06</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>31243030</v>
+        <v>34981900</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
@@ -1144,7 +1144,7 @@
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 6 949 630; 11–31.08: 24 293 400</t>
+          <t>01–10.08: 10 688 500; 11–31.08: 24 293 400</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>64563454</v>
+        <v>61654454</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
@@ -1164,106 +1164,100 @@
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 22 798 514; 11–31.08: 41 764 940</t>
+          <t>01–10.08: 19 889 514; 11–31.08: 41 764 940</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Оплаты физлиц на расчётный счёт</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>1071080</v>
+      </c>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C39" s="12">
-        <f>SUM(C37:C38)</f>
-        <v/>
-      </c>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="13" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="18" t="inlineStr">
+      <c r="C40" s="12">
+        <f>SUM(C37:C39)</f>
+        <v/>
+      </c>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="B42" s="5" t="inlineStr">
+    <row r="43" ht="26" customHeight="1">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>6135792.28</v>
-      </c>
-      <c r="D43" s="7">
-        <f>C43/2</f>
-        <v/>
-      </c>
-      <c r="E43" s="7">
-        <f>C43/2</f>
-        <v/>
-      </c>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Зарплата по банку</t>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>12490831.85</v>
+        <v>6135792.28</v>
       </c>
       <c r="D44" s="7">
         <f>C44/2</f>
@@ -1281,11 +1275,11 @@
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>141281.46</v>
+        <v>12490831.85</v>
       </c>
       <c r="D45" s="7">
         <f>C45/2</f>
@@ -1303,11 +1297,11 @@
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>373487.16</v>
+        <v>141281.46</v>
       </c>
       <c r="D46" s="7">
         <f>C46/2</f>
@@ -1325,11 +1319,11 @@
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>38726.66</v>
+        <v>373487.16</v>
       </c>
       <c r="D47" s="7">
         <f>C47/2</f>
@@ -1345,54 +1339,60 @@
       <c r="I47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D48" s="19">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Алименты (удержание из зарплаты)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>38726.66</v>
+      </c>
+      <c r="D48" s="7">
         <f>C48/2</f>
         <v/>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="7">
         <f>C48/2</f>
         <v/>
       </c>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D49" s="19">
+        <f>C49/2</f>
+        <v/>
+      </c>
+      <c r="E49" s="19">
+        <f>C49/2</f>
+        <v/>
+      </c>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>39819623</v>
-      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
@@ -1403,11 +1403,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>4527900</v>
+        <v>39819623</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
@@ -1419,11 +1419,11 @@
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>3298432.06</v>
+        <v>4527900</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
@@ -1435,11 +1435,11 @@
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>2887658</v>
+        <v>3298432.06</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
@@ -1451,11 +1451,11 @@
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>2250790.16</v>
+        <v>2887658</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
@@ -1467,11 +1467,11 @@
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>827352.65</v>
+        <v>2250790.16</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
@@ -1483,11 +1483,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>515528</v>
+        <v>827352.65</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1499,11 +1499,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1515,11 +1515,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1531,11 +1531,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>582359.62</v>
+        <v>345200</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1545,12 +1545,14 @@
       <c r="I59" s="8" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>582359.62</v>
+      </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
@@ -1559,14 +1561,12 @@
       <c r="I60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="n">
-        <v>4692500</v>
-      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
@@ -1577,11 +1577,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1593,11 +1593,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1609,11 +1609,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>878789.77</v>
+        <v>1155000</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1625,11 +1625,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ЗП Заведягин ОН</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>570005</v>
+        <v>878789.77</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1641,11 +1641,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            ЗП Заведягин ОН</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>516000</v>
+        <v>570005</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1657,11 +1657,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>435435</v>
+        <v>516000</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1673,11 +1673,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>337440</v>
+        <v>435435</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1689,11 +1689,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>330000</v>
+        <v>337440</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1705,11 +1705,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1721,11 +1721,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>2621284.79</v>
+        <v>320000</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1735,163 +1735,156 @@
       <c r="I71" s="8" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>2621284.79</v>
+      </c>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+      <c r="G72" s="8" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
-      <c r="C72" s="15">
-        <f>SUM(C43:C48)</f>
-        <v/>
-      </c>
-      <c r="D72" s="15">
-        <f>SUM(D43:D48)</f>
-        <v/>
-      </c>
-      <c r="E72" s="15">
-        <f>SUM(E43:E48)</f>
-        <v/>
-      </c>
-      <c r="F72" s="16" t="n"/>
-      <c r="G72" s="16" t="n"/>
-      <c r="H72" s="16" t="n"/>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="C73" s="15">
+        <f>SUM(C44:C49)</f>
+        <v/>
+      </c>
+      <c r="D73" s="15">
+        <f>SUM(D44:D49)</f>
+        <v/>
+      </c>
+      <c r="E73" s="15">
+        <f>SUM(E44:E49)</f>
+        <v/>
+      </c>
+      <c r="F73" s="16" t="n"/>
+      <c r="G73" s="16" t="n"/>
+      <c r="H73" s="16" t="n"/>
+      <c r="I73" s="17" t="inlineStr">
         <is>
           <t>строки «в том числе» в сумму не входят</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="21" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C73" s="22" t="n">
+      <c r="C74" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="8" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="3" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="26" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
+    <row r="77" ht="26" customHeight="1">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C77" s="7">
-        <f>D77+E77</f>
-        <v/>
-      </c>
-      <c r="D77" s="7">
-        <f>D34</f>
-        <v/>
-      </c>
-      <c r="E77" s="7">
-        <f>E34</f>
-        <v/>
-      </c>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
+          <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
       <c r="C78" s="7">
-        <f>F34</f>
+        <f>D78+E78</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>F34/2</f>
+        <f>D34</f>
         <v/>
       </c>
       <c r="E78" s="7">
-        <f>F34/2</f>
+        <f>E34</f>
         <v/>
       </c>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C79" s="7">
-        <f>H34</f>
+        <f>F34</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>H34/2</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="E79" s="7">
-        <f>H34/2</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="F79" s="8" t="n"/>
@@ -1902,19 +1895,19 @@
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C80" s="7">
-        <f>G34</f>
+        <f>H34</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>G34/2</f>
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="E80" s="7">
-        <f>G34/2</f>
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="F80" s="8" t="n"/>
@@ -1925,45 +1918,41 @@
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="n">
-        <v>396337.24</v>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C81" s="7">
+        <f>G34</f>
+        <v/>
       </c>
       <c r="D81" s="7">
-        <f>C81/2</f>
+        <f>G34/2</f>
         <v/>
       </c>
       <c r="E81" s="7">
-        <f>C81/2</f>
+        <f>G34/2</f>
         <v/>
       </c>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I81" s="8" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C82" s="24">
-        <f>-C72</f>
-        <v/>
-      </c>
-      <c r="D82" s="24">
-        <f>-D72</f>
-        <v/>
-      </c>
-      <c r="E82" s="24">
-        <f>-E72</f>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D82" s="7">
+        <f>C82/2</f>
+        <v/>
+      </c>
+      <c r="E82" s="7">
+        <f>C82/2</f>
         <v/>
       </c>
       <c r="F82" s="8" t="n"/>
@@ -1971,261 +1960,272 @@
       <c r="H82" s="8" t="n"/>
       <c r="I82" s="10" t="inlineStr">
         <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C83" s="24">
+        <f>-C73</f>
+        <v/>
+      </c>
+      <c r="D83" s="24">
+        <f>-D73</f>
+        <v/>
+      </c>
+      <c r="E83" s="24">
+        <f>-E73</f>
+        <v/>
+      </c>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
           <t>итог блока «Расходы», пополам</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="14" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C83" s="15">
-        <f>SUM(C77:C82)</f>
-        <v/>
-      </c>
-      <c r="D83" s="15">
-        <f>SUM(D77:D82)</f>
-        <v/>
-      </c>
-      <c r="E83" s="15">
-        <f>SUM(E77:E82)</f>
-        <v/>
-      </c>
-      <c r="F83" s="16" t="n"/>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16" t="n"/>
-      <c r="I83" s="16" t="n"/>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="B85" s="3" t="inlineStr">
+      <c r="C84" s="15">
+        <f>SUM(C78:C83)</f>
+        <v/>
+      </c>
+      <c r="D84" s="15">
+        <f>SUM(D78:D83)</f>
+        <v/>
+      </c>
+      <c r="E84" s="15">
+        <f>SUM(E78:E83)</f>
+        <v/>
+      </c>
+      <c r="F84" s="16" t="n"/>
+      <c r="G84" s="16" t="n"/>
+      <c r="H84" s="16" t="n"/>
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C85" s="4" t="n"/>
-      <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="4" t="n"/>
-      <c r="G85" s="4" t="n"/>
-      <c r="H85" s="4" t="n"/>
-      <c r="I85" s="4" t="inlineStr"/>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="B86" s="5" t="inlineStr">
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C87" s="7">
-        <f>C83</f>
-        <v/>
-      </c>
-      <c r="D87" s="7">
-        <f>D83</f>
-        <v/>
-      </c>
-      <c r="E87" s="7">
-        <f>E83</f>
-        <v/>
-      </c>
-      <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
+          <t>Доход за месяц</t>
         </is>
       </c>
       <c r="C88" s="7">
-        <f>D88+E88</f>
-        <v/>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E88" s="7" t="n">
-        <v>45275972.21</v>
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="D88" s="7">
+        <f>D84</f>
+        <v/>
+      </c>
+      <c r="E88" s="7">
+        <f>E84</f>
+        <v/>
       </c>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I88" s="8" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C89" s="24">
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C89" s="7">
         <f>D89+E89</f>
         <v/>
       </c>
-      <c r="D89" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E89" s="24" t="n">
-        <v>-5882353</v>
+      <c r="D89" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
       <c r="I89" s="10" t="inlineStr">
         <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="23" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C90" s="24">
+        <f>D90+E90</f>
+        <v/>
+      </c>
+      <c r="D90" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E90" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="14" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C90" s="15">
-        <f>SUM(C87:C89)</f>
-        <v/>
-      </c>
-      <c r="D90" s="15">
-        <f>SUM(D87:D89)</f>
-        <v/>
-      </c>
-      <c r="E90" s="15">
-        <f>SUM(E87:E89)</f>
-        <v/>
-      </c>
-      <c r="F90" s="16" t="n"/>
-      <c r="G90" s="16" t="n"/>
-      <c r="H90" s="16" t="n"/>
-      <c r="I90" s="16" t="n"/>
-    </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="B92" s="3" t="inlineStr">
+      <c r="C91" s="15">
+        <f>SUM(C88:C90)</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>SUM(D88:D90)</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>SUM(E88:E90)</f>
+        <v/>
+      </c>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="B93" s="5" t="inlineStr">
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — лимит</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>27545367</v>
+        <v>30000000</v>
       </c>
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>долг на дату отчёта</t>
-        </is>
-      </c>
+      <c r="I95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — выбрано</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>2454633</v>
+        <v>27545367</v>
       </c>
       <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>долг на дату отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>396337.24</v>
+        <v>2454633</v>
       </c>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
@@ -2237,36 +2237,52 @@
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="n"/>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="n">
-        <v>373487.16</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4228,7 +4244,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>1197075</v>
+        <v>4365745</v>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
@@ -4243,7 +4259,7 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>4598500</v>
+        <v>2545000</v>
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
@@ -4258,7 +4274,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>4484200</v>
+        <v>4277000</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
@@ -4273,7 +4289,7 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>4073500</v>
+        <v>4552200</v>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
@@ -4288,7 +4304,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>3208094</v>
+        <v>2728594</v>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
@@ -4303,7 +4319,7 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>2403200</v>
+        <v>1615200</v>
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
@@ -4318,7 +4334,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>2301500</v>
+        <v>3019500</v>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
@@ -4333,7 +4349,7 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>1938000</v>
+        <v>3852280</v>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
@@ -4348,7 +4364,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>3858000</v>
+        <v>1491000</v>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
@@ -4363,7 +4379,7 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>1686075</v>
+        <v>3202575</v>
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -71,11 +71,11 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00807A70"/>
+      <color rgb="008A7350"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="008A7350"/>
+      <color rgb="00807A70"/>
       <sz val="11"/>
     </font>
     <font>
@@ -164,14 +164,14 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I100"/>
+  <dimension ref="B1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1205,125 +1205,99 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: оказано услуг за месяц</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>94366672</v>
+      </c>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: авансы под будущие операции</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>3340762</v>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 3,4% выручки месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="B43" s="5" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>6135792.28</v>
-      </c>
-      <c r="D44" s="7">
-        <f>C44/2</f>
-        <v/>
-      </c>
-      <c r="E44" s="7">
-        <f>C44/2</f>
-        <v/>
-      </c>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Зарплата по банку</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>12490831.85</v>
-      </c>
-      <c r="D45" s="7">
-        <f>C45/2</f>
-        <v/>
-      </c>
-      <c r="E45" s="7">
-        <f>C45/2</f>
-        <v/>
-      </c>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Услуги банка (общие)</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>141281.46</v>
-      </c>
-      <c r="D46" s="7">
-        <f>C46/2</f>
-        <v/>
-      </c>
-      <c r="E46" s="7">
-        <f>C46/2</f>
-        <v/>
-      </c>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>373487.16</v>
+        <v>6135792.28</v>
       </c>
       <c r="D47" s="7">
         <f>C47/2</f>
@@ -1341,11 +1315,11 @@
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>38726.66</v>
+        <v>12490831.85</v>
       </c>
       <c r="D48" s="7">
         <f>C48/2</f>
@@ -1361,40 +1335,44 @@
       <c r="I48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D49" s="19">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Услуги банка (общие)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>141281.46</v>
+      </c>
+      <c r="D49" s="7">
         <f>C49/2</f>
         <v/>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="7">
         <f>C49/2</f>
         <v/>
       </c>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Услуги банка (эквайринг)</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D50" s="7">
+        <f>C50/2</f>
+        <v/>
+      </c>
+      <c r="E50" s="7">
+        <f>C50/2</f>
+        <v/>
+      </c>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
@@ -1403,44 +1381,58 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+          <t>Алименты (удержание из зарплаты)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>39819623</v>
-      </c>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
+        <v>38726.66</v>
+      </c>
+      <c r="D51" s="7">
+        <f>C51/2</f>
+        <v/>
+      </c>
+      <c r="E51" s="7">
+        <f>C51/2</f>
+        <v/>
+      </c>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="8" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Импланты</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>4527900</v>
-      </c>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D52" s="21">
+        <f>C52/2</f>
+        <v/>
+      </c>
+      <c r="E52" s="21">
+        <f>C52/2</f>
+        <v/>
+      </c>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>3298432.06</v>
-      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
@@ -1451,11 +1443,11 @@
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>2887658</v>
+        <v>39819623</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
@@ -1467,11 +1459,11 @@
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>2250790.16</v>
+        <v>4527900</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
@@ -1483,11 +1475,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>827352.65</v>
+        <v>3298432.06</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1499,11 +1491,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>515528</v>
+        <v>2887658</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1515,11 +1507,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>376950</v>
+        <v>2250790.16</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1531,11 +1523,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>345200</v>
+        <v>827352.65</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1547,11 +1539,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>582359.62</v>
+        <v>515528</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1561,12 +1553,14 @@
       <c r="I60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Питание</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>376950</v>
+      </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
@@ -1577,11 +1571,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>4692500</v>
+        <v>345200</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1593,11 +1587,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>2505800</v>
+        <v>582359.62</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1607,14 +1601,12 @@
       <c r="I63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>1155000</v>
-      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
@@ -1625,11 +1617,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>878789.77</v>
+        <v>4692500</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1641,11 +1633,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ЗП Заведягин ОН</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>570005</v>
+        <v>2505800</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1657,11 +1649,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>516000</v>
+        <v>1155000</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1673,11 +1665,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>435435</v>
+        <v>878789.77</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1689,11 +1681,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            ЗП Заведягин ОН</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>337440</v>
+        <v>570005</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1705,11 +1697,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>330000</v>
+        <v>516000</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1721,11 +1713,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>320000</v>
+        <v>435435</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1737,11 +1729,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>2621284.79</v>
+        <v>337440</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1751,497 +1743,493 @@
       <c r="I72" s="8" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ</t>
-        </is>
-      </c>
-      <c r="C73" s="15">
-        <f>SUM(C44:C49)</f>
-        <v/>
-      </c>
-      <c r="D73" s="15">
-        <f>SUM(D44:D49)</f>
-        <v/>
-      </c>
-      <c r="E73" s="15">
-        <f>SUM(E44:E49)</f>
-        <v/>
-      </c>
-      <c r="F73" s="16" t="n"/>
-      <c r="G73" s="16" t="n"/>
-      <c r="H73" s="16" t="n"/>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
-        </is>
-      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Услуги юриста</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>Справочно: ремонт за счёт кредитной линии</t>
-        </is>
-      </c>
-      <c r="C74" s="22" t="n">
-        <v>11000000</v>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Складской учет</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>320000</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="I74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>2621284.79</v>
+      </c>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ</t>
+        </is>
+      </c>
+      <c r="C76" s="15">
+        <f>SUM(C47:C52)</f>
+        <v/>
+      </c>
+      <c r="D76" s="15">
+        <f>SUM(D47:D52)</f>
+        <v/>
+      </c>
+      <c r="E76" s="15">
+        <f>SUM(E47:E52)</f>
+        <v/>
+      </c>
+      <c r="F76" s="16" t="n"/>
+      <c r="G76" s="16" t="n"/>
+      <c r="H76" s="16" t="n"/>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: ремонт за счёт кредитной линии</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="B76" s="3" t="inlineStr">
+    <row r="79" ht="22" customHeight="1">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="B77" s="5" t="inlineStr">
+    <row r="80" ht="26" customHeight="1">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C78" s="7">
-        <f>D78+E78</f>
-        <v/>
-      </c>
-      <c r="D78" s="7">
-        <f>D34</f>
-        <v/>
-      </c>
-      <c r="E78" s="7">
-        <f>E34</f>
-        <v/>
-      </c>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>2. Половина выручки других хирургов</t>
-        </is>
-      </c>
-      <c r="C79" s="7">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="D79" s="7">
-        <f>F34/2</f>
-        <v/>
-      </c>
-      <c r="E79" s="7">
-        <f>F34/2</f>
-        <v/>
-      </c>
-      <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="8" t="n"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>3. Половина выручки косметологии</t>
-        </is>
-      </c>
-      <c r="C80" s="7">
-        <f>H34</f>
-        <v/>
-      </c>
-      <c r="D80" s="7">
-        <f>H34/2</f>
-        <v/>
-      </c>
-      <c r="E80" s="7">
-        <f>H34/2</f>
-        <v/>
-      </c>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
       <c r="C81" s="7">
-        <f>G34</f>
+        <f>D81+E81</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>G34/2</f>
+        <f>D34</f>
         <v/>
       </c>
       <c r="E81" s="7">
-        <f>G34/2</f>
+        <f>E34</f>
         <v/>
       </c>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
-      <c r="I81" s="8" t="n"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="n">
-        <v>396337.24</v>
+          <t>2. Половина выручки других хирургов</t>
+        </is>
+      </c>
+      <c r="C82" s="7">
+        <f>F34</f>
+        <v/>
       </c>
       <c r="D82" s="7">
-        <f>C82/2</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="E82" s="7">
-        <f>C82/2</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I82" s="8" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C83" s="24">
-        <f>-C73</f>
-        <v/>
-      </c>
-      <c r="D83" s="24">
-        <f>-D73</f>
-        <v/>
-      </c>
-      <c r="E83" s="24">
-        <f>-E73</f>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>3. Половина выручки косметологии</t>
+        </is>
+      </c>
+      <c r="C83" s="7">
+        <f>H34</f>
+        <v/>
+      </c>
+      <c r="D83" s="7">
+        <f>H34/2</f>
+        <v/>
+      </c>
+      <c r="E83" s="7">
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="I83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C84" s="7">
+        <f>G34</f>
+        <v/>
+      </c>
+      <c r="D84" s="7">
+        <f>G34/2</f>
+        <v/>
+      </c>
+      <c r="E84" s="7">
+        <f>G34/2</f>
+        <v/>
+      </c>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="8" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D85" s="7">
+        <f>C85/2</f>
+        <v/>
+      </c>
+      <c r="E85" s="7">
+        <f>C85/2</f>
+        <v/>
+      </c>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C86" s="24">
+        <f>-C76</f>
+        <v/>
+      </c>
+      <c r="D86" s="24">
+        <f>-D76</f>
+        <v/>
+      </c>
+      <c r="E86" s="24">
+        <f>-E76</f>
+        <v/>
+      </c>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="8" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <t>итог блока «Расходы», пополам</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="14" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C84" s="15">
-        <f>SUM(C78:C83)</f>
-        <v/>
-      </c>
-      <c r="D84" s="15">
-        <f>SUM(D78:D83)</f>
-        <v/>
-      </c>
-      <c r="E84" s="15">
-        <f>SUM(E78:E83)</f>
-        <v/>
-      </c>
-      <c r="F84" s="16" t="n"/>
-      <c r="G84" s="16" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="B86" s="3" t="inlineStr">
+      <c r="C87" s="15">
+        <f>SUM(C81:C86)</f>
+        <v/>
+      </c>
+      <c r="D87" s="15">
+        <f>SUM(D81:D86)</f>
+        <v/>
+      </c>
+      <c r="E87" s="15">
+        <f>SUM(E81:E86)</f>
+        <v/>
+      </c>
+      <c r="F87" s="16" t="n"/>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="inlineStr"/>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="B87" s="5" t="inlineStr">
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="6" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Доход за месяц</t>
         </is>
       </c>
-      <c r="C88" s="7">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="D88" s="7">
-        <f>D84</f>
-        <v/>
-      </c>
-      <c r="E88" s="7">
-        <f>E84</f>
-        <v/>
-      </c>
-      <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="6" t="inlineStr">
+      <c r="C91" s="7">
+        <f>C87</f>
+        <v/>
+      </c>
+      <c r="D91" s="7">
+        <f>D87</f>
+        <v/>
+      </c>
+      <c r="E91" s="7">
+        <f>E87</f>
+        <v/>
+      </c>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Остаток с прошлого месяца</t>
         </is>
       </c>
-      <c r="C89" s="7">
-        <f>D89+E89</f>
-        <v/>
-      </c>
-      <c r="D89" s="7" t="n">
+      <c r="C92" s="7">
+        <f>D92+E92</f>
+        <v/>
+      </c>
+      <c r="D92" s="7" t="n">
         <v>30658896.02</v>
       </c>
-      <c r="E89" s="7" t="n">
+      <c r="E92" s="7" t="n">
         <v>45275972.21</v>
       </c>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="10" t="inlineStr">
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="23" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="23" t="inlineStr">
         <is>
           <t>Выплачены дивиденды</t>
         </is>
       </c>
-      <c r="C90" s="24">
-        <f>D90+E90</f>
-        <v/>
-      </c>
-      <c r="D90" s="24" t="n">
+      <c r="C93" s="24">
+        <f>D93+E93</f>
+        <v/>
+      </c>
+      <c r="D93" s="24" t="n">
         <v>-5882353</v>
       </c>
-      <c r="E90" s="24" t="n">
+      <c r="E93" s="24" t="n">
         <v>-5882353</v>
       </c>
-      <c r="F90" s="8" t="n"/>
-      <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="14" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C91" s="15">
-        <f>SUM(C88:C90)</f>
-        <v/>
-      </c>
-      <c r="D91" s="15">
-        <f>SUM(D88:D90)</f>
-        <v/>
-      </c>
-      <c r="E91" s="15">
-        <f>SUM(E88:E90)</f>
-        <v/>
-      </c>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="16" t="n"/>
-      <c r="H91" s="16" t="n"/>
-      <c r="I91" s="16" t="n"/>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="B93" s="3" t="inlineStr">
+      <c r="C94" s="15">
+        <f>SUM(C91:C93)</f>
+        <v/>
+      </c>
+      <c r="D94" s="15">
+        <f>SUM(D91:D93)</f>
+        <v/>
+      </c>
+      <c r="E94" s="15">
+        <f>SUM(E91:E93)</f>
+        <v/>
+      </c>
+      <c r="F94" s="16" t="n"/>
+      <c r="G94" s="16" t="n"/>
+      <c r="H94" s="16" t="n"/>
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="B94" s="5" t="inlineStr">
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — лимит</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="8" t="n"/>
-      <c r="F95" s="8" t="n"/>
-      <c r="G95" s="8" t="n"/>
-      <c r="H95" s="8" t="n"/>
-      <c r="I95" s="8" t="n"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — выбрано</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="n">
-        <v>27545367</v>
-      </c>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>долг на дату отчёта</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — свободный остаток</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="n">
-        <v>2454633</v>
-      </c>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="8" t="n"/>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C98" s="7" t="n">
-        <v>396337.24</v>
+        <v>30000000</v>
       </c>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
@@ -2253,10 +2241,12 @@
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="n"/>
+          <t>Кредитная линия — выбрано</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>27545367</v>
+      </c>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
@@ -2264,18 +2254,18 @@
       <c r="H99" s="8" t="n"/>
       <c r="I99" s="10" t="inlineStr">
         <is>
-          <t>не проставлен</t>
+          <t>долг на дату отчёта</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>373487.16</v>
+        <v>2454633</v>
       </c>
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
@@ -2283,6 +2273,56 @@
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
       <c r="I100" s="8" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="8" t="n"/>
+      <c r="G102" s="8" t="n"/>
+      <c r="H102" s="8" t="n"/>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="8" t="n"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -1539,11 +1539,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>515528</v>
+        <v>570005</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1555,11 +1555,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1571,11 +1571,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1587,11 +1587,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>582359.62</v>
+        <v>345200</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1601,12 +1601,14 @@
       <c r="I63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>582359.62</v>
+      </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
@@ -1615,14 +1617,12 @@
       <c r="I64" s="8" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="n">
-        <v>4692500</v>
-      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
@@ -1633,11 +1633,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1649,11 +1649,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1665,11 +1665,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>878789.77</v>
+        <v>1155000</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1681,11 +1681,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ЗП Заведягин ОН</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>570005</v>
+        <v>878789.77</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>ЗП Заведягин ОН</t>
+          <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
     </row>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -1555,7 +1555,7 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            18550-расходка, 320588-мед.оборудованеи</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t>18550-расходка, 320588-мед.оборудованеи</t>
+          <t>Медоборудование и расходники</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D95" s="26" t="inlineStr">
         <is>
-          <t>утилизация мед отходов до июль-октябрь</t>
+          <t>Утилизация медотходов</t>
         </is>
       </c>
     </row>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -71,15 +71,15 @@
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="00A3423B"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <color rgb="008A7350"/>
       <sz val="11"/>
     </font>
     <font>
       <color rgb="00807A70"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="00A3423B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -161,21 +161,21 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I103"/>
+  <dimension ref="B1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1100,13 +1100,13 @@
         <v>13054662.21</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>77250611.63</v>
+        <v>76845979.75</v>
       </c>
       <c r="G34" s="15" t="n">
         <v>261238.64</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>2960140.06</v>
+        <v>2959191.93</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>1071080</v>
+        <v>1035500</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
@@ -1185,54 +1185,50 @@
       <c r="I39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Возвраты пациентам</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>-370000</v>
+      </c>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C40" s="12">
-        <f>SUM(C37:C39)</f>
-        <v/>
-      </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="C41" s="12">
+        <f>SUM(C37:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="19" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Справочно: оказано услуг за месяц</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C43" s="22" t="n">
         <v>94366672</v>
-      </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>Справочно: авансы под будущие операции</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="n">
-        <v>3340762</v>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
@@ -1241,85 +1237,83 @@
       <c r="H43" s="8" t="n"/>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 3,4% выручки месяца</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="3" t="inlineStr">
+          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Справочно: авансы под будущие операции</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>2935181.99</v>
+      </c>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 3,0% выручки месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="B46" s="5" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>6135792.28</v>
-      </c>
-      <c r="D47" s="7">
-        <f>C47/2</f>
-        <v/>
-      </c>
-      <c r="E47" s="7">
-        <f>C47/2</f>
-        <v/>
-      </c>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Зарплата по банку</t>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>12490831.85</v>
+        <v>6135792.28</v>
       </c>
       <c r="D48" s="7">
         <f>C48/2</f>
@@ -1337,11 +1331,11 @@
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>141281.46</v>
+        <v>12490831.85</v>
       </c>
       <c r="D49" s="7">
         <f>C49/2</f>
@@ -1359,11 +1353,11 @@
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>373487.16</v>
+        <v>141281.46</v>
       </c>
       <c r="D50" s="7">
         <f>C50/2</f>
@@ -1381,11 +1375,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>38726.66</v>
+        <v>373487.16</v>
       </c>
       <c r="D51" s="7">
         <f>C51/2</f>
@@ -1401,54 +1395,60 @@
       <c r="I51" s="8" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D52" s="21">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Алименты (удержание из зарплаты)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>38726.66</v>
+      </c>
+      <c r="D52" s="7">
         <f>C52/2</f>
         <v/>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="7">
         <f>C52/2</f>
         <v/>
       </c>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D53" s="23">
+        <f>C53/2</f>
+        <v/>
+      </c>
+      <c r="E53" s="23">
+        <f>C53/2</f>
+        <v/>
+      </c>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>39819623</v>
-      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
@@ -1459,11 +1459,11 @@
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>4527900</v>
+        <v>39819623</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
@@ -1475,11 +1475,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>3298432.06</v>
+        <v>4527900</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1491,11 +1491,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>2887658</v>
+        <v>3298432.06</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1507,11 +1507,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>2250790.16</v>
+        <v>2887658</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1523,11 +1523,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>827352.65</v>
+        <v>2250790.16</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1539,11 +1539,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>570005</v>
+        <v>827352.65</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1555,11 +1555,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование и расходники</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>515528</v>
+        <v>570005</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1571,11 +1571,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1587,11 +1587,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1603,11 +1603,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>582359.62</v>
+        <v>345200</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1617,12 +1617,14 @@
       <c r="I64" s="8" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>582359.62</v>
+      </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
@@ -1631,14 +1633,12 @@
       <c r="I65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>4692500</v>
-      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
@@ -1649,11 +1649,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1665,11 +1665,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1681,11 +1681,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>878789.77</v>
+        <v>1155000</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1697,11 +1697,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>516000</v>
+        <v>878789.77</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1713,11 +1713,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>435435</v>
+        <v>516000</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1729,11 +1729,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>337440</v>
+        <v>435435</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1745,11 +1745,11 @@
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>330000</v>
+        <v>337440</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -1761,11 +1761,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1777,11 +1777,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>2621284.79</v>
+        <v>320000</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1791,163 +1791,156 @@
       <c r="I75" s="8" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>2621284.79</v>
+      </c>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
-      <c r="C76" s="15">
-        <f>SUM(C47:C52)</f>
-        <v/>
-      </c>
-      <c r="D76" s="15">
-        <f>SUM(D47:D52)</f>
-        <v/>
-      </c>
-      <c r="E76" s="15">
-        <f>SUM(E47:E52)</f>
-        <v/>
-      </c>
-      <c r="F76" s="16" t="n"/>
-      <c r="G76" s="16" t="n"/>
-      <c r="H76" s="16" t="n"/>
-      <c r="I76" s="17" t="inlineStr">
+      <c r="C77" s="15">
+        <f>SUM(C48:C53)</f>
+        <v/>
+      </c>
+      <c r="D77" s="15">
+        <f>SUM(D48:D53)</f>
+        <v/>
+      </c>
+      <c r="E77" s="15">
+        <f>SUM(E48:E53)</f>
+        <v/>
+      </c>
+      <c r="F77" s="16" t="n"/>
+      <c r="G77" s="16" t="n"/>
+      <c r="H77" s="16" t="n"/>
+      <c r="I77" s="17" t="inlineStr">
         <is>
           <t>строки «в том числе» в сумму не входят</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="19" t="inlineStr">
+    <row r="78">
+      <c r="B78" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C77" s="20" t="n">
+      <c r="C78" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="B79" s="3" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="26" customHeight="1">
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81" ht="26" customHeight="1">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C81" s="7">
-        <f>D81+E81</f>
-        <v/>
-      </c>
-      <c r="D81" s="7">
-        <f>D34</f>
-        <v/>
-      </c>
-      <c r="E81" s="7">
-        <f>E34</f>
-        <v/>
-      </c>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
+          <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
       <c r="C82" s="7">
-        <f>F34</f>
+        <f>D82+E82</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>F34/2</f>
+        <f>D34</f>
         <v/>
       </c>
       <c r="E82" s="7">
-        <f>F34/2</f>
+        <f>E34</f>
         <v/>
       </c>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C83" s="7">
-        <f>H34</f>
+        <f>F34</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>H34/2</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="E83" s="7">
-        <f>H34/2</f>
+        <f>F34/2</f>
         <v/>
       </c>
       <c r="F83" s="8" t="n"/>
@@ -1958,19 +1951,19 @@
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C84" s="7">
-        <f>G34</f>
+        <f>H34</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>G34/2</f>
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="E84" s="7">
-        <f>G34/2</f>
+        <f>H34/2</f>
         <v/>
       </c>
       <c r="F84" s="8" t="n"/>
@@ -1981,45 +1974,41 @@
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="n">
-        <v>396337.24</v>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C85" s="7">
+        <f>G34</f>
+        <v/>
       </c>
       <c r="D85" s="7">
-        <f>C85/2</f>
+        <f>G34/2</f>
         <v/>
       </c>
       <c r="E85" s="7">
-        <f>C85/2</f>
+        <f>G34/2</f>
         <v/>
       </c>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I85" s="8" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C86" s="24">
-        <f>-C76</f>
-        <v/>
-      </c>
-      <c r="D86" s="24">
-        <f>-D76</f>
-        <v/>
-      </c>
-      <c r="E86" s="24">
-        <f>-E76</f>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D86" s="7">
+        <f>C86/2</f>
+        <v/>
+      </c>
+      <c r="E86" s="7">
+        <f>C86/2</f>
         <v/>
       </c>
       <c r="F86" s="8" t="n"/>
@@ -2027,245 +2016,260 @@
       <c r="H86" s="8" t="n"/>
       <c r="I86" s="10" t="inlineStr">
         <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C87" s="19">
+        <f>-C77</f>
+        <v/>
+      </c>
+      <c r="D87" s="19">
+        <f>-D77</f>
+        <v/>
+      </c>
+      <c r="E87" s="19">
+        <f>-E77</f>
+        <v/>
+      </c>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
           <t>итог блока «Расходы», пополам</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="14" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>7. Личные анализы: каждый несёт свои</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="19" t="n">
+        <v>-9186</v>
+      </c>
+      <c r="E88" s="19" t="n">
+        <v>9186</v>
+      </c>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>лист «Расходы врачей»: Маланичев 30 620, Погосян 12 248</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C87" s="15">
-        <f>SUM(C81:C86)</f>
-        <v/>
-      </c>
-      <c r="D87" s="15">
-        <f>SUM(D81:D86)</f>
-        <v/>
-      </c>
-      <c r="E87" s="15">
-        <f>SUM(E81:E86)</f>
-        <v/>
-      </c>
-      <c r="F87" s="16" t="n"/>
-      <c r="G87" s="16" t="n"/>
-      <c r="H87" s="16" t="n"/>
-      <c r="I87" s="16" t="n"/>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="B89" s="3" t="inlineStr">
+      <c r="C89" s="15">
+        <f>SUM(C82:C88)</f>
+        <v/>
+      </c>
+      <c r="D89" s="15">
+        <f>SUM(D82:D88)</f>
+        <v/>
+      </c>
+      <c r="E89" s="15">
+        <f>SUM(E82:E88)</f>
+        <v/>
+      </c>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="16" t="n"/>
+      <c r="H89" s="16" t="n"/>
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90" ht="26" customHeight="1">
-      <c r="B90" s="5" t="inlineStr">
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="6" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Доход за месяц</t>
         </is>
       </c>
-      <c r="C91" s="7">
-        <f>C87</f>
-        <v/>
-      </c>
-      <c r="D91" s="7">
-        <f>D87</f>
-        <v/>
-      </c>
-      <c r="E91" s="7">
-        <f>E87</f>
-        <v/>
-      </c>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="8" t="n"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C92" s="7">
-        <f>D92+E92</f>
-        <v/>
-      </c>
-      <c r="D92" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E92" s="7" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="F92" s="8" t="n"/>
-      <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C93" s="24">
-        <f>D93+E93</f>
-        <v/>
-      </c>
-      <c r="D93" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E93" s="24" t="n">
-        <v>-5882353</v>
+      <c r="C93" s="7">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="D93" s="7">
+        <f>D89</f>
+        <v/>
+      </c>
+      <c r="E93" s="7">
+        <f>E89</f>
+        <v/>
       </c>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="n"/>
-      <c r="I93" s="10" t="inlineStr">
+      <c r="I93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C94" s="7">
+        <f>D94+E94</f>
+        <v/>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C95" s="19">
+        <f>D95+E95</f>
+        <v/>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="10" t="inlineStr">
         <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="14" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C94" s="15">
-        <f>SUM(C91:C93)</f>
-        <v/>
-      </c>
-      <c r="D94" s="15">
-        <f>SUM(D91:D93)</f>
-        <v/>
-      </c>
-      <c r="E94" s="15">
-        <f>SUM(E91:E93)</f>
-        <v/>
-      </c>
-      <c r="F94" s="16" t="n"/>
-      <c r="G94" s="16" t="n"/>
-      <c r="H94" s="16" t="n"/>
-      <c r="I94" s="16" t="n"/>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="B96" s="3" t="inlineStr">
+      <c r="C96" s="15">
+        <f>SUM(C93:C95)</f>
+        <v/>
+      </c>
+      <c r="D96" s="15">
+        <f>SUM(D93:D95)</f>
+        <v/>
+      </c>
+      <c r="E96" s="15">
+        <f>SUM(E93:E95)</f>
+        <v/>
+      </c>
+      <c r="F96" s="16" t="n"/>
+      <c r="G96" s="16" t="n"/>
+      <c r="H96" s="16" t="n"/>
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97" ht="26" customHeight="1">
-      <c r="B97" s="5" t="inlineStr">
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99" ht="26" customHeight="1">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — лимит</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — выбрано</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="n">
-        <v>27545367</v>
-      </c>
-      <c r="D99" s="8" t="n"/>
-      <c r="E99" s="8" t="n"/>
-      <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>долг на дату отчёта</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>2454633</v>
+        <v>30000000</v>
       </c>
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
@@ -2277,45 +2281,47 @@
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Кредитная линия — выбрано</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>396337.24</v>
+        <v>27545367</v>
       </c>
       <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>долг на дату отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="n"/>
+          <t>Кредитная линия — свободный остаток</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>2454633</v>
+      </c>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I102" s="8" t="n"/>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Проценты по депозитам за месяц</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>373487.16</v>
+        <v>396337.24</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
@@ -2323,6 +2329,40 @@
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
       <c r="I103" s="8" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="8" t="n"/>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
+      <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4220,7 +4260,7 @@
       <c r="F127" s="13" t="n"/>
       <c r="G127" s="13" t="n"/>
       <c r="H127" s="13" t="n"/>
-      <c r="I127" s="18" t="inlineStr">
+      <c r="I127" s="20" t="inlineStr">
         <is>
           <t>в т.ч. за счёт кредитной линии — см. справочную строку основного листа</t>
         </is>
@@ -4344,7 +4384,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>2728594</v>
+        <v>2698594</v>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
@@ -4389,7 +4429,7 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3852280</v>
+        <v>3846700</v>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I105"/>
+  <dimension ref="B1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>153295343.14</v>
+        <v>153496343.14</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
@@ -868,11 +868,11 @@
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Налоги</t>
+          <t xml:space="preserve">    Погашение кредита</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7871244.91</v>
+        <v>204388.93</v>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
@@ -881,18 +881,18 @@
       <c r="H23" s="8" t="n"/>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>кор. счёт 68</t>
+          <t>кор. счёт 67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Страховые взносы</t>
+          <t xml:space="preserve">    Налоги</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>29253.37</v>
+        <v>7871244.91</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
@@ -901,18 +901,18 @@
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>кор. счёт 69</t>
+          <t>кор. счёт 68</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Зарплата</t>
+          <t xml:space="preserve">    Страховые взносы</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>12490831.85</v>
+        <v>29253.37</v>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
@@ -921,18 +921,18 @@
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>кор. счёт 70</t>
+          <t>кор. счёт 69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Выплата дивидендов</t>
+          <t xml:space="preserve">    Зарплата</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>10000000</v>
+        <v>12490831.85</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
@@ -941,18 +941,18 @@
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>кор. счёт 75</t>
+          <t>кор. счёт 70</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Алименты</t>
+          <t xml:space="preserve">    Выплата дивидендов</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>38726.66</v>
+        <v>10000000</v>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
@@ -961,18 +961,18 @@
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>кор. счёт 76</t>
+          <t>кор. счёт 75</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Услуги банка</t>
+          <t xml:space="preserve">    Алименты</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>137448.82</v>
+        <v>38726.66</v>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
@@ -981,181 +981,181 @@
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="10" t="inlineStr">
         <is>
+          <t>кор. счёт 76</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Услуги банка</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>141191.07</v>
+      </c>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
           <t>кор. счёт 91</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Итого списания</t>
         </is>
       </c>
-      <c r="C29" s="12">
-        <f>SUM(C19:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
+      <c r="C30" s="12">
+        <f>SUM(C19:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Остаток на конец месяца</t>
         </is>
       </c>
-      <c r="C30" s="15">
-        <f>C7+C16-C29</f>
-        <v/>
-      </c>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="C31" s="15">
+        <f>C7+C16-C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>начальный остаток + поступления − списания</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>2. ВЫРУЧКА</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>деньги, поступившие от пациентов за месяц</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="5" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Другие хирурги</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="14" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C34" s="15">
-        <f>SUM(D34:H34)</f>
-        <v/>
-      </c>
-      <c r="D34" s="15" t="n">
+      <c r="C35" s="15">
+        <f>SUM(D35:H35)</f>
+        <v/>
+      </c>
+      <c r="D35" s="15" t="n">
         <v>4180781.46</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E35" s="15" t="n">
         <v>13054662.21</v>
       </c>
-      <c r="F34" s="15" t="n">
-        <v>76845979.75</v>
-      </c>
-      <c r="G34" s="15" t="n">
+      <c r="F35" s="15" t="n">
+        <v>76495979.75</v>
+      </c>
+      <c r="G35" s="15" t="n">
         <v>261238.64</v>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H35" s="15" t="n">
         <v>2959191.93</v>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>по группам врачей</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="9" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>В том числе по каналам поступления</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Наличными</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>34981900</v>
-      </c>
+      <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>01–10.08: 10 688 500; 11–31.08: 24 293 400</t>
-        </is>
-      </c>
+      <c r="I37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Безналичными (эквайринг)</t>
+          <t xml:space="preserve">    Наличными</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>61654454</v>
+        <v>34981900</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
@@ -1164,34 +1164,38 @@
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 19 889 514; 11–31.08: 41 764 940</t>
+          <t>01–10.08: 10 688 500; 11–31.08: 24 293 400</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Оплаты физлиц на расчётный счёт</t>
+          <t xml:space="preserve">    Безналичными (эквайринг)</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>1035500</v>
+        <v>61654454</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>01–10.08: 19 889 514; 11–31.08: 41 764 940</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Возвраты пациентам</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="n">
-        <v>-370000</v>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Оплаты физлиц на расчётный счёт</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1035500</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
@@ -1201,54 +1205,50 @@
       <c r="I40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Возвраты пациентам</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>-720000</v>
+      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C41" s="12">
-        <f>SUM(C37:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="20" t="inlineStr">
+      <c r="C42" s="12">
+        <f>SUM(C38:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>Справочно: оказано услуг за месяц</t>
-        </is>
-      </c>
-      <c r="C43" s="22" t="n">
-        <v>94366672</v>
-      </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Справочно: авансы под будущие операции</t>
+          <t>Справочно: оказано услуг за месяц</t>
         </is>
       </c>
       <c r="C44" s="22" t="n">
-        <v>2935181.99</v>
+        <v>94366672</v>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
@@ -1257,85 +1257,83 @@
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 3,0% выручки месяца</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="3" t="inlineStr">
+          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Справочно: авансы под будущие операции</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="n">
+        <v>2585181.99</v>
+      </c>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 2,7% выручки месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="B47" s="5" t="inlineStr">
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>6135792.28</v>
-      </c>
-      <c r="D48" s="7">
-        <f>C48/2</f>
-        <v/>
-      </c>
-      <c r="E48" s="7">
-        <f>C48/2</f>
-        <v/>
-      </c>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Зарплата по банку</t>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>12490831.85</v>
+        <v>6135792.28</v>
       </c>
       <c r="D49" s="7">
         <f>C49/2</f>
@@ -1353,11 +1351,11 @@
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>141281.46</v>
+        <v>12490831.85</v>
       </c>
       <c r="D50" s="7">
         <f>C50/2</f>
@@ -1375,11 +1373,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>373487.16</v>
+        <v>141191.07</v>
       </c>
       <c r="D51" s="7">
         <f>C51/2</f>
@@ -1397,11 +1395,11 @@
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>38726.66</v>
+        <v>373487.16</v>
       </c>
       <c r="D52" s="7">
         <f>C52/2</f>
@@ -1417,54 +1415,60 @@
       <c r="I52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D53" s="23">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Алименты (удержание из зарплаты)</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>38726.66</v>
+      </c>
+      <c r="D53" s="7">
         <f>C53/2</f>
         <v/>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="7">
         <f>C53/2</f>
         <v/>
       </c>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D54" s="23">
+        <f>C54/2</f>
+        <v/>
+      </c>
+      <c r="E54" s="23">
+        <f>C54/2</f>
+        <v/>
+      </c>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>39819623</v>
-      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
@@ -1475,11 +1479,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>4527900</v>
+        <v>39819623</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1491,11 +1495,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>3298432.06</v>
+        <v>4527900</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1507,11 +1511,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>2887658</v>
+        <v>3298432.06</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1523,11 +1527,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>2250790.16</v>
+        <v>2887658</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1539,11 +1543,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>827352.65</v>
+        <v>2250790.16</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1555,11 +1559,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>570005</v>
+        <v>827352.65</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1571,11 +1575,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование и расходники</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>515528</v>
+        <v>570005</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1587,11 +1591,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1603,11 +1607,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1619,11 +1623,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>582359.62</v>
+        <v>345200</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1633,12 +1637,14 @@
       <c r="I65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>582359.62</v>
+      </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
@@ -1647,14 +1653,12 @@
       <c r="I66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>4692500</v>
-      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
@@ -1665,11 +1669,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1681,11 +1685,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1697,11 +1701,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>878789.77</v>
+        <v>1155000</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1713,11 +1717,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>516000</v>
+        <v>878789.77</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1729,11 +1733,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>435435</v>
+        <v>516000</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1745,11 +1749,11 @@
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>337440</v>
+        <v>435435</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -1761,11 +1765,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>330000</v>
+        <v>337440</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1777,11 +1781,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1793,11 +1797,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>2621284.79</v>
+        <v>320000</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1807,163 +1811,156 @@
       <c r="I76" s="8" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>2621284.79</v>
+      </c>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
-      <c r="C77" s="15">
-        <f>SUM(C48:C53)</f>
-        <v/>
-      </c>
-      <c r="D77" s="15">
-        <f>SUM(D48:D53)</f>
-        <v/>
-      </c>
-      <c r="E77" s="15">
-        <f>SUM(E48:E53)</f>
-        <v/>
-      </c>
-      <c r="F77" s="16" t="n"/>
-      <c r="G77" s="16" t="n"/>
-      <c r="H77" s="16" t="n"/>
-      <c r="I77" s="17" t="inlineStr">
+      <c r="C78" s="15">
+        <f>SUM(C49:C54)</f>
+        <v/>
+      </c>
+      <c r="D78" s="15">
+        <f>SUM(D49:D54)</f>
+        <v/>
+      </c>
+      <c r="E78" s="15">
+        <f>SUM(E49:E54)</f>
+        <v/>
+      </c>
+      <c r="F78" s="16" t="n"/>
+      <c r="G78" s="16" t="n"/>
+      <c r="H78" s="16" t="n"/>
+      <c r="I78" s="17" t="inlineStr">
         <is>
           <t>строки «в том числе» в сумму не входят</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="21" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C78" s="22" t="n">
+      <c r="C79" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="10" t="inlineStr">
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="8" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="B80" s="3" t="inlineStr">
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="26" customHeight="1">
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82" ht="26" customHeight="1">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C82" s="7">
-        <f>D82+E82</f>
-        <v/>
-      </c>
-      <c r="D82" s="7">
-        <f>D34</f>
-        <v/>
-      </c>
-      <c r="E82" s="7">
-        <f>E34</f>
-        <v/>
-      </c>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
+          <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
       <c r="C83" s="7">
-        <f>F34</f>
+        <f>D83+E83</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>F34/2</f>
+        <f>D35</f>
         <v/>
       </c>
       <c r="E83" s="7">
-        <f>F34/2</f>
+        <f>E35</f>
         <v/>
       </c>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C84" s="7">
-        <f>H34</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>H34/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="E84" s="7">
-        <f>H34/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="F84" s="8" t="n"/>
@@ -1974,19 +1971,19 @@
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C85" s="7">
-        <f>G34</f>
+        <f>H35</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>G34/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="E85" s="7">
-        <f>G34/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="F85" s="8" t="n"/>
@@ -1997,45 +1994,41 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="n">
-        <v>396337.24</v>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C86" s="7">
+        <f>G35</f>
+        <v/>
       </c>
       <c r="D86" s="7">
-        <f>C86/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="E86" s="7">
-        <f>C86/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I86" s="8" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="18" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C87" s="19">
-        <f>-C77</f>
-        <v/>
-      </c>
-      <c r="D87" s="19">
-        <f>-D77</f>
-        <v/>
-      </c>
-      <c r="E87" s="19">
-        <f>-E77</f>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D87" s="7">
+        <f>C87/2</f>
+        <v/>
+      </c>
+      <c r="E87" s="7">
+        <f>C87/2</f>
         <v/>
       </c>
       <c r="F87" s="8" t="n"/>
@@ -2043,285 +2036,296 @@
       <c r="H87" s="8" t="n"/>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>итог блока «Расходы», пополам</t>
+          <t>начислены банком на остатки</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="18" t="inlineStr">
         <is>
-          <t>7. Личные анализы: каждый несёт свои</t>
-        </is>
-      </c>
-      <c r="C88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="19" t="n">
-        <v>-9186</v>
-      </c>
-      <c r="E88" s="19" t="n">
-        <v>9186</v>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C88" s="19">
+        <f>-C78</f>
+        <v/>
+      </c>
+      <c r="D88" s="19">
+        <f>-D78</f>
+        <v/>
+      </c>
+      <c r="E88" s="19">
+        <f>-E78</f>
+        <v/>
       </c>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
       <c r="I88" s="10" t="inlineStr">
         <is>
+          <t>итог блока «Расходы», пополам</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>7. Личные анализы: каждый несёт свои</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>-9186</v>
+      </c>
+      <c r="E89" s="19" t="n">
+        <v>9186</v>
+      </c>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
           <t>лист «Расходы врачей»: Маланичев 30 620, Погосян 12 248</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="14" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C89" s="15">
-        <f>SUM(C82:C88)</f>
-        <v/>
-      </c>
-      <c r="D89" s="15">
-        <f>SUM(D82:D88)</f>
-        <v/>
-      </c>
-      <c r="E89" s="15">
-        <f>SUM(E82:E88)</f>
-        <v/>
-      </c>
-      <c r="F89" s="16" t="n"/>
-      <c r="G89" s="16" t="n"/>
-      <c r="H89" s="16" t="n"/>
-      <c r="I89" s="16" t="n"/>
-    </row>
-    <row r="91" ht="22" customHeight="1">
-      <c r="B91" s="3" t="inlineStr">
+      <c r="C90" s="15">
+        <f>SUM(C83:C89)</f>
+        <v/>
+      </c>
+      <c r="D90" s="15">
+        <f>SUM(D83:D89)</f>
+        <v/>
+      </c>
+      <c r="E90" s="15">
+        <f>SUM(E83:E89)</f>
+        <v/>
+      </c>
+      <c r="F90" s="16" t="n"/>
+      <c r="G90" s="16" t="n"/>
+      <c r="H90" s="16" t="n"/>
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="B92" s="5" t="inlineStr">
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C93" s="7">
-        <f>C89</f>
-        <v/>
-      </c>
-      <c r="D93" s="7">
-        <f>D89</f>
-        <v/>
-      </c>
-      <c r="E93" s="7">
-        <f>E89</f>
-        <v/>
-      </c>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
+          <t>Доход за месяц</t>
         </is>
       </c>
       <c r="C94" s="7">
-        <f>D94+E94</f>
-        <v/>
-      </c>
-      <c r="D94" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E94" s="7" t="n">
-        <v>45275972.21</v>
+        <f>C90</f>
+        <v/>
+      </c>
+      <c r="D94" s="7">
+        <f>D90</f>
+        <v/>
+      </c>
+      <c r="E94" s="7">
+        <f>E90</f>
+        <v/>
       </c>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
       <c r="H94" s="8" t="n"/>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I94" s="8" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="18" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C95" s="19">
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C95" s="7">
         <f>D95+E95</f>
         <v/>
       </c>
-      <c r="D95" s="19" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E95" s="19" t="n">
-        <v>-5882353</v>
+      <c r="D95" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
       <c r="I95" s="10" t="inlineStr">
         <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C96" s="19">
+        <f>D96+E96</f>
+        <v/>
+      </c>
+      <c r="D96" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E96" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="14" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C96" s="15">
-        <f>SUM(C93:C95)</f>
-        <v/>
-      </c>
-      <c r="D96" s="15">
-        <f>SUM(D93:D95)</f>
-        <v/>
-      </c>
-      <c r="E96" s="15">
-        <f>SUM(E93:E95)</f>
-        <v/>
-      </c>
-      <c r="F96" s="16" t="n"/>
-      <c r="G96" s="16" t="n"/>
-      <c r="H96" s="16" t="n"/>
-      <c r="I96" s="16" t="n"/>
-    </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="B98" s="3" t="inlineStr">
+      <c r="C97" s="15">
+        <f>SUM(C94:C96)</f>
+        <v/>
+      </c>
+      <c r="D97" s="15">
+        <f>SUM(D94:D96)</f>
+        <v/>
+      </c>
+      <c r="E97" s="15">
+        <f>SUM(E94:E96)</f>
+        <v/>
+      </c>
+      <c r="F97" s="16" t="n"/>
+      <c r="G97" s="16" t="n"/>
+      <c r="H97" s="16" t="n"/>
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="B99" s="5" t="inlineStr">
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
+      <c r="I99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — лимит</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>27545367</v>
+        <v>30000000</v>
       </c>
       <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>долг на дату отчёта</t>
-        </is>
-      </c>
+      <c r="I101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — выбрано</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>2454633</v>
+        <v>27545367</v>
       </c>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>долг на дату отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>396337.24</v>
+        <v>2454633</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
@@ -2333,36 +2337,52 @@
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="n"/>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I104" s="8" t="n"/>
     </row>
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="n">
-        <v>373487.16</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n"/>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8" t="n"/>
+      <c r="G106" s="8" t="n"/>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I106"/>
+  <dimension ref="B1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1437,54 +1437,60 @@
       <c r="I53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D54" s="23">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>204388.93</v>
+      </c>
+      <c r="D54" s="7">
         <f>C54/2</f>
         <v/>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="7">
         <f>C54/2</f>
         <v/>
       </c>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I54" s="8" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D55" s="23">
+        <f>C55/2</f>
+        <v/>
+      </c>
+      <c r="E55" s="23">
+        <f>C55/2</f>
+        <v/>
+      </c>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>39819623</v>
-      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
@@ -1495,11 +1501,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>4527900</v>
+        <v>39819623</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1511,11 +1517,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>3298432.06</v>
+        <v>4527900</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1527,11 +1533,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>2887658</v>
+        <v>3298432.06</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1543,11 +1549,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>2250790.16</v>
+        <v>2887658</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1559,11 +1565,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>827352.65</v>
+        <v>2250790.16</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1575,11 +1581,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>570005</v>
+        <v>827352.65</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1591,11 +1597,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование и расходники</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>515528</v>
+        <v>570005</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1607,11 +1613,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1623,11 +1629,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1639,11 +1645,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>582359.62</v>
+        <v>345200</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1653,12 +1659,14 @@
       <c r="I66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="n"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>582359.62</v>
+      </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
@@ -1667,14 +1675,12 @@
       <c r="I67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>4692500</v>
-      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
@@ -1685,11 +1691,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1701,11 +1707,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1717,11 +1723,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>878789.77</v>
+        <v>1155000</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1733,11 +1739,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>516000</v>
+        <v>878789.77</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1749,11 +1755,11 @@
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>435435</v>
+        <v>516000</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -1765,11 +1771,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>337440</v>
+        <v>435435</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1781,11 +1787,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>330000</v>
+        <v>337440</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1797,11 +1803,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1813,11 +1819,11 @@
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>2621284.79</v>
+        <v>320000</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
@@ -1827,163 +1833,156 @@
       <c r="I77" s="8" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи блока</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>2621284.79</v>
+      </c>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
-      <c r="C78" s="15">
-        <f>SUM(C49:C54)</f>
-        <v/>
-      </c>
-      <c r="D78" s="15">
-        <f>SUM(D49:D54)</f>
-        <v/>
-      </c>
-      <c r="E78" s="15">
-        <f>SUM(E49:E54)</f>
-        <v/>
-      </c>
-      <c r="F78" s="16" t="n"/>
-      <c r="G78" s="16" t="n"/>
-      <c r="H78" s="16" t="n"/>
-      <c r="I78" s="17" t="inlineStr">
+      <c r="C79" s="15">
+        <f>SUM(C49:C55)</f>
+        <v/>
+      </c>
+      <c r="D79" s="15">
+        <f>SUM(D49:D55)</f>
+        <v/>
+      </c>
+      <c r="E79" s="15">
+        <f>SUM(E49:E55)</f>
+        <v/>
+      </c>
+      <c r="F79" s="16" t="n"/>
+      <c r="G79" s="16" t="n"/>
+      <c r="H79" s="16" t="n"/>
+      <c r="I79" s="17" t="inlineStr">
         <is>
           <t>строки «в том числе» в сумму не входят</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="21" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D79" s="8" t="n"/>
-      <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="8" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="B81" s="3" t="inlineStr">
+    <row r="82" ht="22" customHeight="1">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="26" customHeight="1">
-      <c r="B82" s="5" t="inlineStr">
+    <row r="83" ht="26" customHeight="1">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C83" s="7">
-        <f>D83+E83</f>
-        <v/>
-      </c>
-      <c r="D83" s="7">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="E83" s="7">
-        <f>E35</f>
-        <v/>
-      </c>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
+          <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
       <c r="C84" s="7">
-        <f>F35</f>
+        <f>D84+E84</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>F35/2</f>
+        <f>D35</f>
         <v/>
       </c>
       <c r="E84" s="7">
-        <f>F35/2</f>
+        <f>E35</f>
         <v/>
       </c>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C85" s="7">
-        <f>H35</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>H35/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="E85" s="7">
-        <f>H35/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="F85" s="8" t="n"/>
@@ -1994,19 +1993,19 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C86" s="7">
-        <f>G35</f>
+        <f>H35</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>G35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="E86" s="7">
-        <f>G35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="F86" s="8" t="n"/>
@@ -2017,45 +2016,41 @@
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="n">
-        <v>396337.24</v>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C87" s="7">
+        <f>G35</f>
+        <v/>
       </c>
       <c r="D87" s="7">
-        <f>C87/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="E87" s="7">
-        <f>C87/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I87" s="8" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="18" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C88" s="19">
-        <f>-C78</f>
-        <v/>
-      </c>
-      <c r="D88" s="19">
-        <f>-D78</f>
-        <v/>
-      </c>
-      <c r="E88" s="19">
-        <f>-E78</f>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D88" s="7">
+        <f>C88/2</f>
+        <v/>
+      </c>
+      <c r="E88" s="7">
+        <f>C88/2</f>
         <v/>
       </c>
       <c r="F88" s="8" t="n"/>
@@ -2063,249 +2058,260 @@
       <c r="H88" s="8" t="n"/>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>итог блока «Расходы», пополам</t>
+          <t>начислены банком на остатки</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="18" t="inlineStr">
         <is>
-          <t>7. Личные анализы: каждый несёт свои</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="19" t="n">
-        <v>-9186</v>
-      </c>
-      <c r="E89" s="19" t="n">
-        <v>9186</v>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C89" s="19">
+        <f>-C79</f>
+        <v/>
+      </c>
+      <c r="D89" s="19">
+        <f>-D79</f>
+        <v/>
+      </c>
+      <c r="E89" s="19">
+        <f>-E79</f>
+        <v/>
       </c>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
       <c r="I89" s="10" t="inlineStr">
         <is>
+          <t>итог блока «Расходы», пополам</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>7. Личные анализы: каждый несёт свои</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="19" t="n">
+        <v>-9186</v>
+      </c>
+      <c r="E90" s="19" t="n">
+        <v>9186</v>
+      </c>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
           <t>лист «Расходы врачей»: Маланичев 30 620, Погосян 12 248</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="14" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C90" s="15">
-        <f>SUM(C83:C89)</f>
-        <v/>
-      </c>
-      <c r="D90" s="15">
-        <f>SUM(D83:D89)</f>
-        <v/>
-      </c>
-      <c r="E90" s="15">
-        <f>SUM(E83:E89)</f>
-        <v/>
-      </c>
-      <c r="F90" s="16" t="n"/>
-      <c r="G90" s="16" t="n"/>
-      <c r="H90" s="16" t="n"/>
-      <c r="I90" s="16" t="n"/>
-    </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="B92" s="3" t="inlineStr">
+      <c r="C91" s="15">
+        <f>SUM(C84:C90)</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>SUM(D84:D90)</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>SUM(E84:E90)</f>
+        <v/>
+      </c>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="B93" s="5" t="inlineStr">
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C94" s="7">
-        <f>C90</f>
-        <v/>
-      </c>
-      <c r="D94" s="7">
-        <f>D90</f>
-        <v/>
-      </c>
-      <c r="E94" s="7">
-        <f>E90</f>
-        <v/>
-      </c>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
+          <t>Доход за месяц</t>
         </is>
       </c>
       <c r="C95" s="7">
-        <f>D95+E95</f>
-        <v/>
-      </c>
-      <c r="D95" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E95" s="7" t="n">
-        <v>45275972.21</v>
+        <f>C91</f>
+        <v/>
+      </c>
+      <c r="D95" s="7">
+        <f>D91</f>
+        <v/>
+      </c>
+      <c r="E95" s="7">
+        <f>E91</f>
+        <v/>
       </c>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I95" s="8" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="18" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C96" s="19">
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C96" s="7">
         <f>D96+E96</f>
         <v/>
       </c>
-      <c r="D96" s="19" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E96" s="19" t="n">
-        <v>-5882353</v>
+      <c r="D96" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
       <c r="I96" s="10" t="inlineStr">
         <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C97" s="19">
+        <f>D97+E97</f>
+        <v/>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E97" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="14" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C97" s="15">
-        <f>SUM(C94:C96)</f>
-        <v/>
-      </c>
-      <c r="D97" s="15">
-        <f>SUM(D94:D96)</f>
-        <v/>
-      </c>
-      <c r="E97" s="15">
-        <f>SUM(E94:E96)</f>
-        <v/>
-      </c>
-      <c r="F97" s="16" t="n"/>
-      <c r="G97" s="16" t="n"/>
-      <c r="H97" s="16" t="n"/>
-      <c r="I97" s="16" t="n"/>
-    </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="B99" s="3" t="inlineStr">
+      <c r="C98" s="15">
+        <f>SUM(C95:C97)</f>
+        <v/>
+      </c>
+      <c r="D98" s="15">
+        <f>SUM(D95:D97)</f>
+        <v/>
+      </c>
+      <c r="E98" s="15">
+        <f>SUM(E95:E97)</f>
+        <v/>
+      </c>
+      <c r="F98" s="16" t="n"/>
+      <c r="G98" s="16" t="n"/>
+      <c r="H98" s="16" t="n"/>
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C99" s="4" t="n"/>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="4" t="n"/>
-      <c r="H99" s="4" t="n"/>
-      <c r="I99" s="4" t="inlineStr"/>
-    </row>
-    <row r="100" ht="26" customHeight="1">
-      <c r="B100" s="5" t="inlineStr">
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — лимит</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано</t>
+          <t>Кредитная линия — долг на начало месяца</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>27545367</v>
+        <v>16545367</v>
       </c>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
@@ -2314,34 +2320,38 @@
       <c r="H102" s="8" t="n"/>
       <c r="I102" s="10" t="inlineStr">
         <is>
-          <t>долг на дату отчёта</t>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — выбрано за месяц</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>2454633</v>
+        <v>11000000</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Кредитная линия — долг на конец месяца</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>396337.24</v>
+        <v>27545367</v>
       </c>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
@@ -2353,29 +2363,27 @@
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="n"/>
+          <t>Кредитная линия — лимит</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>30000000</v>
+      </c>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>373487.16</v>
+        <v>2454633</v>
       </c>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
@@ -2383,6 +2391,96 @@
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
       <c r="I106" s="8" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту, уплачено</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>204388.93</v>
+      </c>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="8" t="n"/>
+      <c r="G108" s="8" t="n"/>
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="8" t="n"/>
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="8" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>3284000</v>
+      </c>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -1120,13 +1120,13 @@
         <v>13054662.21</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>76495979.75</v>
+        <v>76495706.81999999</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>261238.64</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>2959191.93</v>
+        <v>2959464.86</v>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>61654454</v>
+        <v>61284454</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
@@ -1184,7 +1184,7 @@
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 19 889 514; 11–31.08: 41 764 940</t>
+          <t>01–10.08: 19 519 514; 11–31.08: 41 764 940</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C41" s="19" t="n">
-        <v>-720000</v>
+        <v>-350000</v>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>4277000</v>
+        <v>3907000</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I111"/>
+  <dimension ref="B1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2465,11 +2465,11 @@
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+          <t>Услуги банка, проведённые через счёт 60</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>3284000</v>
+        <v>1218.56</v>
       </c>
       <c r="D111" s="8" t="n"/>
       <c r="E111" s="8" t="n"/>
@@ -2477,6 +2477,26 @@
       <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="n"/>
       <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>3284000</v>
+      </c>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
+      <c r="G112" s="8" t="n"/>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="10" t="inlineStr">
         <is>
           <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
         </is>
@@ -4344,7 +4364,7 @@
       </c>
       <c r="D125" s="26" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4379,7 @@
       </c>
       <c r="D126" s="26" t="inlineStr">
         <is>
-          <t>Услуги банка</t>
+          <t>Услуги банка (через счёт 60)</t>
         </is>
       </c>
     </row>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I112"/>
+  <dimension ref="B1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1120,7 @@
         <v>13054662.21</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>76495706.81999999</v>
+        <v>76485706.81999999</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>261238.64</v>
@@ -1171,11 +1171,11 @@
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Безналичными (эквайринг)</t>
+          <t xml:space="preserve">    Безналичными (карты и онлайн-оплаты)</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>61284454</v>
+        <v>62319954</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
@@ -1184,18 +1184,18 @@
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 19 519 514; 11–31.08: 41 764 940</t>
+          <t>01–10.08: 20 555 014; из них онлайн-оплаты через сайт 1 035 500; 11–31.08: 41 764 940</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Оплаты физлиц на расчётный счёт</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>1035500</v>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Возвраты пациентам</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>-360000</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
@@ -1205,50 +1205,54 @@
       <c r="I40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Возвраты пациентам</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C42" s="12">
-        <f>SUM(C38:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="20" t="inlineStr">
+      <c r="C41" s="12">
+        <f>SUM(C38:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Справочно: оказано услуг за месяц</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>94366672</v>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Справочно: оказано услуг за месяц</t>
+          <t>Справочно: авансы под будущие операции</t>
         </is>
       </c>
       <c r="C44" s="22" t="n">
-        <v>94366672</v>
+        <v>2575181.99</v>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
@@ -1257,83 +1261,85 @@
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>Справочно: авансы под будущие операции</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="n">
-        <v>2585181.99</v>
-      </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
           <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 2,7% выручки месяца</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>6135792.28</v>
+      </c>
+      <c r="D48" s="7">
+        <f>C48/2</f>
+        <v/>
+      </c>
+      <c r="E48" s="7">
+        <f>C48/2</f>
+        <v/>
+      </c>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>6135792.28</v>
+        <v>12490831.85</v>
       </c>
       <c r="D49" s="7">
         <f>C49/2</f>
@@ -1351,11 +1357,11 @@
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Зарплата по банку</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>12490831.85</v>
+        <v>141191.07</v>
       </c>
       <c r="D50" s="7">
         <f>C50/2</f>
@@ -1373,11 +1379,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>141191.07</v>
+        <v>373487.16</v>
       </c>
       <c r="D51" s="7">
         <f>C51/2</f>
@@ -1395,11 +1401,11 @@
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Алименты (удержание из зарплаты)</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>373487.16</v>
+        <v>38726.66</v>
       </c>
       <c r="D52" s="7">
         <f>C52/2</f>
@@ -1417,11 +1423,11 @@
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Проценты по кредиту</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>38726.66</v>
+        <v>204388.93</v>
       </c>
       <c r="D53" s="7">
         <f>C53/2</f>
@@ -1437,60 +1443,54 @@
       <c r="I53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Проценты по кредиту</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>204388.93</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D54" s="23">
         <f>C54/2</f>
         <v/>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="23">
         <f>C54/2</f>
         <v/>
       </c>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C55" s="23" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D55" s="23">
-        <f>C55/2</f>
-        <v/>
-      </c>
-      <c r="E55" s="23">
-        <f>C55/2</f>
-        <v/>
-      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>39819623</v>
+      </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
@@ -1501,11 +1501,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>39819623</v>
+        <v>4527900</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1517,11 +1517,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>4527900</v>
+        <v>3298432.06</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1533,11 +1533,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>3298432.06</v>
+        <v>2887658</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1549,11 +1549,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>2887658</v>
+        <v>2250790.16</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1565,11 +1565,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>2250790.16</v>
+        <v>827352.65</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1581,11 +1581,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>827352.65</v>
+        <v>570005</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1597,11 +1597,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>570005</v>
+        <v>515528</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1613,11 +1613,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование и расходники</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>515528</v>
+        <v>376950</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1629,11 +1629,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>376950</v>
+        <v>345200</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1645,11 +1645,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>345200</v>
+        <v>582359.62</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1659,14 +1659,12 @@
       <c r="I66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>582359.62</v>
-      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
@@ -1675,12 +1673,14 @@
       <c r="I67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="n"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>4692500</v>
+      </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
@@ -1691,11 +1691,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>4692500</v>
+        <v>2505800</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1707,11 +1707,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>2505800</v>
+        <v>1155000</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1723,11 +1723,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>1155000</v>
+        <v>878789.77</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1739,11 +1739,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>878789.77</v>
+        <v>516000</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1755,11 +1755,11 @@
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>516000</v>
+        <v>435435</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -1771,11 +1771,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>435435</v>
+        <v>337440</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1787,11 +1787,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>337440</v>
+        <v>330000</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1803,11 +1803,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>330000</v>
+        <v>320000</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1819,11 +1819,11 @@
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>320000</v>
+        <v>2621284.79</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
@@ -1833,156 +1833,163 @@
       <c r="I77" s="8" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="n">
-        <v>2621284.79</v>
-      </c>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ</t>
+        </is>
+      </c>
+      <c r="C78" s="15">
+        <f>SUM(C48:C54)</f>
+        <v/>
+      </c>
+      <c r="D78" s="15">
+        <f>SUM(D48:D54)</f>
+        <v/>
+      </c>
+      <c r="E78" s="15">
+        <f>SUM(E48:E54)</f>
+        <v/>
+      </c>
+      <c r="F78" s="16" t="n"/>
+      <c r="G78" s="16" t="n"/>
+      <c r="H78" s="16" t="n"/>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ</t>
-        </is>
-      </c>
-      <c r="C79" s="15">
-        <f>SUM(C49:C55)</f>
-        <v/>
-      </c>
-      <c r="D79" s="15">
-        <f>SUM(D49:D55)</f>
-        <v/>
-      </c>
-      <c r="E79" s="15">
-        <f>SUM(E49:E55)</f>
-        <v/>
-      </c>
-      <c r="F79" s="16" t="n"/>
-      <c r="G79" s="16" t="n"/>
-      <c r="H79" s="16" t="n"/>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="21" t="inlineStr">
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C80" s="22" t="n">
+      <c r="C79" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="8" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="B82" s="3" t="inlineStr">
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="B83" s="5" t="inlineStr">
+    <row r="82" ht="26" customHeight="1">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>1. Личная выручка (свои операции)</t>
+        </is>
+      </c>
+      <c r="C83" s="7">
+        <f>D83+E83</f>
+        <v/>
+      </c>
+      <c r="D83" s="7">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E83" s="7">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>1. Личная выручка (свои операции)</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C84" s="7">
-        <f>D84+E84</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>D35</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="E84" s="7">
-        <f>E35</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
+      <c r="I84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C85" s="7">
-        <f>F35</f>
+        <f>H35</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>F35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="E85" s="7">
-        <f>F35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="F85" s="8" t="n"/>
@@ -1993,19 +2000,19 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>4. Половина прочих доходов</t>
         </is>
       </c>
       <c r="C86" s="7">
-        <f>H35</f>
+        <f>G35</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>H35/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="E86" s="7">
-        <f>H35/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="F86" s="8" t="n"/>
@@ -2016,41 +2023,45 @@
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
-        </is>
-      </c>
-      <c r="C87" s="7">
-        <f>G35</f>
-        <v/>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>396337.24</v>
       </c>
       <c r="D87" s="7">
-        <f>G35/2</f>
+        <f>C87/2</f>
         <v/>
       </c>
       <c r="E87" s="7">
-        <f>G35/2</f>
+        <f>C87/2</f>
         <v/>
       </c>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="n">
-        <v>396337.24</v>
-      </c>
-      <c r="D88" s="7">
-        <f>C88/2</f>
-        <v/>
-      </c>
-      <c r="E88" s="7">
-        <f>C88/2</f>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C88" s="19">
+        <f>-C78</f>
+        <v/>
+      </c>
+      <c r="D88" s="19">
+        <f>-D78-9186.00</f>
+        <v/>
+      </c>
+      <c r="E88" s="19">
+        <f>-E78+9186.00</f>
         <v/>
       </c>
       <c r="F88" s="8" t="n"/>
@@ -2058,300 +2069,281 @@
       <c r="H88" s="8" t="n"/>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>начислены банком на остатки</t>
+          <t>итог блока «Расходы» пополам, плюс личные анализы каждого (Маланичев 30 620, Погосян 12 248 — переносится половина разницы)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="18" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C89" s="19">
-        <f>-C79</f>
-        <v/>
-      </c>
-      <c r="D89" s="19">
-        <f>-D79</f>
-        <v/>
-      </c>
-      <c r="E89" s="19">
-        <f>-E79</f>
-        <v/>
-      </c>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>итог блока «Расходы», пополам</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="18" t="inlineStr">
-        <is>
-          <t>7. Личные анализы: каждый несёт свои</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="19" t="n">
-        <v>-9186</v>
-      </c>
-      <c r="E90" s="19" t="n">
-        <v>9186</v>
-      </c>
-      <c r="F90" s="8" t="n"/>
-      <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>лист «Расходы врачей»: Маланичев 30 620, Погосян 12 248</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C91" s="15">
-        <f>SUM(C84:C90)</f>
-        <v/>
-      </c>
-      <c r="D91" s="15">
-        <f>SUM(D84:D90)</f>
-        <v/>
-      </c>
-      <c r="E91" s="15">
-        <f>SUM(E84:E90)</f>
-        <v/>
-      </c>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="16" t="n"/>
-      <c r="H91" s="16" t="n"/>
-      <c r="I91" s="16" t="n"/>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="B93" s="3" t="inlineStr">
+      <c r="C89" s="15">
+        <f>SUM(C83:C88)</f>
+        <v/>
+      </c>
+      <c r="D89" s="15">
+        <f>SUM(D83:D88)</f>
+        <v/>
+      </c>
+      <c r="E89" s="15">
+        <f>SUM(E83:E88)</f>
+        <v/>
+      </c>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="16" t="n"/>
+      <c r="H89" s="16" t="n"/>
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="B94" s="5" t="inlineStr">
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Доход за месяц</t>
+        </is>
+      </c>
+      <c r="C93" s="7">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="D93" s="7">
+        <f>D89</f>
+        <v/>
+      </c>
+      <c r="E93" s="7">
+        <f>E89</f>
+        <v/>
+      </c>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C94" s="7">
+        <f>D94+E94</f>
+        <v/>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
     <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C95" s="7">
-        <f>C91</f>
-        <v/>
-      </c>
-      <c r="D95" s="7">
-        <f>D91</f>
-        <v/>
-      </c>
-      <c r="E95" s="7">
-        <f>E91</f>
-        <v/>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C95" s="19">
+        <f>D95+E95</f>
+        <v/>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>-5882353</v>
       </c>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
-      <c r="I95" s="8" t="n"/>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>начислено с НДФЛ</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C96" s="7">
-        <f>D96+E96</f>
-        <v/>
-      </c>
-      <c r="D96" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="18" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C97" s="19">
-        <f>D97+E97</f>
-        <v/>
-      </c>
-      <c r="D97" s="19" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E97" s="19" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>начислено с НДФЛ</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="14" t="inlineStr">
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C98" s="15">
-        <f>SUM(C95:C97)</f>
-        <v/>
-      </c>
-      <c r="D98" s="15">
-        <f>SUM(D95:D97)</f>
-        <v/>
-      </c>
-      <c r="E98" s="15">
-        <f>SUM(E95:E97)</f>
-        <v/>
-      </c>
-      <c r="F98" s="16" t="n"/>
-      <c r="G98" s="16" t="n"/>
-      <c r="H98" s="16" t="n"/>
-      <c r="I98" s="16" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="B100" s="3" t="inlineStr">
+      <c r="C96" s="15">
+        <f>SUM(C93:C95)</f>
+        <v/>
+      </c>
+      <c r="D96" s="15">
+        <f>SUM(D93:D95)</f>
+        <v/>
+      </c>
+      <c r="E96" s="15">
+        <f>SUM(E93:E95)</f>
+        <v/>
+      </c>
+      <c r="F96" s="16" t="n"/>
+      <c r="G96" s="16" t="n"/>
+      <c r="H96" s="16" t="n"/>
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="inlineStr"/>
-    </row>
-    <row r="101" ht="26" customHeight="1">
-      <c r="B101" s="5" t="inlineStr">
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99" ht="26" customHeight="1">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — долг на начало месяца</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>16545367</v>
+      </c>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — выбрано за месяц</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на начало месяца</t>
+          <t>Кредитная линия — долг на конец месяца</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>16545367</v>
+        <v>27545367</v>
       </c>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
-        </is>
-      </c>
+      <c r="I102" s="8" t="n"/>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано за месяц</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>11000000</v>
+        <v>30000000</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
-        </is>
-      </c>
+      <c r="I103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на конец месяца</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>27545367</v>
+        <v>2454633</v>
       </c>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
@@ -2363,27 +2355,31 @@
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t>Проценты по кредиту, уплачено</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>30000000</v>
+        <v>204388.93</v>
       </c>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Проценты по депозитам за месяц</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>2454633</v>
+        <v>396337.24</v>
       </c>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
@@ -2395,12 +2391,10 @@
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Проценты по кредиту, уплачено</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="n">
-        <v>204388.93</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n"/>
       <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
@@ -2408,18 +2402,18 @@
       <c r="H107" s="8" t="n"/>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+          <t>не проставлен</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Комиссия эквайринга</t>
         </is>
       </c>
       <c r="C108" s="7" t="n">
-        <v>396337.24</v>
+        <v>373487.16</v>
       </c>
       <c r="D108" s="8" t="n"/>
       <c r="E108" s="8" t="n"/>
@@ -2431,10 +2425,12 @@
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n"/>
+          <t>Услуги банка, проведённые через счёт 60</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>1218.56</v>
+      </c>
       <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
@@ -2442,61 +2438,25 @@
       <c r="H109" s="8" t="n"/>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>не проставлен</t>
+          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
         </is>
       </c>
       <c r="C110" s="7" t="n">
-        <v>373487.16</v>
+        <v>3284000</v>
       </c>
       <c r="D110" s="8" t="n"/>
       <c r="E110" s="8" t="n"/>
       <c r="F110" s="8" t="n"/>
       <c r="G110" s="8" t="n"/>
       <c r="H110" s="8" t="n"/>
-      <c r="I110" s="8" t="n"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Услуги банка, проведённые через счёт 60</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>1218.56</v>
-      </c>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="8" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="10" t="inlineStr">
-        <is>
-          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="n">
-        <v>3284000</v>
-      </c>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="8" t="n"/>
-      <c r="G112" s="8" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="10" t="inlineStr">
+      <c r="I110" s="10" t="inlineStr">
         <is>
           <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
         </is>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -71,15 +71,15 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00A3423B"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <color rgb="008A7350"/>
       <sz val="11"/>
     </font>
     <font>
       <color rgb="00807A70"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00A3423B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,21 +161,24 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -545,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I110"/>
+  <dimension ref="B1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1175,7 +1178,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>62319954</v>
+        <v>61959954</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
@@ -1184,55 +1187,59 @@
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 20 555 014; из них онлайн-оплаты через сайт 1 035 500; 11–31.08: 41 764 940</t>
+          <t>01–10.08: 20 555 014, из них онлайн-оплаты через сайт 1 035 500; 11–31.08: 41 764 940; за вычетом возвратов пациентам 360 000</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Возвраты пациентам</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="n">
-        <v>-360000</v>
-      </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C41" s="12">
-        <f>SUM(C38:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="20" t="inlineStr">
+      <c r="C40" s="12">
+        <f>SUM(C38:C39)</f>
+        <v/>
+      </c>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: оказано услуг за месяц</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>94366672</v>
+      </c>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>Справочно: оказано услуг за месяц</t>
-        </is>
-      </c>
-      <c r="C43" s="22" t="n">
-        <v>94366672</v>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: авансы под будущие операции</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>2575181.99</v>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
@@ -1241,83 +1248,85 @@
       <c r="H43" s="8" t="n"/>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="21" t="inlineStr">
-        <is>
-          <t>Справочно: авансы под будущие операции</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="n">
-        <v>2575181.99</v>
-      </c>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
           <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 2,7% выручки месяца</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="3" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="B47" s="5" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>6135792.28</v>
+      </c>
+      <c r="D47" s="7">
+        <f>C47/2</f>
+        <v/>
+      </c>
+      <c r="E47" s="7">
+        <f>C47/2</f>
+        <v/>
+      </c>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>6135792.28</v>
+        <v>12490831.85</v>
       </c>
       <c r="D48" s="7">
         <f>C48/2</f>
@@ -1335,11 +1344,11 @@
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Зарплата по банку</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>12490831.85</v>
+        <v>141191.07</v>
       </c>
       <c r="D49" s="7">
         <f>C49/2</f>
@@ -1357,11 +1366,11 @@
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Услуги банка (эквайринг)</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>141191.07</v>
+        <v>373487.16</v>
       </c>
       <c r="D50" s="7">
         <f>C50/2</f>
@@ -1379,11 +1388,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Алименты (удержание из зарплаты)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>373487.16</v>
+        <v>38726.66</v>
       </c>
       <c r="D51" s="7">
         <f>C51/2</f>
@@ -1401,11 +1410,11 @@
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Проценты по кредиту</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>38726.66</v>
+        <v>204388.93</v>
       </c>
       <c r="D52" s="7">
         <f>C52/2</f>
@@ -1421,60 +1430,54 @@
       <c r="I52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Проценты по кредиту</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>204388.93</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>69794048.05</v>
+      </c>
+      <c r="D53" s="21">
         <f>C53/2</f>
         <v/>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="21">
         <f>C53/2</f>
         <v/>
       </c>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>69794048.05</v>
-      </c>
-      <c r="D54" s="23">
-        <f>C54/2</f>
-        <v/>
-      </c>
-      <c r="E54" s="23">
-        <f>C54/2</f>
-        <v/>
-      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I54" s="8" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>39819623</v>
+      </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
@@ -1485,11 +1488,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>39819623</v>
+        <v>4527900</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1501,11 +1504,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>4527900</v>
+        <v>3298432.06</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1517,11 +1520,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>3298432.06</v>
+        <v>2887658</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1533,11 +1536,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>2887658</v>
+        <v>2250790.16</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1549,11 +1552,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>2250790.16</v>
+        <v>827352.65</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1565,11 +1568,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>827352.65</v>
+        <v>570005</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1581,11 +1584,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>570005</v>
+        <v>515528</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1597,11 +1600,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование и расходники</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>515528</v>
+        <v>376950</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1613,11 +1616,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>376950</v>
+        <v>345200</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1629,11 +1632,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>345200</v>
+        <v>582359.62</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1643,14 +1646,12 @@
       <c r="I65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>582359.62</v>
-      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
@@ -1659,12 +1660,14 @@
       <c r="I66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="n"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>4692500</v>
+      </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
@@ -1675,11 +1678,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>4692500</v>
+        <v>2505800</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1691,11 +1694,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>2505800</v>
+        <v>1155000</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1707,11 +1710,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Прочие управленческие</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>1155000</v>
+        <v>878789.77</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1723,11 +1726,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>878789.77</v>
+        <v>516000</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1739,11 +1742,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>516000</v>
+        <v>435435</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1755,11 +1758,11 @@
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>435435</v>
+        <v>337440</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -1771,11 +1774,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>337440</v>
+        <v>330000</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1787,11 +1790,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>330000</v>
+        <v>320000</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1803,11 +1806,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            прочие статьи блока</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>320000</v>
+        <v>2621284.79</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1817,56 +1820,60 @@
       <c r="I76" s="8" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="n">
-        <v>2621284.79</v>
-      </c>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="8" t="n"/>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ</t>
+        </is>
+      </c>
+      <c r="C77" s="15">
+        <f>SUM(C47:C53)</f>
+        <v/>
+      </c>
+      <c r="D77" s="15">
+        <f>SUM(D47:D53)</f>
+        <v/>
+      </c>
+      <c r="E77" s="15">
+        <f>SUM(E47:E53)</f>
+        <v/>
+      </c>
+      <c r="F77" s="16" t="n"/>
+      <c r="G77" s="16" t="n"/>
+      <c r="H77" s="16" t="n"/>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ</t>
-        </is>
-      </c>
-      <c r="C78" s="15">
-        <f>SUM(C48:C54)</f>
-        <v/>
-      </c>
-      <c r="D78" s="15">
-        <f>SUM(D48:D54)</f>
-        <v/>
-      </c>
-      <c r="E78" s="15">
-        <f>SUM(E48:E54)</f>
-        <v/>
-      </c>
-      <c r="F78" s="16" t="n"/>
-      <c r="G78" s="16" t="n"/>
-      <c r="H78" s="16" t="n"/>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: ремонт за счёт кредитной линии</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="21" t="inlineStr">
-        <is>
-          <t>Справочно: ремонт за счёт кредитной линии</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="n">
-        <v>11000000</v>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: из них личные расходы врачей</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="n">
+        <v>42868</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
@@ -1875,7 +1882,7 @@
       <c r="H79" s="8" t="n"/>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
+          <t>пополам не делятся, отнесены каждому свои — см. шаг 7</t>
         </is>
       </c>
     </row>
@@ -2047,21 +2054,21 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="18" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C88" s="19">
-        <f>-C78</f>
-        <v/>
-      </c>
-      <c r="D88" s="19">
-        <f>-D78-9186.00</f>
-        <v/>
-      </c>
-      <c r="E88" s="19">
-        <f>-E78+9186.00</f>
+      <c r="B88" s="23" t="inlineStr">
+        <is>
+          <t>6. Минус ½ общих расходов</t>
+        </is>
+      </c>
+      <c r="C88" s="24">
+        <f>-(C77-42868.0)</f>
+        <v/>
+      </c>
+      <c r="D88" s="24">
+        <f>-(D77-21434.0)</f>
+        <v/>
+      </c>
+      <c r="E88" s="24">
+        <f>-(E77-21434.0)</f>
         <v/>
       </c>
       <c r="F88" s="8" t="n"/>
@@ -2069,281 +2076,293 @@
       <c r="H88" s="8" t="n"/>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>итог блока «Расходы» пополам, плюс личные анализы каждого (Маланичев 30 620, Погосян 12 248 — переносится половина разницы)</t>
+          <t>итог блока «Расходы» без личных, пополам</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>7. Минус личные расходы (каждый свои)</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="n">
+        <v>-42868</v>
+      </c>
+      <c r="D89" s="24" t="n">
+        <v>-30620</v>
+      </c>
+      <c r="E89" s="24" t="n">
+        <v>-12248</v>
+      </c>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>заказано лично под врача, пополам не делится</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Анализы</t>
+        </is>
+      </c>
+      <c r="C90" s="25" t="n">
+        <v>-42868</v>
+      </c>
+      <c r="D90" s="25" t="n">
+        <v>-30620</v>
+      </c>
+      <c r="E90" s="25" t="n">
+        <v>-12248</v>
+      </c>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C89" s="15">
-        <f>SUM(C83:C88)</f>
-        <v/>
-      </c>
-      <c r="D89" s="15">
-        <f>SUM(D83:D88)</f>
-        <v/>
-      </c>
-      <c r="E89" s="15">
-        <f>SUM(E83:E88)</f>
-        <v/>
-      </c>
-      <c r="F89" s="16" t="n"/>
-      <c r="G89" s="16" t="n"/>
-      <c r="H89" s="16" t="n"/>
-      <c r="I89" s="16" t="n"/>
-    </row>
-    <row r="91" ht="22" customHeight="1">
-      <c r="B91" s="3" t="inlineStr">
+      <c r="C91" s="15">
+        <f>SUM(C83:C89)</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>SUM(D83:D89)</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>SUM(E83:E89)</f>
+        <v/>
+      </c>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="B92" s="5" t="inlineStr">
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="6" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Доход за месяц</t>
         </is>
       </c>
-      <c r="C93" s="7">
-        <f>C89</f>
-        <v/>
-      </c>
-      <c r="D93" s="7">
-        <f>D89</f>
-        <v/>
-      </c>
-      <c r="E93" s="7">
-        <f>E89</f>
-        <v/>
-      </c>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C94" s="7">
-        <f>D94+E94</f>
-        <v/>
-      </c>
-      <c r="D94" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E94" s="7" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="18" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C95" s="19">
-        <f>D95+E95</f>
-        <v/>
-      </c>
-      <c r="D95" s="19" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E95" s="19" t="n">
-        <v>-5882353</v>
+      <c r="C95" s="7">
+        <f>C91</f>
+        <v/>
+      </c>
+      <c r="D95" s="7">
+        <f>D91</f>
+        <v/>
+      </c>
+      <c r="E95" s="7">
+        <f>E91</f>
+        <v/>
       </c>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
-      <c r="I95" s="10" t="inlineStr">
+      <c r="I95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C96" s="7">
+        <f>D96+E96</f>
+        <v/>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="23" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C97" s="24">
+        <f>D97+E97</f>
+        <v/>
+      </c>
+      <c r="D97" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E97" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="14" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C96" s="15">
-        <f>SUM(C93:C95)</f>
-        <v/>
-      </c>
-      <c r="D96" s="15">
-        <f>SUM(D93:D95)</f>
-        <v/>
-      </c>
-      <c r="E96" s="15">
-        <f>SUM(E93:E95)</f>
-        <v/>
-      </c>
-      <c r="F96" s="16" t="n"/>
-      <c r="G96" s="16" t="n"/>
-      <c r="H96" s="16" t="n"/>
-      <c r="I96" s="16" t="n"/>
-    </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="B98" s="3" t="inlineStr">
+      <c r="C98" s="15">
+        <f>SUM(C95:C97)</f>
+        <v/>
+      </c>
+      <c r="D98" s="15">
+        <f>SUM(D95:D97)</f>
+        <v/>
+      </c>
+      <c r="E98" s="15">
+        <f>SUM(E95:E97)</f>
+        <v/>
+      </c>
+      <c r="F98" s="16" t="n"/>
+      <c r="G98" s="16" t="n"/>
+      <c r="H98" s="16" t="n"/>
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="B99" s="5" t="inlineStr">
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — долг на начало месяца</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>16545367</v>
-      </c>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — выбрано за месяц</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на конец месяца</t>
+          <t>Кредитная линия — долг на начало месяца</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>27545367</v>
+        <v>16545367</v>
       </c>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t>Кредитная линия — выбрано за месяц</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>30000000</v>
+        <v>11000000</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — долг на конец месяца</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>2454633</v>
+        <v>27545367</v>
       </c>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
@@ -2355,31 +2374,27 @@
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Проценты по кредиту, уплачено</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>204388.93</v>
+        <v>30000000</v>
       </c>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
-        </is>
-      </c>
+      <c r="I105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>396337.24</v>
+        <v>2454633</v>
       </c>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
@@ -2391,10 +2406,12 @@
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="n"/>
+          <t>Проценты по кредиту, уплачено</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>204388.93</v>
+      </c>
       <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
@@ -2402,18 +2419,18 @@
       <c r="H107" s="8" t="n"/>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>не проставлен</t>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
+          <t>Проценты по депозитам за месяц</t>
         </is>
       </c>
       <c r="C108" s="7" t="n">
-        <v>373487.16</v>
+        <v>396337.24</v>
       </c>
       <c r="D108" s="8" t="n"/>
       <c r="E108" s="8" t="n"/>
@@ -2425,12 +2442,10 @@
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка, проведённые через счёт 60</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n">
-        <v>1218.56</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n"/>
       <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
@@ -2438,25 +2453,61 @@
       <c r="H109" s="8" t="n"/>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
+          <t>не проставлен</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+          <t>Комиссия эквайринга</t>
         </is>
       </c>
       <c r="C110" s="7" t="n">
-        <v>3284000</v>
+        <v>373487.16</v>
       </c>
       <c r="D110" s="8" t="n"/>
       <c r="E110" s="8" t="n"/>
       <c r="F110" s="8" t="n"/>
       <c r="G110" s="8" t="n"/>
       <c r="H110" s="8" t="n"/>
-      <c r="I110" s="10" t="inlineStr">
+      <c r="I110" s="8" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Услуги банка, проведённые через счёт 60</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>1218.56</v>
+      </c>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>3284000</v>
+      </c>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
+      <c r="G112" s="8" t="n"/>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="10" t="inlineStr">
         <is>
           <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
         </is>
@@ -2519,10 +2570,10 @@
           <t>КВАЛИТЕТ ООО</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <v>11000000</v>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Ремонт Самокатная 1 стр12</t>
         </is>
@@ -2534,10 +2585,10 @@
           <t>Маркарян Максим Рачьянович ИП</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>10966274</v>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2549,10 +2600,10 @@
           <t>БУРДИНА Е.С. ИП</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>5382764</v>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2564,10 +2615,10 @@
           <t>Сехина Виктория Дмитриевна</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <v>4692500</v>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Урегулирование досудебного спора</t>
         </is>
@@ -2579,10 +2630,10 @@
           <t>Ужахов Тимур Магомедович ИП</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <v>4518074</v>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2594,10 +2645,10 @@
           <t>КЛОВЕРМЕД ООО</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <v>4196900</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -2609,10 +2660,10 @@
           <t>Завиркин Антон Владимирович ИП</t>
         </is>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>2887658</v>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>ИП Завиркин А.В.</t>
         </is>
@@ -2624,10 +2675,10 @@
           <t>Маржохов Астемир Ануарович ИП</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="26" t="n">
         <v>2811745</v>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2639,10 +2690,10 @@
           <t>Габеев Алан Ирбекович ИП</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <v>2631347</v>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2654,10 +2705,10 @@
           <t>Ласукова Екатерина Борисовна</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <v>2505800</v>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Маркетинговые услуги</t>
         </is>
@@ -2669,10 +2720,10 @@
           <t>Пономарёва Елена Юрьевна ИП</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="26" t="n">
         <v>2272677</v>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2684,10 +2735,10 @@
           <t>БУРДИН С. А. ИП</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="26" t="n">
         <v>2227217</v>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2699,10 +2750,10 @@
           <t>Ханукаев Александр Ильич</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="26" t="n">
         <v>2210015</v>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2714,10 +2765,10 @@
           <t>СистеМед ООО</t>
         </is>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="26" t="n">
         <v>1857678.61</v>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -2729,10 +2780,10 @@
           <t>ПОКАЛЕНЬЕВ Н. С. ИП</t>
         </is>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="26" t="n">
         <v>1740957</v>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2744,10 +2795,10 @@
           <t>СЛЕСАРЕВ ПАВЕЛ ИГОРЕВИЧ ИП</t>
         </is>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="26" t="n">
         <v>1337422</v>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2759,10 +2810,10 @@
           <t>ДельтаМед ООО</t>
         </is>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="26" t="n">
         <v>1157543.1</v>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -2774,10 +2825,10 @@
           <t>Никифоров Сергей Арнольдович</t>
         </is>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="26" t="n">
         <v>1155000</v>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Аренда Самокатная 1 стр1</t>
         </is>
@@ -2789,10 +2840,10 @@
           <t>Врачев Владислав Юрьевич ИП</t>
         </is>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="26" t="n">
         <v>927938</v>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2804,10 +2855,10 @@
           <t>Береснев Алексей Игоревич ИП</t>
         </is>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="26" t="n">
         <v>792876</v>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2819,10 +2870,10 @@
           <t>Макеенко Николай Владимирович ИП</t>
         </is>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="26" t="n">
         <v>703266</v>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2834,10 +2885,10 @@
           <t>ИП КАЧАЯН В.А. ИП</t>
         </is>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="26" t="n">
         <v>656611</v>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -2849,10 +2900,10 @@
           <t>Чугуевская Ирина Сергеевна ИП</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="26" t="n">
         <v>570005</v>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
@@ -2864,10 +2915,10 @@
           <t>СИРИУС ММ ООО</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="26" t="n">
         <v>550653.36</v>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -2879,10 +2930,10 @@
           <t>Громова Наталья Юрьевна ИП</t>
         </is>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="26" t="n">
         <v>516000</v>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Ремонт</t>
         </is>
@@ -2894,10 +2945,10 @@
           <t>КИТ МЕД ООО</t>
         </is>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="26" t="n">
         <v>515528</v>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Медоборудование и расходники</t>
         </is>
@@ -2909,10 +2960,10 @@
           <t>ЦВ ПРОТЕК АО</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <v>477406.58</v>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -2924,10 +2975,10 @@
           <t>ИТ-ЭКСПЕРТ ООО</t>
         </is>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="26" t="n">
         <v>435435</v>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Обслуживание 1СУправление</t>
         </is>
@@ -2939,10 +2990,10 @@
           <t>АЛЬДЖЕНСА ООО</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="26" t="n">
         <v>376950</v>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Питание</t>
         </is>
@@ -2954,10 +3005,10 @@
           <t>ВИТТА КОМПАНИ ООО</t>
         </is>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="26" t="n">
         <v>349946.07</v>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>Лекарства</t>
         </is>
@@ -2969,10 +3020,10 @@
           <t>РЕНЕССАНС ЭСТЕТИКА ООО</t>
         </is>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="26" t="n">
         <v>331000</v>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>Импланты</t>
         </is>
@@ -2984,10 +3035,10 @@
           <t>Электростальский филиал МОКА</t>
         </is>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="26" t="n">
         <v>330000</v>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Услуги юриста</t>
         </is>
@@ -2999,10 +3050,10 @@
           <t>Самозанятый Завиркина Лилия Викторовна</t>
         </is>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="26" t="n">
         <v>320000</v>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Складской учет</t>
         </is>
@@ -3014,10 +3065,10 @@
           <t>Стародубов Дмитрий Александрович ИП</t>
         </is>
       </c>
-      <c r="C38" s="25" t="n">
+      <c r="C38" s="26" t="n">
         <v>293400</v>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3029,10 +3080,10 @@
           <t>ПФ СКБ Контур АО</t>
         </is>
       </c>
-      <c r="C39" s="25" t="n">
+      <c r="C39" s="26" t="n">
         <v>279349.86</v>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>ПО и IT-сервисы</t>
         </is>
@@ -3044,10 +3095,10 @@
           <t>Выскуб Ольга Анатольевна ИП</t>
         </is>
       </c>
-      <c r="C40" s="25" t="n">
+      <c r="C40" s="26" t="n">
         <v>275300</v>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -3059,10 +3110,10 @@
           <t>РОКЕТ СЕРВИС ООО</t>
         </is>
       </c>
-      <c r="C41" s="25" t="n">
+      <c r="C41" s="26" t="n">
         <v>264850</v>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>Битрикс 24</t>
         </is>
@@ -3074,10 +3125,10 @@
           <t>ГЕРАСИМОВА А.В. ИП</t>
         </is>
       </c>
-      <c r="C42" s="25" t="n">
+      <c r="C42" s="26" t="n">
         <v>260766</v>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -3089,10 +3140,10 @@
           <t>Хафизов Станислав Ильшатович ИП</t>
         </is>
       </c>
-      <c r="C43" s="25" t="n">
+      <c r="C43" s="26" t="n">
         <v>254000</v>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D43" s="27" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -3104,10 +3155,10 @@
           <t>КРЕЙТ ООО</t>
         </is>
       </c>
-      <c r="C44" s="25" t="n">
+      <c r="C44" s="26" t="n">
         <v>246913.68</v>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3119,10 +3170,10 @@
           <t>МЕДПРО ООО</t>
         </is>
       </c>
-      <c r="C45" s="25" t="n">
+      <c r="C45" s="26" t="n">
         <v>235200</v>
       </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="D45" s="27" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -3134,10 +3185,10 @@
           <t>ЛЕ МОНЛИД ООО</t>
         </is>
       </c>
-      <c r="C46" s="25" t="n">
+      <c r="C46" s="26" t="n">
         <v>222551.24</v>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3149,10 +3200,10 @@
           <t>Рыболова Анастасия Алексеевна ИП</t>
         </is>
       </c>
-      <c r="C47" s="25" t="n">
+      <c r="C47" s="26" t="n">
         <v>220000</v>
       </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D47" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -3164,10 +3215,10 @@
           <t>Богачко Елизавета Максимовна ИП</t>
         </is>
       </c>
-      <c r="C48" s="25" t="n">
+      <c r="C48" s="26" t="n">
         <v>210000</v>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
         <is>
           <t>Аренда Inmode</t>
         </is>
@@ -3179,10 +3230,10 @@
           <t>МЕДИНТОРГ АО</t>
         </is>
       </c>
-      <c r="C49" s="25" t="n">
+      <c r="C49" s="26" t="n">
         <v>206303.7</v>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -3194,10 +3245,10 @@
           <t>ФГБУЗ Центр крови ФМБА России УФК по г.Москве (ФГБУЗ Центр крови ФМБА России) л/с 20736У64550</t>
         </is>
       </c>
-      <c r="C50" s="25" t="n">
+      <c r="C50" s="26" t="n">
         <v>181735.9</v>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>Кровь</t>
         </is>
@@ -3209,10 +3260,10 @@
           <t>ПЗСПП ООО</t>
         </is>
       </c>
-      <c r="C51" s="25" t="n">
+      <c r="C51" s="26" t="n">
         <v>179400</v>
       </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="D51" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3224,10 +3275,10 @@
           <t>БЕЛВА ООО ПТК</t>
         </is>
       </c>
-      <c r="C52" s="25" t="n">
+      <c r="C52" s="26" t="n">
         <v>173834.16</v>
       </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3239,10 +3290,10 @@
           <t>Самозанятый Маланичев Юрий Васильевич</t>
         </is>
       </c>
-      <c r="C53" s="25" t="n">
+      <c r="C53" s="26" t="n">
         <v>159575</v>
       </c>
-      <c r="D53" s="26" t="inlineStr">
+      <c r="D53" s="27" t="inlineStr">
         <is>
           <t>Услуги инженера</t>
         </is>
@@ -3254,10 +3305,10 @@
           <t>КОМУС ООО</t>
         </is>
       </c>
-      <c r="C54" s="25" t="n">
+      <c r="C54" s="26" t="n">
         <v>157671.72</v>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D54" s="27" t="inlineStr">
         <is>
           <t>Канц и хоз расходы</t>
         </is>
@@ -3269,10 +3320,10 @@
           <t>ИМОТИО ООО</t>
         </is>
       </c>
-      <c r="C55" s="25" t="n">
+      <c r="C55" s="26" t="n">
         <v>152250</v>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D55" s="27" t="inlineStr">
         <is>
           <t>Сервис речевой аналитики</t>
         </is>
@@ -3284,10 +3335,10 @@
           <t>Кудря Дарья Сергеевна ИП</t>
         </is>
       </c>
-      <c r="C56" s="25" t="n">
+      <c r="C56" s="26" t="n">
         <v>149600</v>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -3299,10 +3350,10 @@
           <t>АЛКАНА А ООО</t>
         </is>
       </c>
-      <c r="C57" s="25" t="n">
+      <c r="C57" s="26" t="n">
         <v>146600</v>
       </c>
-      <c r="D57" s="26" t="inlineStr">
+      <c r="D57" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3314,10 +3365,10 @@
           <t>ИТМЕДИКАЛ ООО</t>
         </is>
       </c>
-      <c r="C58" s="25" t="n">
+      <c r="C58" s="26" t="n">
         <v>136000</v>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="D58" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3329,10 +3380,10 @@
           <t>ТД ТИНКО ООО</t>
         </is>
       </c>
-      <c r="C59" s="25" t="n">
+      <c r="C59" s="26" t="n">
         <v>118740.75</v>
       </c>
-      <c r="D59" s="26" t="inlineStr">
+      <c r="D59" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3344,10 +3395,10 @@
           <t>Елизаров Андрей Владимирович ИП</t>
         </is>
       </c>
-      <c r="C60" s="25" t="n">
+      <c r="C60" s="26" t="n">
         <v>118735.06</v>
       </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="D60" s="27" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -3359,10 +3410,10 @@
           <t>А410 ООО</t>
         </is>
       </c>
-      <c r="C61" s="25" t="n">
+      <c r="C61" s="26" t="n">
         <v>114858</v>
       </c>
-      <c r="D61" s="26" t="inlineStr">
+      <c r="D61" s="27" t="inlineStr">
         <is>
           <t>Косметология</t>
         </is>
@@ -3374,10 +3425,10 @@
           <t>Ершов Эдуард Владимирович ИП</t>
         </is>
       </c>
-      <c r="C62" s="25" t="n">
+      <c r="C62" s="26" t="n">
         <v>111300</v>
       </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="D62" s="27" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -3389,10 +3440,10 @@
           <t>МИА ООО</t>
         </is>
       </c>
-      <c r="C63" s="25" t="n">
+      <c r="C63" s="26" t="n">
         <v>110000</v>
       </c>
-      <c r="D63" s="26" t="inlineStr">
+      <c r="D63" s="27" t="inlineStr">
         <is>
           <t>Белье</t>
         </is>
@@ -3404,10 +3455,10 @@
           <t>Дубровина Юлия Игоревна ИП</t>
         </is>
       </c>
-      <c r="C64" s="25" t="n">
+      <c r="C64" s="26" t="n">
         <v>104374</v>
       </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="D64" s="27" t="inlineStr">
         <is>
           <t>Гонорары ИП хирургов</t>
         </is>
@@ -3419,10 +3470,10 @@
           <t>КДЛ ДОМОДЕДОВО-ТЕСТ ООО</t>
         </is>
       </c>
-      <c r="C65" s="25" t="n">
+      <c r="C65" s="26" t="n">
         <v>102102</v>
       </c>
-      <c r="D65" s="26" t="inlineStr">
+      <c r="D65" s="27" t="inlineStr">
         <is>
           <t>Анализы</t>
         </is>
@@ -3434,10 +3485,10 @@
           <t>Звоник Юрий Алексеевич</t>
         </is>
       </c>
-      <c r="C66" s="25" t="n">
+      <c r="C66" s="26" t="n">
         <v>100000</v>
       </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="D66" s="27" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
@@ -3449,10 +3500,10 @@
           <t>ЯНДЕКС.ТАКСИ ООО</t>
         </is>
       </c>
-      <c r="C67" s="25" t="n">
+      <c r="C67" s="26" t="n">
         <v>100000</v>
       </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="D67" s="27" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
@@ -3464,10 +3515,10 @@
           <t>ТЕХПРОФИТ ООО</t>
         </is>
       </c>
-      <c r="C68" s="25" t="n">
+      <c r="C68" s="26" t="n">
         <v>99200</v>
       </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="D68" s="27" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -3479,10 +3530,10 @@
           <t>Самозанятый Дроздецкий Дмитрий Александрович</t>
         </is>
       </c>
-      <c r="C69" s="25" t="n">
+      <c r="C69" s="26" t="n">
         <v>90100</v>
       </c>
-      <c r="D69" s="26" t="inlineStr">
+      <c r="D69" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3494,10 +3545,10 @@
           <t>ДельтаМедКомпани ООО</t>
         </is>
       </c>
-      <c r="C70" s="25" t="n">
+      <c r="C70" s="26" t="n">
         <v>87600</v>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="D70" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -3509,10 +3560,10 @@
           <t>ИННОВАЦИОННЫЕ ТЕХНОЛОГИИ ООО</t>
         </is>
       </c>
-      <c r="C71" s="25" t="n">
+      <c r="C71" s="26" t="n">
         <v>85000</v>
       </c>
-      <c r="D71" s="26" t="inlineStr">
+      <c r="D71" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3524,10 +3575,10 @@
           <t>ЦЕНТР-ОТЕЛЬ ООО</t>
         </is>
       </c>
-      <c r="C72" s="25" t="n">
+      <c r="C72" s="26" t="n">
         <v>81075</v>
       </c>
-      <c r="D72" s="26" t="inlineStr">
+      <c r="D72" s="27" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
@@ -3539,10 +3590,10 @@
           <t>М-ИНВЕСТ ООО</t>
         </is>
       </c>
-      <c r="C73" s="25" t="n">
+      <c r="C73" s="26" t="n">
         <v>77412</v>
       </c>
-      <c r="D73" s="26" t="inlineStr">
+      <c r="D73" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3554,10 +3605,10 @@
           <t>ИНТЕРНЕТ РЕШЕНИЯ ООО</t>
         </is>
       </c>
-      <c r="C74" s="25" t="n">
+      <c r="C74" s="26" t="n">
         <v>77247</v>
       </c>
-      <c r="D74" s="26" t="inlineStr">
+      <c r="D74" s="27" t="inlineStr">
         <is>
           <t>Хоз расходы</t>
         </is>
@@ -3569,10 +3620,10 @@
           <t>ДЕЗНЭТ ООО</t>
         </is>
       </c>
-      <c r="C75" s="25" t="n">
+      <c r="C75" s="26" t="n">
         <v>76940</v>
       </c>
-      <c r="D75" s="26" t="inlineStr">
+      <c r="D75" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3584,10 +3635,10 @@
           <t>Самозанятый Лукина Екатерина Витальевна</t>
         </is>
       </c>
-      <c r="C76" s="25" t="n">
+      <c r="C76" s="26" t="n">
         <v>76540</v>
       </c>
-      <c r="D76" s="26" t="inlineStr">
+      <c r="D76" s="27" t="inlineStr">
         <is>
           <t>Фото видео</t>
         </is>
@@ -3599,10 +3650,10 @@
           <t>ПРОМТЕКСТИЛЬ ООО ТД</t>
         </is>
       </c>
-      <c r="C77" s="25" t="n">
+      <c r="C77" s="26" t="n">
         <v>76000</v>
       </c>
-      <c r="D77" s="26" t="inlineStr">
+      <c r="D77" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3614,10 +3665,10 @@
           <t>Самозанятый Орлов Сергей Юрьевич</t>
         </is>
       </c>
-      <c r="C78" s="25" t="n">
+      <c r="C78" s="26" t="n">
         <v>72360</v>
       </c>
-      <c r="D78" s="26" t="inlineStr">
+      <c r="D78" s="27" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -3629,10 +3680,10 @@
           <t>Евтеев Александр Викторович Самозанятый</t>
         </is>
       </c>
-      <c r="C79" s="25" t="n">
+      <c r="C79" s="26" t="n">
         <v>64756</v>
       </c>
-      <c r="D79" s="26" t="inlineStr">
+      <c r="D79" s="27" t="inlineStr">
         <is>
           <t>Общехозяйственные</t>
         </is>
@@ -3644,10 +3695,10 @@
           <t>АЛКАНА М ООО</t>
         </is>
       </c>
-      <c r="C80" s="25" t="n">
+      <c r="C80" s="26" t="n">
         <v>64600</v>
       </c>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="D80" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3659,10 +3710,10 @@
           <t>СитиМед ООО</t>
         </is>
       </c>
-      <c r="C81" s="25" t="n">
+      <c r="C81" s="26" t="n">
         <v>63600</v>
       </c>
-      <c r="D81" s="26" t="inlineStr">
+      <c r="D81" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3674,10 +3725,10 @@
           <t>ЭКОТЕХПРОМ АО</t>
         </is>
       </c>
-      <c r="C82" s="25" t="n">
+      <c r="C82" s="26" t="n">
         <v>52136.72</v>
       </c>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="D82" s="27" t="inlineStr">
         <is>
           <t>Вывоз ТКО и мед отходов</t>
         </is>
@@ -3689,10 +3740,10 @@
           <t>МЕДИКЛЦЕНТРСЕРВИС ООО</t>
         </is>
       </c>
-      <c r="C83" s="25" t="n">
+      <c r="C83" s="26" t="n">
         <v>51760</v>
       </c>
-      <c r="D83" s="26" t="inlineStr">
+      <c r="D83" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3704,10 +3755,10 @@
           <t>КРИОФАРМ ООО</t>
         </is>
       </c>
-      <c r="C84" s="25" t="n">
+      <c r="C84" s="26" t="n">
         <v>51675</v>
       </c>
-      <c r="D84" s="26" t="inlineStr">
+      <c r="D84" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3719,10 +3770,10 @@
           <t>БАРИСТА ООО</t>
         </is>
       </c>
-      <c r="C85" s="25" t="n">
+      <c r="C85" s="26" t="n">
         <v>48301.44</v>
       </c>
-      <c r="D85" s="26" t="inlineStr">
+      <c r="D85" s="27" t="inlineStr">
         <is>
           <t>Кофе</t>
         </is>
@@ -3734,10 +3785,10 @@
           <t>СИСТЕМА ООО</t>
         </is>
       </c>
-      <c r="C86" s="25" t="n">
+      <c r="C86" s="26" t="n">
         <v>48285.78</v>
       </c>
-      <c r="D86" s="26" t="inlineStr">
+      <c r="D86" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -3749,10 +3800,10 @@
           <t>Семин Сергей Владиславович</t>
         </is>
       </c>
-      <c r="C87" s="25" t="n">
+      <c r="C87" s="26" t="n">
         <v>40000</v>
       </c>
-      <c r="D87" s="26" t="inlineStr">
+      <c r="D87" s="27" t="inlineStr">
         <is>
           <t>Цветы</t>
         </is>
@@ -3764,10 +3815,10 @@
           <t>КОЛТАЧ СОЛЮШНС ООО</t>
         </is>
       </c>
-      <c r="C88" s="25" t="n">
+      <c r="C88" s="26" t="n">
         <v>39200</v>
       </c>
-      <c r="D88" s="26" t="inlineStr">
+      <c r="D88" s="27" t="inlineStr">
         <is>
           <t>Программное обнспечение</t>
         </is>
@@ -3779,10 +3830,10 @@
           <t>СМБ-СЕРВИС ООО</t>
         </is>
       </c>
-      <c r="C89" s="25" t="n">
+      <c r="C89" s="26" t="n">
         <v>37700</v>
       </c>
-      <c r="D89" s="26" t="inlineStr">
+      <c r="D89" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3794,10 +3845,10 @@
           <t>ГРАНД КОМФОРТ ООО</t>
         </is>
       </c>
-      <c r="C90" s="25" t="n">
+      <c r="C90" s="26" t="n">
         <v>37568</v>
       </c>
-      <c r="D90" s="26" t="inlineStr">
+      <c r="D90" s="27" t="inlineStr">
         <is>
           <t>Средства гигиены</t>
         </is>
@@ -3809,10 +3860,10 @@
           <t>ДОКТОР ДИСКАУНТ ООО</t>
         </is>
       </c>
-      <c r="C91" s="25" t="n">
+      <c r="C91" s="26" t="n">
         <v>35920.61</v>
       </c>
-      <c r="D91" s="26" t="inlineStr">
+      <c r="D91" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -3824,10 +3875,10 @@
           <t>Селектел АО</t>
         </is>
       </c>
-      <c r="C92" s="25" t="n">
+      <c r="C92" s="26" t="n">
         <v>30000</v>
       </c>
-      <c r="D92" s="26" t="inlineStr">
+      <c r="D92" s="27" t="inlineStr">
         <is>
           <t>IT услуги</t>
         </is>
@@ -3839,10 +3890,10 @@
           <t>МЕДЛИГА АО</t>
         </is>
       </c>
-      <c r="C93" s="25" t="n">
+      <c r="C93" s="26" t="n">
         <v>29800</v>
       </c>
-      <c r="D93" s="26" t="inlineStr">
+      <c r="D93" s="27" t="inlineStr">
         <is>
           <t>Капвложения и работы</t>
         </is>
@@ -3854,10 +3905,10 @@
           <t>ХЭДХАНТЕР ООО</t>
         </is>
       </c>
-      <c r="C94" s="25" t="n">
+      <c r="C94" s="26" t="n">
         <v>27629</v>
       </c>
-      <c r="D94" s="26" t="inlineStr">
+      <c r="D94" s="27" t="inlineStr">
         <is>
           <t>Подбор персонала</t>
         </is>
@@ -3869,10 +3920,10 @@
           <t>ЭКМУС ООО</t>
         </is>
       </c>
-      <c r="C95" s="25" t="n">
+      <c r="C95" s="26" t="n">
         <v>23625</v>
       </c>
-      <c r="D95" s="26" t="inlineStr">
+      <c r="D95" s="27" t="inlineStr">
         <is>
           <t>Утилизация медотходов</t>
         </is>
@@ -3884,10 +3935,10 @@
           <t>МЕТАЛЛИЧЕСКАЯ МЕБЕЛЬ ООО</t>
         </is>
       </c>
-      <c r="C96" s="25" t="n">
+      <c r="C96" s="26" t="n">
         <v>22130</v>
       </c>
-      <c r="D96" s="26" t="inlineStr">
+      <c r="D96" s="27" t="inlineStr">
         <is>
           <t>Мебель, инвентарь</t>
         </is>
@@ -3899,10 +3950,10 @@
           <t>МАНГО ТЕЛЕКОМ ООО</t>
         </is>
       </c>
-      <c r="C97" s="25" t="n">
+      <c r="C97" s="26" t="n">
         <v>20000</v>
       </c>
-      <c r="D97" s="26" t="inlineStr">
+      <c r="D97" s="27" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3914,10 +3965,10 @@
           <t>ТАТАРОВА В. Г. ИП</t>
         </is>
       </c>
-      <c r="C98" s="25" t="n">
+      <c r="C98" s="26" t="n">
         <v>20000</v>
       </c>
-      <c r="D98" s="26" t="inlineStr">
+      <c r="D98" s="27" t="inlineStr">
         <is>
           <t>Вода</t>
         </is>
@@ -3929,10 +3980,10 @@
           <t>ТАКСКОМ ООО</t>
         </is>
       </c>
-      <c r="C99" s="25" t="n">
+      <c r="C99" s="26" t="n">
         <v>17900</v>
       </c>
-      <c r="D99" s="26" t="inlineStr">
+      <c r="D99" s="27" t="inlineStr">
         <is>
           <t>Техподдержка ККТ</t>
         </is>
@@ -3944,10 +3995,10 @@
           <t>МРК-СНАБ ООО</t>
         </is>
       </c>
-      <c r="C100" s="25" t="n">
+      <c r="C100" s="26" t="n">
         <v>17750</v>
       </c>
-      <c r="D100" s="26" t="inlineStr">
+      <c r="D100" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -3959,10 +4010,10 @@
           <t>ОнЛайн Трейд ООО</t>
         </is>
       </c>
-      <c r="C101" s="25" t="n">
+      <c r="C101" s="26" t="n">
         <v>17740</v>
       </c>
-      <c r="D101" s="26" t="inlineStr">
+      <c r="D101" s="27" t="inlineStr">
         <is>
           <t>Электрооборудование</t>
         </is>
@@ -3974,10 +4025,10 @@
           <t>КантриКом АО</t>
         </is>
       </c>
-      <c r="C102" s="25" t="n">
+      <c r="C102" s="26" t="n">
         <v>17568</v>
       </c>
-      <c r="D102" s="26" t="inlineStr">
+      <c r="D102" s="27" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3989,10 +4040,10 @@
           <t>ЧОО Спектр секъюрити ООО</t>
         </is>
       </c>
-      <c r="C103" s="25" t="n">
+      <c r="C103" s="26" t="n">
         <v>16800</v>
       </c>
-      <c r="D103" s="26" t="inlineStr">
+      <c r="D103" s="27" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -4004,10 +4055,10 @@
           <t>ВЕСТ КОЛЛ ЛТД ООО</t>
         </is>
       </c>
-      <c r="C104" s="25" t="n">
+      <c r="C104" s="26" t="n">
         <v>16235.15</v>
       </c>
-      <c r="D104" s="26" t="inlineStr">
+      <c r="D104" s="27" t="inlineStr">
         <is>
           <t>Интернет</t>
         </is>
@@ -4019,10 +4070,10 @@
           <t>ТЕЛЕМИР ООО</t>
         </is>
       </c>
-      <c r="C105" s="25" t="n">
+      <c r="C105" s="26" t="n">
         <v>16192</v>
       </c>
-      <c r="D105" s="26" t="inlineStr">
+      <c r="D105" s="27" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -4034,10 +4085,10 @@
           <t>ИНСТРУ-МЕД ООО</t>
         </is>
       </c>
-      <c r="C106" s="25" t="n">
+      <c r="C106" s="26" t="n">
         <v>15120</v>
       </c>
-      <c r="D106" s="26" t="inlineStr">
+      <c r="D106" s="27" t="inlineStr">
         <is>
           <t>Расходник</t>
         </is>
@@ -4049,10 +4100,10 @@
           <t>Алдошин Павел Александрович ИП</t>
         </is>
       </c>
-      <c r="C107" s="25" t="n">
+      <c r="C107" s="26" t="n">
         <v>15000</v>
       </c>
-      <c r="D107" s="26" t="inlineStr">
+      <c r="D107" s="27" t="inlineStr">
         <is>
           <t>Аренда кофемашины</t>
         </is>
@@ -4064,10 +4115,10 @@
           <t>Вилорд ООО</t>
         </is>
       </c>
-      <c r="C108" s="25" t="n">
+      <c r="C108" s="26" t="n">
         <v>12800</v>
       </c>
-      <c r="D108" s="26" t="inlineStr">
+      <c r="D108" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -4079,10 +4130,10 @@
           <t>ГБУЗ ЦЛО ДЗМ</t>
         </is>
       </c>
-      <c r="C109" s="25" t="n">
+      <c r="C109" s="26" t="n">
         <v>12760</v>
       </c>
-      <c r="D109" s="26" t="inlineStr">
+      <c r="D109" s="27" t="inlineStr">
         <is>
           <t>Наркотики</t>
         </is>
@@ -4094,10 +4145,10 @@
           <t>АТОЛ ОНЛАЙН ООО</t>
         </is>
       </c>
-      <c r="C110" s="25" t="n">
+      <c r="C110" s="26" t="n">
         <v>12505</v>
       </c>
-      <c r="D110" s="26" t="inlineStr">
+      <c r="D110" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -4109,10 +4160,10 @@
           <t>Самозанятый Кожина Наталия Васильевна</t>
         </is>
       </c>
-      <c r="C111" s="25" t="n">
+      <c r="C111" s="26" t="n">
         <v>11660</v>
       </c>
-      <c r="D111" s="26" t="inlineStr">
+      <c r="D111" s="27" t="inlineStr">
         <is>
           <t>Дизайн-услуги</t>
         </is>
@@ -4124,10 +4175,10 @@
           <t>АСПРОМЕД ООО</t>
         </is>
       </c>
-      <c r="C112" s="25" t="n">
+      <c r="C112" s="26" t="n">
         <v>10940</v>
       </c>
-      <c r="D112" s="26" t="inlineStr">
+      <c r="D112" s="27" t="inlineStr">
         <is>
           <t>Расходка</t>
         </is>
@@ -4139,10 +4190,10 @@
           <t>МГУТУ АНО ДПО</t>
         </is>
       </c>
-      <c r="C113" s="25" t="n">
+      <c r="C113" s="26" t="n">
         <v>10900</v>
       </c>
-      <c r="D113" s="26" t="inlineStr">
+      <c r="D113" s="27" t="inlineStr">
         <is>
           <t>Обучение персонала</t>
         </is>
@@ -4154,10 +4205,10 @@
           <t>АО "Почта России"</t>
         </is>
       </c>
-      <c r="C114" s="25" t="n">
+      <c r="C114" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="D114" s="26" t="inlineStr">
+      <c r="D114" s="27" t="inlineStr">
         <is>
           <t>Общехоз.расходы прочие</t>
         </is>
@@ -4169,10 +4220,10 @@
           <t>МЕДРОКЕТ ООО</t>
         </is>
       </c>
-      <c r="C115" s="25" t="n">
+      <c r="C115" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="D115" s="26" t="inlineStr">
+      <c r="D115" s="27" t="inlineStr">
         <is>
           <t>ПроДокторов</t>
         </is>
@@ -4184,10 +4235,10 @@
           <t>ТЕХМОНТАЖ ООО</t>
         </is>
       </c>
-      <c r="C116" s="25" t="n">
+      <c r="C116" s="26" t="n">
         <v>9800</v>
       </c>
-      <c r="D116" s="26" t="inlineStr">
+      <c r="D116" s="27" t="inlineStr">
         <is>
           <t>Охрана</t>
         </is>
@@ -4199,10 +4250,10 @@
           <t>Деловые линии ООО</t>
         </is>
       </c>
-      <c r="C117" s="25" t="n">
+      <c r="C117" s="26" t="n">
         <v>7495</v>
       </c>
-      <c r="D117" s="26" t="inlineStr">
+      <c r="D117" s="27" t="inlineStr">
         <is>
           <t>Доставка</t>
         </is>
@@ -4214,10 +4265,10 @@
           <t>ТЕХМОНТАЖСЕРВИС ООО</t>
         </is>
       </c>
-      <c r="C118" s="25" t="n">
+      <c r="C118" s="26" t="n">
         <v>7000</v>
       </c>
-      <c r="D118" s="26" t="inlineStr">
+      <c r="D118" s="27" t="inlineStr">
         <is>
           <t>ТО СКУД, пожарной сигнализации</t>
         </is>
@@ -4229,10 +4280,10 @@
           <t>КИКОТЬ ОЛЕГ МИХАЙЛОВИЧ ИП</t>
         </is>
       </c>
-      <c r="C119" s="25" t="n">
+      <c r="C119" s="26" t="n">
         <v>6135</v>
       </c>
-      <c r="D119" s="26" t="inlineStr">
+      <c r="D119" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -4244,10 +4295,10 @@
           <t>Самозанятый Кучер Татьяна Александровна</t>
         </is>
       </c>
-      <c r="C120" s="25" t="n">
+      <c r="C120" s="26" t="n">
         <v>5400</v>
       </c>
-      <c r="D120" s="26" t="inlineStr">
+      <c r="D120" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -4259,10 +4310,10 @@
           <t>ДЕАЛМЕД АО</t>
         </is>
       </c>
-      <c r="C121" s="25" t="n">
+      <c r="C121" s="26" t="n">
         <v>5170</v>
       </c>
-      <c r="D121" s="26" t="inlineStr">
+      <c r="D121" s="27" t="inlineStr">
         <is>
           <t>Медицинские материалы</t>
         </is>
@@ -4274,10 +4325,10 @@
           <t>ИНФОТЕХ ООО</t>
         </is>
       </c>
-      <c r="C122" s="25" t="n">
+      <c r="C122" s="26" t="n">
         <v>5100</v>
       </c>
-      <c r="D122" s="26" t="inlineStr">
+      <c r="D122" s="27" t="inlineStr">
         <is>
           <t>Оргтехника</t>
         </is>
@@ -4289,10 +4340,10 @@
           <t>Аквапрактика ООО</t>
         </is>
       </c>
-      <c r="C123" s="25" t="n">
+      <c r="C123" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="D123" s="26" t="inlineStr">
+      <c r="D123" s="27" t="inlineStr">
         <is>
           <t>Обслуживание аквариума</t>
         </is>
@@ -4304,10 +4355,10 @@
           <t>Cамозанятый Котлярова Олеся Владимировна</t>
         </is>
       </c>
-      <c r="C124" s="25" t="n">
+      <c r="C124" s="26" t="n">
         <v>1100</v>
       </c>
-      <c r="D124" s="26" t="inlineStr">
+      <c r="D124" s="27" t="inlineStr">
         <is>
           <t>Прочие управленческие</t>
         </is>
@@ -4319,10 +4370,10 @@
           <t>АО "Альфа Банк"</t>
         </is>
       </c>
-      <c r="C125" s="25" t="n">
+      <c r="C125" s="26" t="n">
         <v>668.5599999999999</v>
       </c>
-      <c r="D125" s="26" t="inlineStr">
+      <c r="D125" s="27" t="inlineStr">
         <is>
           <t>Услуги банка (через счёт 60)</t>
         </is>
@@ -4334,10 +4385,10 @@
           <t>БАНК ВТБ (ПАО)</t>
         </is>
       </c>
-      <c r="C126" s="25" t="n">
+      <c r="C126" s="26" t="n">
         <v>550</v>
       </c>
-      <c r="D126" s="26" t="inlineStr">
+      <c r="D126" s="27" t="inlineStr">
         <is>
           <t>Услуги банка (через счёт 60)</t>
         </is>
@@ -4358,7 +4409,7 @@
       <c r="F127" s="13" t="n"/>
       <c r="G127" s="13" t="n"/>
       <c r="H127" s="13" t="n"/>
-      <c r="I127" s="20" t="inlineStr">
+      <c r="I127" s="18" t="inlineStr">
         <is>
           <t>в т.ч. за счёт кредитной линии — см. справочную строку основного листа</t>
         </is>
@@ -4421,10 +4472,10 @@
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <v>4365745</v>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4436,10 +4487,10 @@
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>2545000</v>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4451,10 +4502,10 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>3907000</v>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4466,10 +4517,10 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <v>4552200</v>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4481,10 +4532,10 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <v>2698594</v>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4496,10 +4547,10 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <v>1615200</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4511,10 +4562,10 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>3019500</v>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4526,10 +4577,10 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="26" t="n">
         <v>3846700</v>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4541,10 +4592,10 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <v>1491000</v>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4556,10 +4607,10 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <v>3202575</v>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>старая управленка</t>
         </is>
@@ -4571,10 +4622,10 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="26" t="n">
         <v>2902000</v>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4586,10 +4637,10 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="26" t="n">
         <v>5222500</v>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4601,10 +4652,10 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="26" t="n">
         <v>5695800</v>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4616,10 +4667,10 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="26" t="n">
         <v>1905500</v>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4631,10 +4682,10 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="26" t="n">
         <v>4595500</v>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4646,10 +4697,10 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="26" t="n">
         <v>2365500</v>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4661,10 +4712,10 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="26" t="n">
         <v>1636700</v>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4676,10 +4727,10 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="26" t="n">
         <v>2297600</v>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4691,10 +4742,10 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="26" t="n">
         <v>4293000</v>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4706,10 +4757,10 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="26" t="n">
         <v>4903500</v>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4721,10 +4772,10 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="26" t="n">
         <v>1239300</v>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4736,10 +4787,10 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="26" t="n">
         <v>3397700</v>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4751,10 +4802,10 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="26" t="n">
         <v>1935000</v>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4766,10 +4817,10 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="26" t="n">
         <v>2027500</v>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4781,10 +4832,10 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="26" t="n">
         <v>5054800</v>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4796,10 +4847,10 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="26" t="n">
         <v>3195500</v>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4811,10 +4862,10 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <v>1630000</v>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4826,10 +4877,10 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="26" t="n">
         <v>2421540</v>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4841,10 +4892,10 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="26" t="n">
         <v>2486500</v>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4856,10 +4907,10 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="26" t="n">
         <v>3711000</v>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>
@@ -4871,10 +4922,10 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="26" t="n">
         <v>3141900</v>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>новая управленка</t>
         </is>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I112"/>
+  <dimension ref="B1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>141191.07</v>
+        <v>142409.63</v>
       </c>
       <c r="D49" s="7">
         <f>C49/2</f>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="C53" s="21" t="n">
-        <v>69794048.05</v>
+        <v>69792829.48999999</v>
       </c>
       <c r="D53" s="21">
         <f>C53/2</f>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>2621284.79</v>
+        <v>2620066.23</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="C79" s="20" t="n">
-        <v>42868</v>
+        <v>1658023.69</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
@@ -2060,15 +2060,15 @@
         </is>
       </c>
       <c r="C88" s="24">
-        <f>-(C77-42868.0)</f>
+        <f>-(C77-C79)</f>
         <v/>
       </c>
       <c r="D88" s="24">
-        <f>-(D77-21434.0)</f>
+        <f>-(D77-C79/2)</f>
         <v/>
       </c>
       <c r="E88" s="24">
-        <f>-(E77-21434.0)</f>
+        <f>-(E77-C79/2)</f>
         <v/>
       </c>
       <c r="F88" s="8" t="n"/>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="C89" s="24" t="n">
-        <v>-42868</v>
+        <v>-1658023.69</v>
       </c>
       <c r="D89" s="24" t="n">
-        <v>-30620</v>
+        <v>-170861.64</v>
       </c>
       <c r="E89" s="24" t="n">
-        <v>-12248</v>
+        <v>-1487162.05</v>
       </c>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
@@ -2125,224 +2125,224 @@
       <c r="I90" s="8" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Материалы за операции</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="n">
+        <v>-1615155.69</v>
+      </c>
+      <c r="D91" s="25" t="n">
+        <v>-140241.64</v>
+      </c>
+      <c r="E91" s="25" t="n">
+        <v>-1474914.05</v>
+      </c>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C91" s="15">
+      <c r="C92" s="15">
         <f>SUM(C83:C89)</f>
         <v/>
       </c>
-      <c r="D91" s="15">
+      <c r="D92" s="15">
         <f>SUM(D83:D89)</f>
         <v/>
       </c>
-      <c r="E91" s="15">
+      <c r="E92" s="15">
         <f>SUM(E83:E89)</f>
         <v/>
       </c>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="16" t="n"/>
-      <c r="H91" s="16" t="n"/>
-      <c r="I91" s="16" t="n"/>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="B93" s="3" t="inlineStr">
+      <c r="F92" s="16" t="n"/>
+      <c r="G92" s="16" t="n"/>
+      <c r="H92" s="16" t="n"/>
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="B94" s="5" t="inlineStr">
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C95" s="7">
-        <f>C91</f>
-        <v/>
-      </c>
-      <c r="D95" s="7">
-        <f>D91</f>
-        <v/>
-      </c>
-      <c r="E95" s="7">
-        <f>E91</f>
-        <v/>
-      </c>
-      <c r="F95" s="8" t="n"/>
-      <c r="G95" s="8" t="n"/>
-      <c r="H95" s="8" t="n"/>
-      <c r="I95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
+          <t>Доход за месяц</t>
         </is>
       </c>
       <c r="C96" s="7">
-        <f>D96+E96</f>
-        <v/>
-      </c>
-      <c r="D96" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>45275972.21</v>
+        <f>C92</f>
+        <v/>
+      </c>
+      <c r="D96" s="7">
+        <f>D92</f>
+        <v/>
+      </c>
+      <c r="E96" s="7">
+        <f>E92</f>
+        <v/>
       </c>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I96" s="8" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C97" s="24">
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C97" s="7">
         <f>D97+E97</f>
         <v/>
       </c>
-      <c r="D97" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E97" s="24" t="n">
-        <v>-5882353</v>
+      <c r="D97" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="n"/>
       <c r="I97" s="10" t="inlineStr">
         <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="23" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C98" s="24">
+        <f>D98+E98</f>
+        <v/>
+      </c>
+      <c r="D98" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E98" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="14" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C98" s="15">
-        <f>SUM(C95:C97)</f>
-        <v/>
-      </c>
-      <c r="D98" s="15">
-        <f>SUM(D95:D97)</f>
-        <v/>
-      </c>
-      <c r="E98" s="15">
-        <f>SUM(E95:E97)</f>
-        <v/>
-      </c>
-      <c r="F98" s="16" t="n"/>
-      <c r="G98" s="16" t="n"/>
-      <c r="H98" s="16" t="n"/>
-      <c r="I98" s="16" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="B100" s="3" t="inlineStr">
+      <c r="C99" s="15">
+        <f>SUM(C96:C98)</f>
+        <v/>
+      </c>
+      <c r="D99" s="15">
+        <f>SUM(D96:D98)</f>
+        <v/>
+      </c>
+      <c r="E99" s="15">
+        <f>SUM(E96:E98)</f>
+        <v/>
+      </c>
+      <c r="F99" s="16" t="n"/>
+      <c r="G99" s="16" t="n"/>
+      <c r="H99" s="16" t="n"/>
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="inlineStr"/>
-    </row>
-    <row r="101" ht="26" customHeight="1">
-      <c r="B101" s="5" t="inlineStr">
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I102" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — долг на начало месяца</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>16545367</v>
-      </c>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="n"/>
-      <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано за месяц</t>
+          <t>Кредитная линия — долг на начало месяца</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>11000000</v>
+        <v>16545367</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
@@ -2351,34 +2351,38 @@
       <c r="H103" s="8" t="n"/>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на конец месяца</t>
+          <t>Кредитная линия — выбрано за месяц</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>27545367</v>
+        <v>11000000</v>
       </c>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t>Кредитная линия — долг на конец месяца</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>30000000</v>
+        <v>27545367</v>
       </c>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
@@ -2390,11 +2394,11 @@
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>2454633</v>
+        <v>30000000</v>
       </c>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
@@ -2406,101 +2410,97 @@
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Проценты по кредиту, уплачено</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>204388.93</v>
+        <v>2454633</v>
       </c>
       <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
       <c r="G107" s="8" t="n"/>
       <c r="H107" s="8" t="n"/>
-      <c r="I107" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
-        </is>
-      </c>
+      <c r="I107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Проценты по кредиту, уплачено</t>
         </is>
       </c>
       <c r="C108" s="7" t="n">
-        <v>396337.24</v>
+        <v>204388.93</v>
       </c>
       <c r="D108" s="8" t="n"/>
       <c r="E108" s="8" t="n"/>
       <c r="F108" s="8" t="n"/>
       <c r="G108" s="8" t="n"/>
       <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n"/>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="8" t="n"/>
       <c r="H109" s="8" t="n"/>
-      <c r="I109" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="n">
-        <v>373487.16</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n"/>
       <c r="D110" s="8" t="n"/>
       <c r="E110" s="8" t="n"/>
       <c r="F110" s="8" t="n"/>
       <c r="G110" s="8" t="n"/>
       <c r="H110" s="8" t="n"/>
-      <c r="I110" s="8" t="n"/>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка, проведённые через счёт 60</t>
+          <t>Комиссия эквайринга</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>1218.56</v>
+        <v>373487.16</v>
       </c>
       <c r="D111" s="8" t="n"/>
       <c r="E111" s="8" t="n"/>
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="n"/>
-      <c r="I111" s="10" t="inlineStr">
-        <is>
-          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
-        </is>
-      </c>
+      <c r="I111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+          <t>Услуги банка, проведённые через счёт 60</t>
         </is>
       </c>
       <c r="C112" s="7" t="n">
-        <v>3284000</v>
+        <v>1218.56</v>
       </c>
       <c r="D112" s="8" t="n"/>
       <c r="E112" s="8" t="n"/>
@@ -2508,6 +2508,26 @@
       <c r="G112" s="8" t="n"/>
       <c r="H112" s="8" t="n"/>
       <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>3284000</v>
+      </c>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="8" t="n"/>
+      <c r="G113" s="8" t="n"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="10" t="inlineStr">
         <is>
           <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
         </is>
@@ -4375,7 +4395,7 @@
       </c>
       <c r="D125" s="27" t="inlineStr">
         <is>
-          <t>Услуги банка (через счёт 60)</t>
+          <t>Услуги банка</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4410,7 @@
       </c>
       <c r="D126" s="27" t="inlineStr">
         <is>
-          <t>Услуги банка (через счёт 60)</t>
+          <t>Услуги банка</t>
         </is>
       </c>
     </row>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -2496,11 +2496,11 @@
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка, проведённые через счёт 60</t>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
         </is>
       </c>
       <c r="C112" s="7" t="n">
-        <v>1218.56</v>
+        <v>3284000</v>
       </c>
       <c r="D112" s="8" t="n"/>
       <c r="E112" s="8" t="n"/>
@@ -2509,18 +2509,18 @@
       <c r="H112" s="8" t="n"/>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>Альфа-Банк 668,56 и ВТБ 550,00 — ошибка проводки, место им на счёте 91; на итог не влияет, деньги посчитаны один раз</t>
+          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+          <t>Авансы арендодателям на конец месяца</t>
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>3284000</v>
+        <v>31195343.31</v>
       </c>
       <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
@@ -2529,7 +2529,7 @@
       <c r="H113" s="8" t="n"/>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+          <t>дебетовое сальдо счёта 60: Паритет (стр.12) работает июльскую предоплату, поэтому коммунальных платежей в августе нет</t>
         </is>
       </c>
     </row>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Расчёт" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Расходы по контрагентам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Выручка по дням" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Статьи расходов" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Выручка по дням" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;—"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -132,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,17 +174,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I113"/>
+  <dimension ref="B1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1492,7 +1495,7 @@
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>4527900</v>
+        <v>4728500</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1632,11 +1635,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Аренда Inmode</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>582359.62</v>
+        <v>210000</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1646,12 +1649,14 @@
       <c r="I65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Кровь</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>181735.9</v>
+      </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
@@ -1662,11 +1667,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+          <t xml:space="preserve">            Медоборудование</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>4692500</v>
+        <v>173834.16</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1678,11 +1683,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Анализы</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>2505800</v>
+        <v>102102</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1692,30 +1697,32 @@
       <c r="I68" s="8" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>1155000</v>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            прочие статьи, 4 шт</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="n">
+        <v>152121.72</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>полный список — лист «Статьи расходов»</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Прочие управленческие</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>878789.77</v>
-      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
@@ -1726,11 +1733,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>516000</v>
+        <v>4692500</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1742,11 +1749,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>435435</v>
+        <v>2505800</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1758,11 +1765,11 @@
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>337440</v>
+        <v>1155000</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -1774,11 +1781,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>330000</v>
+        <v>516000</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1790,11 +1797,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>320000</v>
+        <v>441570</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1806,11 +1813,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            прочие статьи блока</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>2620066.23</v>
+        <v>337440</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1820,162 +1827,128 @@
       <c r="I76" s="8" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ</t>
-        </is>
-      </c>
-      <c r="C77" s="15">
-        <f>SUM(C47:C53)</f>
-        <v/>
-      </c>
-      <c r="D77" s="15">
-        <f>SUM(D47:D53)</f>
-        <v/>
-      </c>
-      <c r="E77" s="15">
-        <f>SUM(E47:E53)</f>
-        <v/>
-      </c>
-      <c r="F77" s="16" t="n"/>
-      <c r="G77" s="16" t="n"/>
-      <c r="H77" s="16" t="n"/>
-      <c r="I77" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
-        </is>
-      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Услуги юриста</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>Справочно: ремонт за счёт кредитной линии</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="n">
-        <v>11000000</v>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Складской учет</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>320000</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
-        </is>
-      </c>
+      <c r="I78" s="8" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>Справочно: из них личные расходы врачей</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="n">
-        <v>1658023.69</v>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ПО и IT-сервисы</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>279349.86</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>пополам не делятся, отнесены каждому свои — см. шаг 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>методика 50/50</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="26" customHeight="1">
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Маланичев</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>Погосян</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Как считается</t>
-        </is>
-      </c>
+      <c r="I79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Битрикс 24</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>264850</v>
+      </c>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="8" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Сайт</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>254000</v>
+      </c>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            IT услуги</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>247935.06</v>
+      </c>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="8" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C83" s="7">
-        <f>D83+E83</f>
-        <v/>
-      </c>
-      <c r="D83" s="7">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="E83" s="7">
-        <f>E35</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Реклама</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>227800</v>
+      </c>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
+      <c r="I83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
-        </is>
-      </c>
-      <c r="C84" s="7">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="D84" s="7">
-        <f>F35/2</f>
-        <v/>
-      </c>
-      <c r="E84" s="7">
-        <f>F35/2</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Светильники и оборудование</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>179400</v>
+      </c>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
@@ -1984,21 +1957,14 @@
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
-        </is>
-      </c>
-      <c r="C85" s="7">
-        <f>H35</f>
-        <v/>
-      </c>
-      <c r="D85" s="7">
-        <f>H35/2</f>
-        <v/>
-      </c>
-      <c r="E85" s="7">
-        <f>H35/2</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Услуги инженера</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>159575</v>
+      </c>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
@@ -2007,21 +1973,14 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
-        </is>
-      </c>
-      <c r="C86" s="7">
-        <f>G35</f>
-        <v/>
-      </c>
-      <c r="D86" s="7">
-        <f>G35/2</f>
-        <v/>
-      </c>
-      <c r="E86" s="7">
-        <f>G35/2</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Канц и хоз расходы</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>157671.72</v>
+      </c>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
@@ -2030,95 +1989,62 @@
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
+          <t xml:space="preserve">            Сервис речевой аналитики</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>396337.24</v>
-      </c>
-      <c r="D87" s="7">
-        <f>C87/2</f>
-        <v/>
-      </c>
-      <c r="E87" s="7">
-        <f>C87/2</f>
-        <v/>
-      </c>
+        <v>152250</v>
+      </c>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I87" s="8" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус ½ общих расходов</t>
-        </is>
-      </c>
-      <c r="C88" s="24">
-        <f>-(C77-C79)</f>
-        <v/>
-      </c>
-      <c r="D88" s="24">
-        <f>-(D77-C79/2)</f>
-        <v/>
-      </c>
-      <c r="E88" s="24">
-        <f>-(E77-C79/2)</f>
-        <v/>
-      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Общехозяйственные</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>137116</v>
+      </c>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>итог блока «Расходы» без личных, пополам</t>
-        </is>
-      </c>
+      <c r="I88" s="8" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>7. Минус личные расходы (каждый свои)</t>
-        </is>
-      </c>
-      <c r="C89" s="24" t="n">
-        <v>-1658023.69</v>
-      </c>
-      <c r="D89" s="24" t="n">
-        <v>-170861.64</v>
-      </c>
-      <c r="E89" s="24" t="n">
-        <v>-1487162.05</v>
-      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Косметология</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>114858</v>
+      </c>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>заказано лично под врача, пополам не делится</t>
-        </is>
-      </c>
+      <c r="I89" s="8" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Анализы</t>
-        </is>
-      </c>
-      <c r="C90" s="25" t="n">
-        <v>-42868</v>
-      </c>
-      <c r="D90" s="25" t="n">
-        <v>-30620</v>
-      </c>
-      <c r="E90" s="25" t="n">
-        <v>-12248</v>
-      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Такси</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="n"/>
@@ -2127,367 +2053,430 @@
     <row r="91">
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Материалы за операции</t>
-        </is>
-      </c>
-      <c r="C91" s="25" t="n">
-        <v>-1615155.69</v>
-      </c>
-      <c r="D91" s="25" t="n">
-        <v>-140241.64</v>
-      </c>
-      <c r="E91" s="25" t="n">
-        <v>-1474914.05</v>
-      </c>
+          <t xml:space="preserve">            прочие статьи, 28 шт</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="n">
+        <v>779881.2000000001</v>
+      </c>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
-      <c r="I91" s="8" t="n"/>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>полный список — лист «Статьи расходов»</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>ДОХОД ЗА МЕСЯЦ</t>
+          <t>ИТОГО РАСХОДЫ</t>
         </is>
       </c>
       <c r="C92" s="15">
-        <f>SUM(C83:C89)</f>
+        <f>SUM(C47:C53)</f>
         <v/>
       </c>
       <c r="D92" s="15">
-        <f>SUM(D83:D89)</f>
+        <f>SUM(D47:D53)</f>
         <v/>
       </c>
       <c r="E92" s="15">
-        <f>SUM(E83:E89)</f>
+        <f>SUM(E47:E53)</f>
         <v/>
       </c>
       <c r="F92" s="16" t="n"/>
       <c r="G92" s="16" t="n"/>
       <c r="H92" s="16" t="n"/>
-      <c r="I92" s="16" t="n"/>
-    </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="n"/>
-      <c r="F94" s="4" t="n"/>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="n"/>
-      <c r="I94" s="4" t="inlineStr"/>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: ремонт за счёт кредитной линии</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: из них личные расходы врачей</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="n">
+        <v>1658023.69</v>
+      </c>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>пополам не делятся, отнесены каждому свои — см. шаг 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>методика 50/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C96" s="7">
-        <f>C92</f>
-        <v/>
-      </c>
-      <c r="D96" s="7">
-        <f>D92</f>
-        <v/>
-      </c>
-      <c r="E96" s="7">
-        <f>E92</f>
-        <v/>
-      </c>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C97" s="7">
-        <f>D97+E97</f>
-        <v/>
-      </c>
-      <c r="D97" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>45275972.21</v>
-      </c>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Как считается</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C98" s="24">
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>1. Личная выручка (свои операции)</t>
+        </is>
+      </c>
+      <c r="C98" s="7">
         <f>D98+E98</f>
         <v/>
       </c>
-      <c r="D98" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E98" s="24" t="n">
-        <v>-5882353</v>
+      <c r="D98" s="7">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E98" s="7">
+        <f>E35</f>
+        <v/>
       </c>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>начислено с НДФЛ</t>
+          <t>своя строка из блока «Выручка»</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
-        </is>
-      </c>
-      <c r="C99" s="15">
-        <f>SUM(C96:C98)</f>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>2. Половина выручки других хирургов</t>
+        </is>
+      </c>
+      <c r="C99" s="7">
+        <f>F35</f>
         <v/>
       </c>
-      <c r="D99" s="15">
-        <f>SUM(D96:D98)</f>
+      <c r="D99" s="7">
+        <f>F35/2</f>
         <v/>
       </c>
-      <c r="E99" s="15">
-        <f>SUM(E96:E98)</f>
+      <c r="E99" s="7">
+        <f>F35/2</f>
         <v/>
       </c>
-      <c r="F99" s="16" t="n"/>
-      <c r="G99" s="16" t="n"/>
-      <c r="H99" s="16" t="n"/>
-      <c r="I99" s="16" t="n"/>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>6. СПРАВОЧНО</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="n"/>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="inlineStr"/>
-    </row>
-    <row r="102" ht="26" customHeight="1">
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Сумма</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>3. Половина выручки косметологии</t>
+        </is>
+      </c>
+      <c r="C100" s="7">
+        <f>H35</f>
+        <v/>
+      </c>
+      <c r="D100" s="7">
+        <f>H35/2</f>
+        <v/>
+      </c>
+      <c r="E100" s="7">
+        <f>H35/2</f>
+        <v/>
+      </c>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C101" s="7">
+        <f>G35</f>
+        <v/>
+      </c>
+      <c r="D101" s="7">
+        <f>G35/2</f>
+        <v/>
+      </c>
+      <c r="E101" s="7">
+        <f>G35/2</f>
+        <v/>
+      </c>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D102" s="7">
+        <f>C102/2</f>
+        <v/>
+      </c>
+      <c r="E102" s="7">
+        <f>C102/2</f>
+        <v/>
+      </c>
+      <c r="F102" s="8" t="n"/>
+      <c r="G102" s="8" t="n"/>
+      <c r="H102" s="8" t="n"/>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>начислены банком на остатки</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — долг на начало месяца</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="n">
-        <v>16545367</v>
-      </c>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
+      <c r="B103" s="24" t="inlineStr">
+        <is>
+          <t>6. Минус ½ общих расходов</t>
+        </is>
+      </c>
+      <c r="C103" s="25">
+        <f>-(C92-C94)</f>
+        <v/>
+      </c>
+      <c r="D103" s="25">
+        <f>-(D92-C94/2)</f>
+        <v/>
+      </c>
+      <c r="E103" s="25">
+        <f>-(E92-C94/2)</f>
+        <v/>
+      </c>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
+          <t>итог блока «Расходы» без личных, пополам</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — выбрано за месяц</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="8" t="n"/>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>7. Минус личные расходы (каждый свои)</t>
+        </is>
+      </c>
+      <c r="C104" s="25" t="n">
+        <v>-1658023.69</v>
+      </c>
+      <c r="D104" s="25" t="n">
+        <v>-170861.64</v>
+      </c>
+      <c r="E104" s="25" t="n">
+        <v>-1487162.05</v>
+      </c>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+          <t>заказано лично под врача, пополам не делится</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — долг на конец месяца</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="n">
-        <v>27545367</v>
-      </c>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Анализы</t>
+        </is>
+      </c>
+      <c r="C105" s="23" t="n">
+        <v>-42868</v>
+      </c>
+      <c r="D105" s="23" t="n">
+        <v>-30620</v>
+      </c>
+      <c r="E105" s="23" t="n">
+        <v>-12248</v>
+      </c>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
       <c r="I105" s="8" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — лимит</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Материалы за операции</t>
+        </is>
+      </c>
+      <c r="C106" s="23" t="n">
+        <v>-1615155.69</v>
+      </c>
+      <c r="D106" s="23" t="n">
+        <v>-140241.64</v>
+      </c>
+      <c r="E106" s="23" t="n">
+        <v>-1474914.05</v>
+      </c>
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
       <c r="I106" s="8" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — свободный остаток</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="n">
-        <v>2454633</v>
-      </c>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>Проценты по кредиту, уплачено</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="n">
-        <v>204388.93</v>
-      </c>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>Проценты по депозитам за месяц</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n">
-        <v>396337.24</v>
-      </c>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
-      <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="8" t="n"/>
-      <c r="G110" s="8" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>ДОХОД ЗА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="C107" s="15">
+        <f>SUM(C98:C104)</f>
+        <v/>
+      </c>
+      <c r="D107" s="15">
+        <f>SUM(D98:D104)</f>
+        <v/>
+      </c>
+      <c r="E107" s="15">
+        <f>SUM(E98:E104)</f>
+        <v/>
+      </c>
+      <c r="F107" s="16" t="n"/>
+      <c r="G107" s="16" t="n"/>
+      <c r="H107" s="16" t="n"/>
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110" ht="26" customHeight="1">
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Маланичев</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Погосян</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>373487.16</v>
-      </c>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
+          <t>Доход за месяц</t>
+        </is>
+      </c>
+      <c r="C111" s="7">
+        <f>C107</f>
+        <v/>
+      </c>
+      <c r="D111" s="7">
+        <f>D107</f>
+        <v/>
+      </c>
+      <c r="E111" s="7">
+        <f>E107</f>
+        <v/>
+      </c>
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="n"/>
@@ -2496,38 +2485,300 @@
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="n">
-        <v>3284000</v>
-      </c>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C112" s="7">
+        <f>D112+E112</f>
+        <v/>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>45275972.21</v>
+      </c>
       <c r="F112" s="8" t="n"/>
       <c r="G112" s="8" t="n"/>
       <c r="H112" s="8" t="n"/>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+          <t>ручной ввод бухгалтерии</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>Авансы арендодателям на конец месяца</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="n">
-        <v>31195343.31</v>
-      </c>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C113" s="25">
+        <f>D113+E113</f>
+        <v/>
+      </c>
+      <c r="D113" s="25" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E113" s="25" t="n">
+        <v>-5882353</v>
+      </c>
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="n"/>
       <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>начислено с НДФЛ</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
+        </is>
+      </c>
+      <c r="C114" s="15">
+        <f>SUM(C111:C113)</f>
+        <v/>
+      </c>
+      <c r="D114" s="15">
+        <f>SUM(D111:D113)</f>
+        <v/>
+      </c>
+      <c r="E114" s="15">
+        <f>SUM(E111:E113)</f>
+        <v/>
+      </c>
+      <c r="F114" s="16" t="n"/>
+      <c r="G114" s="16" t="n"/>
+      <c r="H114" s="16" t="n"/>
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>6. СПРАВОЧНО</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117" ht="26" customHeight="1">
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — долг на начало месяца</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>16545367</v>
+      </c>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="8" t="n"/>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — выбрано за месяц</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="8" t="n"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — долг на конец месяца</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>27545367</v>
+      </c>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8" t="n"/>
+      <c r="G120" s="8" t="n"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — лимит</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="8" t="n"/>
+      <c r="G121" s="8" t="n"/>
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="8" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — свободный остаток</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>2454633</v>
+      </c>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
+      <c r="G122" s="8" t="n"/>
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="8" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту, уплачено</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>204388.93</v>
+      </c>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="8" t="n"/>
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="8" t="n"/>
+      <c r="G124" s="8" t="n"/>
+      <c r="H124" s="8" t="n"/>
+      <c r="I124" s="8" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
+      <c r="G126" s="8" t="n"/>
+      <c r="H126" s="8" t="n"/>
+      <c r="I126" s="8" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>3284000</v>
+      </c>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="8" t="n"/>
+      <c r="F127" s="8" t="n"/>
+      <c r="G127" s="8" t="n"/>
+      <c r="H127" s="8" t="n"/>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Авансы арендодателям на конец месяца</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>31195343.31</v>
+      </c>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="8" t="n"/>
+      <c r="F128" s="8" t="n"/>
+      <c r="G128" s="8" t="n"/>
+      <c r="H128" s="8" t="n"/>
+      <c r="I128" s="10" t="inlineStr">
         <is>
           <t>дебетовое сальдо счёта 60: Паритет (стр.12) работает июльскую предоплату, поэтому коммунальных платежей в августе нет</t>
         </is>
@@ -3285,7 +3536,7 @@
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Светильники и оборудование</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3551,7 @@
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Медоборудование</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3641,7 @@
       </c>
       <c r="D58" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Импланты</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3806,7 @@
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Реклама</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3836,7 @@
       </c>
       <c r="D71" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Внедрение финансового учёта</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3971,7 @@
       </c>
       <c r="D80" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Импланты</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3986,7 @@
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Бланки, мед.журналы, мед.книжки</t>
         </is>
       </c>
     </row>
@@ -3855,7 +4106,7 @@
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Реклама</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4556,7 @@
       </c>
       <c r="D119" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Обслуживание 1СУправление</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4571,7 @@
       </c>
       <c r="D120" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Дизайн-услуги</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4631,7 @@
       </c>
       <c r="D124" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Консультационные услуги</t>
         </is>
       </c>
     </row>
@@ -4441,6 +4692,1303 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Все статьи расходов по счёту 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Полная расшифровка блока «Расходы» основного листа, без сворачивания</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Доля</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Блок</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Медицинские — итого</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>56439832.64999999</v>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Гонорары ИП хирургов</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>39819623</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0.5705403161180821</v>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Импланты</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>4728500</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0.06775051297608596</v>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Медицинские материалы</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>3298432.06</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0.04726032866274039</v>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ИП Завиркин А.В.</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>2887658</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0.0413747088504808</v>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Расходка</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>2250790.16</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>0.03224959034398363</v>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Лекарства</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>827352.65</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>0.01185440762390274</v>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ИП Чугуевская (ЗП Заведягин ОН)</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>570005</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>0.008167099745994265</v>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Медоборудование и расходники</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>515528</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>0.007386546780910573</v>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Питание</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>376950</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>0.005400984639174285</v>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Белье</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>345200</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>0.004946066845584197</v>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Аренда Inmode</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>0.003008905091461997</v>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Кровь</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>181735.9</v>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>0.00260393368957823</v>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Медоборудование</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>173834.16</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>0.002490716614733426</v>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Анализы</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="n">
+        <v>102102</v>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>0.001462929655468823</v>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Бланки, мед.журналы, мед.книжки</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>63600</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>0.0009112683991284906</v>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Вывоз ТКО и мед отходов</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>52136.72</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>0.0007470211536196597</v>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Утилизация медотходов</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>23625</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>0.0003385018227894747</v>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Наркотики</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>12760</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>0.0001828268046050242</v>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>медицинские</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Управленческие — итого</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>13352996.84</v>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Урегулирование досудебного спора</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>4692500</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <v>0.06723470067469248</v>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Маркетинговые услуги</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>2505800</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <v>0.0359034018008832</v>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Аренда Самокатная 1 стр1</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>0.01654897800304098</v>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ремонт</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>516000</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <v>0.007393309653306621</v>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Обслуживание 1СУправление</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>441570</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>0.006326867720175591</v>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Фото видео</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>337440</v>
+      </c>
+      <c r="D30" s="28" t="n">
+        <v>0.004834880638394935</v>
+      </c>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Услуги юриста</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D31" s="28" t="n">
+        <v>0.004728279429440281</v>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Складской учет</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>320000</v>
+      </c>
+      <c r="D32" s="28" t="n">
+        <v>0.004584998234608758</v>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ПО и IT-сервисы</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>279349.86</v>
+      </c>
+      <c r="D33" s="28" t="n">
+        <v>0.004002558171681886</v>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Битрикс 24</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>264850</v>
+      </c>
+      <c r="D34" s="28" t="n">
+        <v>0.003794802445112904</v>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Сайт</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>254000</v>
+      </c>
+      <c r="D35" s="28" t="n">
+        <v>0.003639342348720701</v>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    IT услуги</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>247935.06</v>
+      </c>
+      <c r="D36" s="28" t="n">
+        <v>0.003552443163742551</v>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Реклама</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n">
+        <v>227800</v>
+      </c>
+      <c r="D37" s="28" t="n">
+        <v>0.003263945618262109</v>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Светильники и оборудование</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>179400</v>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>0.002570464635277535</v>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Услуги инженера</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="n">
+        <v>159575</v>
+      </c>
+      <c r="D39" s="28" t="n">
+        <v>0.002286409666524039</v>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Канц и хоз расходы</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>157671.72</v>
+      </c>
+      <c r="D40" s="28" t="n">
+        <v>0.002259139243274145</v>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Сервис речевой аналитики</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n">
+        <v>152250</v>
+      </c>
+      <c r="D41" s="28" t="n">
+        <v>0.002181456191309948</v>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Общехозяйственные</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>137116</v>
+      </c>
+      <c r="D42" s="28" t="n">
+        <v>0.00196461443105192</v>
+      </c>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Косметология</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>114858</v>
+      </c>
+      <c r="D43" s="28" t="n">
+        <v>0.001645699147595914</v>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Такси</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D44" s="28" t="n">
+        <v>0.001432811948315237</v>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Внедрение финансового учёта</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D45" s="28" t="n">
+        <v>0.001217890156067951</v>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Краснодар</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>81075</v>
+      </c>
+      <c r="D46" s="28" t="n">
+        <v>0.001161652287096578</v>
+      </c>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Хоз расходы</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>77247</v>
+      </c>
+      <c r="D47" s="28" t="n">
+        <v>0.001106804245715071</v>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Связь</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>53760</v>
+      </c>
+      <c r="D48" s="28" t="n">
+        <v>0.0007702797034142713</v>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Кофе</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>48301.44</v>
+      </c>
+      <c r="D49" s="28" t="n">
+        <v>0.0006920688035283151</v>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Цветы</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>0.0005731247793260947</v>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Программное обнспечение</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>39200</v>
+      </c>
+      <c r="D51" s="28" t="n">
+        <v>0.0005616622837395727</v>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Средства гигиены</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="n">
+        <v>37568</v>
+      </c>
+      <c r="D52" s="28" t="n">
+        <v>0.0005382787927430681</v>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Прочие управленческие</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="n">
+        <v>35920.61</v>
+      </c>
+      <c r="D53" s="28" t="n">
+        <v>0.0005146747919877177</v>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Капвложения и работы</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="n">
+        <v>29800</v>
+      </c>
+      <c r="D54" s="28" t="n">
+        <v>0.0004269779605979405</v>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Подбор персонала</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>27629</v>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>0.0003958716132000168</v>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Охрана</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="n">
+        <v>26600</v>
+      </c>
+      <c r="D56" s="28" t="n">
+        <v>0.0003811279782518529</v>
+      </c>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Мебель, инвентарь</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="n">
+        <v>22130</v>
+      </c>
+      <c r="D57" s="28" t="n">
+        <v>0.0003170812841621619</v>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Вода</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D58" s="28" t="n">
+        <v>0.0002865623896630474</v>
+      </c>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Техподдержка ККТ</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>17900</v>
+      </c>
+      <c r="D59" s="28" t="n">
+        <v>0.0002564733387484274</v>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Электрооборудование</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>17740</v>
+      </c>
+      <c r="D60" s="28" t="n">
+        <v>0.000254180839631123</v>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Дизайн-услуги</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>17060</v>
+      </c>
+      <c r="D61" s="28" t="n">
+        <v>0.0002444377183825794</v>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Интернет</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>16235.15</v>
+      </c>
+      <c r="D62" s="28" t="n">
+        <v>0.0002326191690269011</v>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Расходник</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>15120</v>
+      </c>
+      <c r="D63" s="28" t="n">
+        <v>0.0002166411665852638</v>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Аренда кофемашины</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D64" s="28" t="n">
+        <v>0.0002149217922472855</v>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Обучение персонала</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>10900</v>
+      </c>
+      <c r="D65" s="28" t="n">
+        <v>0.0001561765023663608</v>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Общехоз.расходы прочие</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D66" s="28" t="n">
+        <v>0.0001432811948315237</v>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ПроДокторов</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D67" s="28" t="n">
+        <v>0.0001432811948315237</v>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Доставка</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="n">
+        <v>7495</v>
+      </c>
+      <c r="D68" s="28" t="n">
+        <v>0.000107389255526227</v>
+      </c>
+      <c r="E68" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ТО СКУД, пожарной сигнализации</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D69" s="28" t="n">
+        <v>0.0001002968363820666</v>
+      </c>
+      <c r="E69" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Оргтехника</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>5100</v>
+      </c>
+      <c r="D70" s="28" t="n">
+        <v>7.307340936407707e-05</v>
+      </c>
+      <c r="E70" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Обслуживание аквариума</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D71" s="28" t="n">
+        <v>7.164059741576184e-05</v>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D72" s="28" t="n">
+        <v>1.57609314314676e-05</v>
+      </c>
+      <c r="E72" s="27" t="inlineStr">
+        <is>
+          <t>управленческие</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО СЧЁТУ 60</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="n">
+        <v>69792829.48999999</v>
+      </c>
+      <c r="D73" s="13" t="n"/>
+      <c r="E73" s="13" t="n"/>
+      <c r="F73" s="13" t="n"/>
+      <c r="G73" s="13" t="n"/>
+      <c r="H73" s="13" t="n"/>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>совпадает со строкой «Поставщики и подрядчики» основного листа</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -174,11 +174,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I128"/>
+  <dimension ref="B1:I160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1697,32 +1697,30 @@
       <c r="I68" s="8" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи, 4 шт</t>
-        </is>
-      </c>
-      <c r="C69" s="23" t="n">
-        <v>152121.72</v>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Бланки, мед.журналы, мед.книжки</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>63600</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>полный список — лист «Статьи расходов»</t>
-        </is>
-      </c>
+      <c r="I69" s="8" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="n"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Вывоз ТКО и мед отходов</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>52136.72</v>
+      </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
@@ -1733,11 +1731,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
+          <t xml:space="preserve">            Утилизация медотходов</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>4692500</v>
+        <v>23625</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1749,11 +1747,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Наркотики</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>2505800</v>
+        <v>12760</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1763,14 +1761,12 @@
       <c r="I72" s="8" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="n">
-        <v>1155000</v>
-      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
@@ -1781,11 +1777,11 @@
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>516000</v>
+        <v>4692500</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
@@ -1797,11 +1793,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>441570</v>
+        <v>2505800</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1813,11 +1809,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>337440</v>
+        <v>1155000</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1829,11 +1825,11 @@
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>330000</v>
+        <v>516000</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
@@ -1845,11 +1841,11 @@
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>320000</v>
+        <v>441570</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
@@ -1861,11 +1857,11 @@
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ПО и IT-сервисы</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>279349.86</v>
+        <v>337440</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
@@ -1877,11 +1873,11 @@
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Битрикс 24</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C80" s="7" t="n">
-        <v>264850</v>
+        <v>330000</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
@@ -1893,11 +1889,11 @@
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Сайт</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>254000</v>
+        <v>320000</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
@@ -1909,11 +1905,11 @@
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            IT услуги</t>
+          <t xml:space="preserve">            ПО и IT-сервисы</t>
         </is>
       </c>
       <c r="C82" s="7" t="n">
-        <v>247935.06</v>
+        <v>279349.86</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
@@ -1925,11 +1921,11 @@
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Реклама</t>
+          <t xml:space="preserve">            Битрикс 24</t>
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>227800</v>
+        <v>264850</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
@@ -1941,11 +1937,11 @@
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Светильники и оборудование</t>
+          <t xml:space="preserve">            Сайт</t>
         </is>
       </c>
       <c r="C84" s="7" t="n">
-        <v>179400</v>
+        <v>254000</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
@@ -1957,11 +1953,11 @@
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги инженера</t>
+          <t xml:space="preserve">            IT услуги</t>
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>159575</v>
+        <v>247935.06</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
@@ -1973,11 +1969,11 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Канц и хоз расходы</t>
+          <t xml:space="preserve">            Реклама</t>
         </is>
       </c>
       <c r="C86" s="7" t="n">
-        <v>157671.72</v>
+        <v>227800</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
@@ -1989,11 +1985,11 @@
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Сервис речевой аналитики</t>
+          <t xml:space="preserve">            Светильники и оборудование</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>152250</v>
+        <v>179400</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
@@ -2005,11 +2001,11 @@
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Общехозяйственные</t>
+          <t xml:space="preserve">            Услуги инженера</t>
         </is>
       </c>
       <c r="C88" s="7" t="n">
-        <v>137116</v>
+        <v>159575</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
@@ -2021,11 +2017,11 @@
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Косметология</t>
+          <t xml:space="preserve">            Канц и хоз расходы</t>
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>114858</v>
+        <v>157671.72</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
@@ -2037,11 +2033,11 @@
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Такси</t>
+          <t xml:space="preserve">            Сервис речевой аналитики</t>
         </is>
       </c>
       <c r="C90" s="7" t="n">
-        <v>100000</v>
+        <v>152250</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
@@ -2051,182 +2047,144 @@
       <c r="I90" s="8" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            прочие статьи, 28 шт</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="n">
-        <v>779881.2000000001</v>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Общехозяйственные</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>137116</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
-      <c r="I91" s="10" t="inlineStr">
-        <is>
-          <t>полный список — лист «Статьи расходов»</t>
-        </is>
-      </c>
+      <c r="I91" s="8" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ</t>
-        </is>
-      </c>
-      <c r="C92" s="15">
-        <f>SUM(C47:C53)</f>
-        <v/>
-      </c>
-      <c r="D92" s="15">
-        <f>SUM(D47:D53)</f>
-        <v/>
-      </c>
-      <c r="E92" s="15">
-        <f>SUM(E47:E53)</f>
-        <v/>
-      </c>
-      <c r="F92" s="16" t="n"/>
-      <c r="G92" s="16" t="n"/>
-      <c r="H92" s="16" t="n"/>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
-        </is>
-      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Косметология</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>114858</v>
+      </c>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="8" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="19" t="inlineStr">
-        <is>
-          <t>Справочно: ремонт за счёт кредитной линии</t>
-        </is>
-      </c>
-      <c r="C93" s="20" t="n">
-        <v>11000000</v>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Такси</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>100000</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="n"/>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
-        </is>
-      </c>
+      <c r="I93" s="8" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="19" t="inlineStr">
-        <is>
-          <t>Справочно: из них личные расходы врачей</t>
-        </is>
-      </c>
-      <c r="C94" s="20" t="n">
-        <v>1658023.69</v>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Внедрение финансового учёта</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>85000</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
       <c r="H94" s="8" t="n"/>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>пополам не делятся, отнесены каждому свои — см. шаг 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>методика 50/50</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="26" customHeight="1">
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Шаг</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Маланичев</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Погосян</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>Как считается</t>
-        </is>
-      </c>
+      <c r="I94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Краснодар</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>81075</v>
+      </c>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Хоз расходы</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>77247</v>
+      </c>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Связь</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>53760</v>
+      </c>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>1. Личная выручка (свои операции)</t>
-        </is>
-      </c>
-      <c r="C98" s="7">
-        <f>D98+E98</f>
-        <v/>
-      </c>
-      <c r="D98" s="7">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="E98" s="7">
-        <f>E35</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Кофе</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>48301.44</v>
+      </c>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
+      <c r="I98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>2. Половина выручки других хирургов</t>
-        </is>
-      </c>
-      <c r="C99" s="7">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="D99" s="7">
-        <f>F35/2</f>
-        <v/>
-      </c>
-      <c r="E99" s="7">
-        <f>F35/2</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Цветы</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="n"/>
@@ -2235,21 +2193,14 @@
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
-        </is>
-      </c>
-      <c r="C100" s="7">
-        <f>H35</f>
-        <v/>
-      </c>
-      <c r="D100" s="7">
-        <f>H35/2</f>
-        <v/>
-      </c>
-      <c r="E100" s="7">
-        <f>H35/2</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Программное обнспечение</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>39200</v>
+      </c>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
@@ -2258,21 +2209,14 @@
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
-        </is>
-      </c>
-      <c r="C101" s="7">
-        <f>G35</f>
-        <v/>
-      </c>
-      <c r="D101" s="7">
-        <f>G35/2</f>
-        <v/>
-      </c>
-      <c r="E101" s="7">
-        <f>G35/2</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Средства гигиены</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>37568</v>
+      </c>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
@@ -2281,202 +2225,158 @@
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
+          <t xml:space="preserve">            Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>396337.24</v>
-      </c>
-      <c r="D102" s="7">
-        <f>C102/2</f>
-        <v/>
-      </c>
-      <c r="E102" s="7">
-        <f>C102/2</f>
-        <v/>
-      </c>
+        <v>35920.61</v>
+      </c>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I102" s="8" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="24" t="inlineStr">
-        <is>
-          <t>6. Минус ½ общих расходов</t>
-        </is>
-      </c>
-      <c r="C103" s="25">
-        <f>-(C92-C94)</f>
-        <v/>
-      </c>
-      <c r="D103" s="25">
-        <f>-(D92-C94/2)</f>
-        <v/>
-      </c>
-      <c r="E103" s="25">
-        <f>-(E92-C94/2)</f>
-        <v/>
-      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Капвложения и работы</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>29800</v>
+      </c>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>итог блока «Расходы» без личных, пополам</t>
-        </is>
-      </c>
+      <c r="I103" s="8" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="24" t="inlineStr">
-        <is>
-          <t>7. Минус личные расходы (каждый свои)</t>
-        </is>
-      </c>
-      <c r="C104" s="25" t="n">
-        <v>-1658023.69</v>
-      </c>
-      <c r="D104" s="25" t="n">
-        <v>-170861.64</v>
-      </c>
-      <c r="E104" s="25" t="n">
-        <v>-1487162.05</v>
-      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Подбор персонала</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>27629</v>
+      </c>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>заказано лично под врача, пополам не делится</t>
-        </is>
-      </c>
+      <c r="I104" s="8" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Анализы</t>
-        </is>
-      </c>
-      <c r="C105" s="23" t="n">
-        <v>-42868</v>
-      </c>
-      <c r="D105" s="23" t="n">
-        <v>-30620</v>
-      </c>
-      <c r="E105" s="23" t="n">
-        <v>-12248</v>
-      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Охрана</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>26600</v>
+      </c>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
       <c r="I105" s="8" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Материалы за операции</t>
-        </is>
-      </c>
-      <c r="C106" s="23" t="n">
-        <v>-1615155.69</v>
-      </c>
-      <c r="D106" s="23" t="n">
-        <v>-140241.64</v>
-      </c>
-      <c r="E106" s="23" t="n">
-        <v>-1474914.05</v>
-      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Мебель, инвентарь</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>22130</v>
+      </c>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
       <c r="I106" s="8" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t>ДОХОД ЗА МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="C107" s="15">
-        <f>SUM(C98:C104)</f>
-        <v/>
-      </c>
-      <c r="D107" s="15">
-        <f>SUM(D98:D104)</f>
-        <v/>
-      </c>
-      <c r="E107" s="15">
-        <f>SUM(E98:E104)</f>
-        <v/>
-      </c>
-      <c r="F107" s="16" t="n"/>
-      <c r="G107" s="16" t="n"/>
-      <c r="H107" s="16" t="n"/>
-      <c r="I107" s="16" t="n"/>
-    </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="4" t="n"/>
-      <c r="G109" s="4" t="n"/>
-      <c r="H109" s="4" t="n"/>
-      <c r="I109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110" ht="26" customHeight="1">
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>Маланичев</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>Погосян</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Вода</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Техподдержка ККТ</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>17900</v>
+      </c>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="8" t="n"/>
+      <c r="G108" s="8" t="n"/>
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Электрооборудование</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>17740</v>
+      </c>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="8" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Дизайн-услуги</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>17060</v>
+      </c>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="8" t="n"/>
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="8" t="n"/>
     </row>
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C111" s="7">
-        <f>C107</f>
-        <v/>
-      </c>
-      <c r="D111" s="7">
-        <f>D107</f>
-        <v/>
-      </c>
-      <c r="E111" s="7">
-        <f>E107</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">            Интернет</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>16235.15</v>
+      </c>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="n"/>
@@ -2485,155 +2385,139 @@
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
-        </is>
-      </c>
-      <c r="C112" s="7">
-        <f>D112+E112</f>
-        <v/>
-      </c>
-      <c r="D112" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>45275972.21</v>
-      </c>
+          <t xml:space="preserve">            Расходник</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>15120</v>
+      </c>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
       <c r="F112" s="8" t="n"/>
       <c r="G112" s="8" t="n"/>
       <c r="H112" s="8" t="n"/>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I112" s="8" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C113" s="25">
-        <f>D113+E113</f>
-        <v/>
-      </c>
-      <c r="D113" s="25" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E113" s="25" t="n">
-        <v>-5882353</v>
-      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Аренда кофемашины</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="n"/>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>начислено с НДФЛ</t>
-        </is>
-      </c>
+      <c r="I113" s="8" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
-        </is>
-      </c>
-      <c r="C114" s="15">
-        <f>SUM(C111:C113)</f>
-        <v/>
-      </c>
-      <c r="D114" s="15">
-        <f>SUM(D111:D113)</f>
-        <v/>
-      </c>
-      <c r="E114" s="15">
-        <f>SUM(E111:E113)</f>
-        <v/>
-      </c>
-      <c r="F114" s="16" t="n"/>
-      <c r="G114" s="16" t="n"/>
-      <c r="H114" s="16" t="n"/>
-      <c r="I114" s="16" t="n"/>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>6. СПРАВОЧНО</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="n"/>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="n"/>
-      <c r="I116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117" ht="26" customHeight="1">
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>Сумма</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Обучение персонала</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>10900</v>
+      </c>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="n"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Общехоз.расходы прочие</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="8" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ПроДокторов</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="8" t="n"/>
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="8" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Доставка</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>7495</v>
+      </c>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="8" t="n"/>
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на начало месяца</t>
+          <t xml:space="preserve">            ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
       <c r="C118" s="7" t="n">
-        <v>16545367</v>
+        <v>7000</v>
       </c>
       <c r="D118" s="8" t="n"/>
       <c r="E118" s="8" t="n"/>
       <c r="F118" s="8" t="n"/>
       <c r="G118" s="8" t="n"/>
       <c r="H118" s="8" t="n"/>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
-        </is>
-      </c>
+      <c r="I118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано за месяц</t>
+          <t xml:space="preserve">            Оргтехника</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>11000000</v>
+        <v>5100</v>
       </c>
       <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="8" t="n"/>
       <c r="G119" s="8" t="n"/>
       <c r="H119" s="8" t="n"/>
-      <c r="I119" s="10" t="inlineStr">
-        <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
-        </is>
-      </c>
+      <c r="I119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на конец месяца</t>
+          <t xml:space="preserve">            Обслуживание аквариума</t>
         </is>
       </c>
       <c r="C120" s="7" t="n">
-        <v>27545367</v>
+        <v>5000</v>
       </c>
       <c r="D120" s="8" t="n"/>
       <c r="E120" s="8" t="n"/>
@@ -2645,11 +2529,11 @@
     <row r="121">
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t xml:space="preserve">            Консультационные услуги</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>30000000</v>
+        <v>1100</v>
       </c>
       <c r="D121" s="8" t="n"/>
       <c r="E121" s="8" t="n"/>
@@ -2659,29 +2543,34 @@
       <c r="I121" s="8" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — свободный остаток</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="n">
-        <v>2454633</v>
-      </c>
-      <c r="D122" s="8" t="n"/>
-      <c r="E122" s="8" t="n"/>
-      <c r="F122" s="8" t="n"/>
-      <c r="G122" s="8" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="8" t="n"/>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ ЗА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="C122" s="15">
+        <f>SUM(C47:C53)</f>
+        <v/>
+      </c>
+      <c r="D122" s="16" t="n"/>
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="16" t="n"/>
+      <c r="G122" s="16" t="n"/>
+      <c r="H122" s="16" t="n"/>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>Проценты по кредиту, уплачено</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="n">
-        <v>204388.93</v>
+      <c r="B123" s="23" t="inlineStr">
+        <is>
+          <t>Минус личные расходы врачей</t>
+        </is>
+      </c>
+      <c r="C123" s="24" t="n">
+        <v>-1658023.69</v>
       </c>
       <c r="D123" s="8" t="n"/>
       <c r="E123" s="8" t="n"/>
@@ -2690,21 +2579,28 @@
       <c r="H123" s="8" t="n"/>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+          <t>заказано лично под врача — делить пополам нельзя</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>Проценты по депозитам за месяц</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="n">
-        <v>396337.24</v>
-      </c>
-      <c r="D124" s="8" t="n"/>
-      <c r="E124" s="8" t="n"/>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>ОБЩИЕ РАСХОДЫ (делятся 50/50)</t>
+        </is>
+      </c>
+      <c r="C124" s="21">
+        <f>C122+C123</f>
+        <v/>
+      </c>
+      <c r="D124" s="21">
+        <f>C124/2</f>
+        <v/>
+      </c>
+      <c r="E124" s="21">
+        <f>C124/2</f>
+        <v/>
+      </c>
       <c r="F124" s="8" t="n"/>
       <c r="G124" s="8" t="n"/>
       <c r="H124" s="8" t="n"/>
@@ -2713,72 +2609,695 @@
     <row r="125">
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C125" s="7" t="n"/>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
+          <t>Личные расходы, каждому свои</t>
+        </is>
+      </c>
+      <c r="C125" s="7">
+        <f>D125+E125</f>
+        <v/>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>170861.64</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>1487162.05</v>
+      </c>
       <c r="F125" s="8" t="n"/>
       <c r="G125" s="8" t="n"/>
       <c r="H125" s="8" t="n"/>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>не проставлен</t>
+          <t>из листа «Расходы врачей» и «Финансового результата»</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="n">
-        <v>373487.16</v>
-      </c>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Анализы</t>
+        </is>
+      </c>
+      <c r="C126" s="25">
+        <f>D126+E126</f>
+        <v/>
+      </c>
+      <c r="D126" s="25" t="n">
+        <v>30620</v>
+      </c>
+      <c r="E126" s="25" t="n">
+        <v>12248</v>
+      </c>
       <c r="F126" s="8" t="n"/>
       <c r="G126" s="8" t="n"/>
       <c r="H126" s="8" t="n"/>
       <c r="I126" s="8" t="n"/>
     </row>
     <row r="127">
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
-        </is>
-      </c>
-      <c r="C127" s="7" t="n">
-        <v>3284000</v>
-      </c>
-      <c r="D127" s="8" t="n"/>
-      <c r="E127" s="8" t="n"/>
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Материалы за операции</t>
+        </is>
+      </c>
+      <c r="C127" s="25">
+        <f>D127+E127</f>
+        <v/>
+      </c>
+      <c r="D127" s="25" t="n">
+        <v>140241.64</v>
+      </c>
+      <c r="E127" s="25" t="n">
+        <v>1474914.05</v>
+      </c>
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="8" t="n"/>
       <c r="H127" s="8" t="n"/>
-      <c r="I127" s="10" t="inlineStr">
+      <c r="I127" s="8" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>ДОЛЯ РАСХОДОВ КАЖДОГО</t>
+        </is>
+      </c>
+      <c r="C128" s="15">
+        <f>D128+E128</f>
+        <v/>
+      </c>
+      <c r="D128" s="15">
+        <f>D124+D125</f>
+        <v/>
+      </c>
+      <c r="E128" s="15">
+        <f>E124+E125</f>
+        <v/>
+      </c>
+      <c r="F128" s="16" t="n"/>
+      <c r="G128" s="16" t="n"/>
+      <c r="H128" s="16" t="n"/>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>общие пополам плюс свои личные</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>Справочно: ремонт за счёт кредитной линии</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="8" t="n"/>
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="n"/>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>методика 50/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="26" customHeight="1">
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Маланичев</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Погосян</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Как считается</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>1. Личная выручка (свои операции)</t>
+        </is>
+      </c>
+      <c r="C133" s="7">
+        <f>D133+E133</f>
+        <v/>
+      </c>
+      <c r="D133" s="7">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E133" s="7">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F133" s="8" t="n"/>
+      <c r="G133" s="8" t="n"/>
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>2. Половина выручки других хирургов</t>
+        </is>
+      </c>
+      <c r="C134" s="7">
+        <f>F35</f>
+        <v/>
+      </c>
+      <c r="D134" s="7">
+        <f>F35/2</f>
+        <v/>
+      </c>
+      <c r="E134" s="7">
+        <f>F35/2</f>
+        <v/>
+      </c>
+      <c r="F134" s="8" t="n"/>
+      <c r="G134" s="8" t="n"/>
+      <c r="H134" s="8" t="n"/>
+      <c r="I134" s="8" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>3. Половина выручки косметологии</t>
+        </is>
+      </c>
+      <c r="C135" s="7">
+        <f>H35</f>
+        <v/>
+      </c>
+      <c r="D135" s="7">
+        <f>H35/2</f>
+        <v/>
+      </c>
+      <c r="E135" s="7">
+        <f>H35/2</f>
+        <v/>
+      </c>
+      <c r="F135" s="8" t="n"/>
+      <c r="G135" s="8" t="n"/>
+      <c r="H135" s="8" t="n"/>
+      <c r="I135" s="8" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C136" s="7">
+        <f>G35</f>
+        <v/>
+      </c>
+      <c r="D136" s="7">
+        <f>G35/2</f>
+        <v/>
+      </c>
+      <c r="E136" s="7">
+        <f>G35/2</f>
+        <v/>
+      </c>
+      <c r="F136" s="8" t="n"/>
+      <c r="G136" s="8" t="n"/>
+      <c r="H136" s="8" t="n"/>
+      <c r="I136" s="8" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D137" s="7">
+        <f>C137/2</f>
+        <v/>
+      </c>
+      <c r="E137" s="7">
+        <f>C137/2</f>
+        <v/>
+      </c>
+      <c r="F137" s="8" t="n"/>
+      <c r="G137" s="8" t="n"/>
+      <c r="H137" s="8" t="n"/>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C138" s="24">
+        <f>-C128</f>
+        <v/>
+      </c>
+      <c r="D138" s="24">
+        <f>-D128</f>
+        <v/>
+      </c>
+      <c r="E138" s="24">
+        <f>-E128</f>
+        <v/>
+      </c>
+      <c r="F138" s="8" t="n"/>
+      <c r="G138" s="8" t="n"/>
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>строка «Доля расходов каждого» блока 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>ДОХОД ЗА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="C139" s="15">
+        <f>SUM(C133:C138)</f>
+        <v/>
+      </c>
+      <c r="D139" s="15">
+        <f>SUM(D133:D138)</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>SUM(E133:E138)</f>
+        <v/>
+      </c>
+      <c r="F139" s="16" t="n"/>
+      <c r="G139" s="16" t="n"/>
+      <c r="H139" s="16" t="n"/>
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142" ht="26" customHeight="1">
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Маланичев</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Погосян</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Доход за месяц</t>
+        </is>
+      </c>
+      <c r="C143" s="7">
+        <f>C139</f>
+        <v/>
+      </c>
+      <c r="D143" s="7">
+        <f>D139</f>
+        <v/>
+      </c>
+      <c r="E143" s="7">
+        <f>E139</f>
+        <v/>
+      </c>
+      <c r="F143" s="8" t="n"/>
+      <c r="G143" s="8" t="n"/>
+      <c r="H143" s="8" t="n"/>
+      <c r="I143" s="8" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C144" s="7">
+        <f>D144+E144</f>
+        <v/>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>45275972.21</v>
+      </c>
+      <c r="F144" s="8" t="n"/>
+      <c r="G144" s="8" t="n"/>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="23" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C145" s="24">
+        <f>D145+E145</f>
+        <v/>
+      </c>
+      <c r="D145" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E145" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F145" s="8" t="n"/>
+      <c r="G145" s="8" t="n"/>
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>начислено с НДФЛ</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
+        </is>
+      </c>
+      <c r="C146" s="15">
+        <f>SUM(C143:C145)</f>
+        <v/>
+      </c>
+      <c r="D146" s="15">
+        <f>SUM(D143:D145)</f>
+        <v/>
+      </c>
+      <c r="E146" s="15">
+        <f>SUM(E143:E145)</f>
+        <v/>
+      </c>
+      <c r="F146" s="16" t="n"/>
+      <c r="G146" s="16" t="n"/>
+      <c r="H146" s="16" t="n"/>
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>6. СПРАВОЧНО</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="4" t="n"/>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149" ht="26" customHeight="1">
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — долг на начало месяца</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>16545367</v>
+      </c>
+      <c r="D150" s="8" t="n"/>
+      <c r="E150" s="8" t="n"/>
+      <c r="F150" s="8" t="n"/>
+      <c r="G150" s="8" t="n"/>
+      <c r="H150" s="8" t="n"/>
+      <c r="I150" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — выбрано за месяц</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="D151" s="8" t="n"/>
+      <c r="E151" s="8" t="n"/>
+      <c r="F151" s="8" t="n"/>
+      <c r="G151" s="8" t="n"/>
+      <c r="H151" s="8" t="n"/>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — долг на конец месяца</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="n">
+        <v>27545367</v>
+      </c>
+      <c r="D152" s="8" t="n"/>
+      <c r="E152" s="8" t="n"/>
+      <c r="F152" s="8" t="n"/>
+      <c r="G152" s="8" t="n"/>
+      <c r="H152" s="8" t="n"/>
+      <c r="I152" s="8" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — лимит</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+      <c r="F153" s="8" t="n"/>
+      <c r="G153" s="8" t="n"/>
+      <c r="H153" s="8" t="n"/>
+      <c r="I153" s="8" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>Кредитная линия — свободный остаток</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>2454633</v>
+      </c>
+      <c r="D154" s="8" t="n"/>
+      <c r="E154" s="8" t="n"/>
+      <c r="F154" s="8" t="n"/>
+      <c r="G154" s="8" t="n"/>
+      <c r="H154" s="8" t="n"/>
+      <c r="I154" s="8" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту, уплачено</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>204388.93</v>
+      </c>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="8" t="n"/>
+      <c r="F155" s="8" t="n"/>
+      <c r="G155" s="8" t="n"/>
+      <c r="H155" s="8" t="n"/>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D156" s="8" t="n"/>
+      <c r="E156" s="8" t="n"/>
+      <c r="F156" s="8" t="n"/>
+      <c r="G156" s="8" t="n"/>
+      <c r="H156" s="8" t="n"/>
+      <c r="I156" s="8" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="8" t="n"/>
+      <c r="F157" s="8" t="n"/>
+      <c r="G157" s="8" t="n"/>
+      <c r="H157" s="8" t="n"/>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Комиссия эквайринга</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D158" s="8" t="n"/>
+      <c r="E158" s="8" t="n"/>
+      <c r="F158" s="8" t="n"/>
+      <c r="G158" s="8" t="n"/>
+      <c r="H158" s="8" t="n"/>
+      <c r="I158" s="8" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>3284000</v>
+      </c>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="8" t="n"/>
+      <c r="F159" s="8" t="n"/>
+      <c r="G159" s="8" t="n"/>
+      <c r="H159" s="8" t="n"/>
+      <c r="I159" s="10" t="inlineStr">
         <is>
           <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" s="6" t="inlineStr">
+    <row r="160">
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>Авансы арендодателям на конец месяца</t>
         </is>
       </c>
-      <c r="C128" s="7" t="n">
+      <c r="C160" s="7" t="n">
         <v>31195343.31</v>
       </c>
-      <c r="D128" s="8" t="n"/>
-      <c r="E128" s="8" t="n"/>
-      <c r="F128" s="8" t="n"/>
-      <c r="G128" s="8" t="n"/>
-      <c r="H128" s="8" t="n"/>
-      <c r="I128" s="10" t="inlineStr">
+      <c r="D160" s="8" t="n"/>
+      <c r="E160" s="8" t="n"/>
+      <c r="F160" s="8" t="n"/>
+      <c r="G160" s="8" t="n"/>
+      <c r="H160" s="8" t="n"/>
+      <c r="I160" s="10" t="inlineStr">
         <is>
           <t>дебетовое сальдо счёта 60: Паритет (стр.12) работает июльскую предоплату, поэтому коммунальных платежей в августе нет</t>
         </is>
@@ -4136,7 +4655,7 @@
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Прочие управленческие</t>
+          <t>Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
     </row>
@@ -5606,7 +6125,7 @@
     <row r="53">
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Прочие управленческие</t>
+          <t xml:space="preserve">    Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
       <c r="C53" s="26" t="n">

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Расчёт" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Расходы по контрагентам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Статьи расходов" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Выручка по дням" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Сверка с банком" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Статьи расходов" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Выручка по дням" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5216,6 +5217,255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Почему выручка не равна деньгам на счёте</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Бухгалтерия считает по счёту 57 — это деньги, дошедшие до расчётного счёта. Выручка — то, что пробито в управленке. Базы разные, вот переход.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Откуда</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Поступило на р/с через счёт 57 (нетто)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>97353224.14</v>
+      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>153 496 343.14 с 57 на р/с минус 56 143 119.00 переводов между своими счетами</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        инкассация наличных</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>35370000</v>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>счёт 50 → 57</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        эквайринг зачислен</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>61983224.14</v>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>банк перечислил за вычетом комиссии</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>+ Комиссия эквайринга, удержана банком</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>373487.16</v>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>счёт 57 → 91: пробито больше, чем зачислено</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="9">
+        <f> Пробито по банку</f>
+        <v/>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>97726711.3</v>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>инкассация + эквайринг до комиссии</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>− Инкассация больше пробитой налички</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>-388100</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>сдали 35 370 000.00 при кассе 34 981 900.00 — вместе с остатком кассы с июля</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>− Эквайринг конца июля, зачисленный в августе</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>-36757.29999999702</v>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>по банку 62 356 711.30 против 62 319 954.00 по картам</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9">
+        <f> Поступления от пациентов за август</f>
+        <v/>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>97301854</v>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>до возвратов</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>− Возвраты пациентам</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>-360000</v>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>ушли с р/с напрямую через счёт 62, счёта 57 не касаются</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>ВЫРУЧКА В ОТЧЁТЕ</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>96941853.98999999</v>
+      </c>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>сходится до копейки</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6507,7 +6757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I160"/>
+  <dimension ref="B1:I161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1442,14 +1442,8 @@
       <c r="C53" s="21" t="n">
         <v>69792829.48999999</v>
       </c>
-      <c r="D53" s="21">
-        <f>C53/2</f>
-        <v/>
-      </c>
-      <c r="E53" s="21">
-        <f>C53/2</f>
-        <v/>
-      </c>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
@@ -2544,34 +2538,33 @@
       <c r="I121" s="8" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ ЗА МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="C122" s="15">
-        <f>SUM(C47:C53)</f>
-        <v/>
-      </c>
-      <c r="D122" s="16" t="n"/>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="16" t="n"/>
-      <c r="G122" s="16" t="n"/>
-      <c r="H122" s="16" t="n"/>
-      <c r="I122" s="17" t="inlineStr">
-        <is>
-          <t>строки «в том числе» в сумму не входят</t>
+      <c r="B122" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        − личные расходы Маланичева, они внутри счёта 60</t>
+        </is>
+      </c>
+      <c r="C122" s="24" t="n">
+        <v>-170861.64</v>
+      </c>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
+      <c r="G122" s="8" t="n"/>
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>заказано лично под врача — пополам не делится</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="23" t="inlineStr">
         <is>
-          <t>Минус личные расходы врачей</t>
+          <t xml:space="preserve">        − личные расходы Погосяна, они внутри счёта 60</t>
         </is>
       </c>
       <c r="C123" s="24" t="n">
-        <v>-1658023.69</v>
+        <v>-1487162.05</v>
       </c>
       <c r="D123" s="8" t="n"/>
       <c r="E123" s="8" t="n"/>
@@ -2580,18 +2573,18 @@
       <c r="H123" s="8" t="n"/>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>заказано лично под врача — делить пополам нельзя</t>
+          <t>заказано лично под врача — пополам не делится</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>ОБЩИЕ РАСХОДЫ (делятся 50/50)</t>
+          <t>Поставщики к делению пополам</t>
         </is>
       </c>
       <c r="C124" s="21">
-        <f>C122+C123</f>
+        <f>C53+C122+C123</f>
         <v/>
       </c>
       <c r="D124" s="21">
@@ -2608,55 +2601,61 @@
       <c r="I124" s="8" t="n"/>
     </row>
     <row r="125">
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>Личные расходы, каждому свои</t>
-        </is>
-      </c>
-      <c r="C125" s="7">
-        <f>D125+E125</f>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ К ДЕЛЕНИЮ ПОПОЛАМ</t>
+        </is>
+      </c>
+      <c r="C125" s="15">
+        <f>SUM(C47:C52)+C124</f>
         <v/>
       </c>
-      <c r="D125" s="7" t="n">
-        <v>170861.64</v>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>1487162.05</v>
-      </c>
-      <c r="F125" s="8" t="n"/>
-      <c r="G125" s="8" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>из листа «Расходы врачей» и «Финансового результата»</t>
+      <c r="D125" s="15">
+        <f>C125/2</f>
+        <v/>
+      </c>
+      <c r="E125" s="15">
+        <f>C125/2</f>
+        <v/>
+      </c>
+      <c r="F125" s="16" t="n"/>
+      <c r="G125" s="16" t="n"/>
+      <c r="H125" s="16" t="n"/>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>строки «в том числе» в сумму не входят</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Анализы</t>
-        </is>
-      </c>
-      <c r="C126" s="25">
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>+ Личные расходы, каждому свои</t>
+        </is>
+      </c>
+      <c r="C126" s="7">
         <f>D126+E126</f>
         <v/>
       </c>
-      <c r="D126" s="25" t="n">
-        <v>30620</v>
-      </c>
-      <c r="E126" s="25" t="n">
-        <v>12248</v>
+      <c r="D126" s="7" t="n">
+        <v>170861.64</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>1487162.05</v>
       </c>
       <c r="F126" s="8" t="n"/>
       <c r="G126" s="8" t="n"/>
       <c r="H126" s="8" t="n"/>
-      <c r="I126" s="8" t="n"/>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>те самые суммы, что вычтены из счёта 60 выше</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="B127" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Материалы за операции</t>
+          <t xml:space="preserve">        Анализы</t>
         </is>
       </c>
       <c r="C127" s="25">
@@ -2664,10 +2663,10 @@
         <v/>
       </c>
       <c r="D127" s="25" t="n">
-        <v>140241.64</v>
+        <v>30620</v>
       </c>
       <c r="E127" s="25" t="n">
-        <v>1474914.05</v>
+        <v>12248</v>
       </c>
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="8" t="n"/>
@@ -2675,163 +2674,161 @@
       <c r="I127" s="8" t="n"/>
     </row>
     <row r="128">
-      <c r="B128" s="14" t="inlineStr">
-        <is>
-          <t>ДОЛЯ РАСХОДОВ КАЖДОГО</t>
-        </is>
-      </c>
-      <c r="C128" s="15">
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Материалы за операции</t>
+        </is>
+      </c>
+      <c r="C128" s="25">
         <f>D128+E128</f>
         <v/>
       </c>
-      <c r="D128" s="15">
-        <f>D124+D125</f>
+      <c r="D128" s="25" t="n">
+        <v>140241.64</v>
+      </c>
+      <c r="E128" s="25" t="n">
+        <v>1474914.05</v>
+      </c>
+      <c r="F128" s="8" t="n"/>
+      <c r="G128" s="8" t="n"/>
+      <c r="H128" s="8" t="n"/>
+      <c r="I128" s="8" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>ДОЛЯ РАСХОДОВ КАЖДОГО</t>
+        </is>
+      </c>
+      <c r="C129" s="15">
+        <f>D129+E129</f>
         <v/>
       </c>
-      <c r="E128" s="15">
-        <f>E124+E125</f>
+      <c r="D129" s="15">
+        <f>D125+D126</f>
         <v/>
       </c>
-      <c r="F128" s="16" t="n"/>
-      <c r="G128" s="16" t="n"/>
-      <c r="H128" s="16" t="n"/>
-      <c r="I128" s="17" t="inlineStr">
-        <is>
-          <t>общие пополам плюс свои личные</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="19" t="inlineStr">
+      <c r="E129" s="15">
+        <f>E125+E126</f>
+        <v/>
+      </c>
+      <c r="F129" s="16" t="n"/>
+      <c r="G129" s="16" t="n"/>
+      <c r="H129" s="16" t="n"/>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>к делению пополам плюс свои личные</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="19" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C129" s="20" t="n">
+      <c r="C130" s="20" t="n">
         <v>11000000</v>
       </c>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-      <c r="F129" s="8" t="n"/>
-      <c r="G129" s="8" t="n"/>
-      <c r="H129" s="8" t="n"/>
-      <c r="I129" s="10" t="inlineStr">
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="8" t="n"/>
+      <c r="H130" s="8" t="n"/>
+      <c r="I130" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="B131" s="3" t="inlineStr">
+    <row r="132" ht="22" customHeight="1">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C131" s="4" t="n"/>
-      <c r="D131" s="4" t="n"/>
-      <c r="E131" s="4" t="n"/>
-      <c r="F131" s="4" t="n"/>
-      <c r="G131" s="4" t="n"/>
-      <c r="H131" s="4" t="n"/>
-      <c r="I131" s="4" t="inlineStr">
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="26" customHeight="1">
-      <c r="B132" s="5" t="inlineStr">
+    <row r="133" ht="26" customHeight="1">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="B133" s="6" t="inlineStr">
+    <row r="134">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
-      <c r="C133" s="7">
-        <f>D133+E133</f>
+      <c r="C134" s="7">
+        <f>D134+E134</f>
         <v/>
       </c>
-      <c r="D133" s="7">
+      <c r="D134" s="7">
         <f>D35</f>
         <v/>
       </c>
-      <c r="E133" s="7">
+      <c r="E134" s="7">
         <f>E35</f>
-        <v/>
-      </c>
-      <c r="F133" s="8" t="n"/>
-      <c r="G133" s="8" t="n"/>
-      <c r="H133" s="8" t="n"/>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>2. Половина выручки других хирургов</t>
-        </is>
-      </c>
-      <c r="C134" s="7">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="D134" s="7">
-        <f>F35/2</f>
-        <v/>
-      </c>
-      <c r="E134" s="7">
-        <f>F35/2</f>
         <v/>
       </c>
       <c r="F134" s="8" t="n"/>
       <c r="G134" s="8" t="n"/>
       <c r="H134" s="8" t="n"/>
-      <c r="I134" s="8" t="n"/>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C135" s="7">
-        <f>H35</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>H35/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="E135" s="7">
-        <f>H35/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="F135" s="8" t="n"/>
@@ -2842,19 +2839,19 @@
     <row r="136">
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C136" s="7">
-        <f>G35</f>
+        <f>H35</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>G35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="E136" s="7">
-        <f>G35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="F136" s="8" t="n"/>
@@ -2865,45 +2862,41 @@
     <row r="137">
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="n">
-        <v>396337.24</v>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C137" s="7">
+        <f>G35</f>
+        <v/>
       </c>
       <c r="D137" s="7">
-        <f>C137/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="E137" s="7">
-        <f>C137/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="F137" s="8" t="n"/>
       <c r="G137" s="8" t="n"/>
       <c r="H137" s="8" t="n"/>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I137" s="8" t="n"/>
     </row>
     <row r="138">
-      <c r="B138" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C138" s="24">
-        <f>-C128</f>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D138" s="7">
+        <f>C138/2</f>
         <v/>
       </c>
-      <c r="D138" s="24">
-        <f>-D128</f>
-        <v/>
-      </c>
-      <c r="E138" s="24">
-        <f>-E128</f>
+      <c r="E138" s="7">
+        <f>C138/2</f>
         <v/>
       </c>
       <c r="F138" s="8" t="n"/>
@@ -2911,229 +2904,236 @@
       <c r="H138" s="8" t="n"/>
       <c r="I138" s="10" t="inlineStr">
         <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="23" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C139" s="24">
+        <f>-C129</f>
+        <v/>
+      </c>
+      <c r="D139" s="24">
+        <f>-D129</f>
+        <v/>
+      </c>
+      <c r="E139" s="24">
+        <f>-E129</f>
+        <v/>
+      </c>
+      <c r="F139" s="8" t="n"/>
+      <c r="G139" s="8" t="n"/>
+      <c r="H139" s="8" t="n"/>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
           <t>строка «Доля расходов каждого» блока 3</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" s="14" t="inlineStr">
+    <row r="140">
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C139" s="15">
-        <f>SUM(C133:C138)</f>
+      <c r="C140" s="15">
+        <f>SUM(C134:C139)</f>
         <v/>
       </c>
-      <c r="D139" s="15">
-        <f>SUM(D133:D138)</f>
+      <c r="D140" s="15">
+        <f>SUM(D134:D139)</f>
         <v/>
       </c>
-      <c r="E139" s="15">
-        <f>SUM(E133:E138)</f>
+      <c r="E140" s="15">
+        <f>SUM(E134:E139)</f>
         <v/>
       </c>
-      <c r="F139" s="16" t="n"/>
-      <c r="G139" s="16" t="n"/>
-      <c r="H139" s="16" t="n"/>
-      <c r="I139" s="16" t="n"/>
-    </row>
-    <row r="141" ht="22" customHeight="1">
-      <c r="B141" s="3" t="inlineStr">
+      <c r="F140" s="16" t="n"/>
+      <c r="G140" s="16" t="n"/>
+      <c r="H140" s="16" t="n"/>
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C141" s="4" t="n"/>
-      <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="4" t="n"/>
-      <c r="H141" s="4" t="n"/>
-      <c r="I141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142" ht="26" customHeight="1">
-      <c r="B142" s="5" t="inlineStr">
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143" ht="26" customHeight="1">
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I142" s="5" t="inlineStr">
+      <c r="I143" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C143" s="7">
-        <f>C139</f>
-        <v/>
-      </c>
-      <c r="D143" s="7">
-        <f>D139</f>
-        <v/>
-      </c>
-      <c r="E143" s="7">
-        <f>E139</f>
-        <v/>
-      </c>
-      <c r="F143" s="8" t="n"/>
-      <c r="G143" s="8" t="n"/>
-      <c r="H143" s="8" t="n"/>
-      <c r="I143" s="8" t="n"/>
     </row>
     <row r="144">
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
+          <t>Доход за месяц</t>
         </is>
       </c>
       <c r="C144" s="7">
-        <f>D144+E144</f>
+        <f>C140</f>
         <v/>
       </c>
-      <c r="D144" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E144" s="7" t="n">
-        <v>45275972.21</v>
+      <c r="D144" s="7">
+        <f>D140</f>
+        <v/>
+      </c>
+      <c r="E144" s="7">
+        <f>E140</f>
+        <v/>
       </c>
       <c r="F144" s="8" t="n"/>
       <c r="G144" s="8" t="n"/>
       <c r="H144" s="8" t="n"/>
-      <c r="I144" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I144" s="8" t="n"/>
     </row>
     <row r="145">
-      <c r="B145" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C145" s="24">
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C145" s="7">
         <f>D145+E145</f>
         <v/>
       </c>
-      <c r="D145" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E145" s="24" t="n">
-        <v>-5882353</v>
+      <c r="D145" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F145" s="8" t="n"/>
       <c r="G145" s="8" t="n"/>
       <c r="H145" s="8" t="n"/>
       <c r="I145" s="10" t="inlineStr">
         <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="23" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C146" s="24">
+        <f>D146+E146</f>
+        <v/>
+      </c>
+      <c r="D146" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E146" s="24" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F146" s="8" t="n"/>
+      <c r="G146" s="8" t="n"/>
+      <c r="H146" s="8" t="n"/>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="B146" s="14" t="inlineStr">
+    <row r="147">
+      <c r="B147" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C146" s="15">
-        <f>SUM(C143:C145)</f>
+      <c r="C147" s="15">
+        <f>SUM(C144:C146)</f>
         <v/>
       </c>
-      <c r="D146" s="15">
-        <f>SUM(D143:D145)</f>
+      <c r="D147" s="15">
+        <f>SUM(D144:D146)</f>
         <v/>
       </c>
-      <c r="E146" s="15">
-        <f>SUM(E143:E145)</f>
+      <c r="E147" s="15">
+        <f>SUM(E144:E146)</f>
         <v/>
       </c>
-      <c r="F146" s="16" t="n"/>
-      <c r="G146" s="16" t="n"/>
-      <c r="H146" s="16" t="n"/>
-      <c r="I146" s="16" t="n"/>
-    </row>
-    <row r="148" ht="22" customHeight="1">
-      <c r="B148" s="3" t="inlineStr">
+      <c r="F147" s="16" t="n"/>
+      <c r="G147" s="16" t="n"/>
+      <c r="H147" s="16" t="n"/>
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n"/>
-      <c r="D148" s="4" t="n"/>
-      <c r="E148" s="4" t="n"/>
-      <c r="F148" s="4" t="n"/>
-      <c r="G148" s="4" t="n"/>
-      <c r="H148" s="4" t="n"/>
-      <c r="I148" s="4" t="inlineStr"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="B149" s="5" t="inlineStr">
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150" ht="26" customHeight="1">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I149" s="5" t="inlineStr">
+      <c r="I150" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — долг на начало месяца</t>
-        </is>
-      </c>
-      <c r="C150" s="7" t="n">
-        <v>16545367</v>
-      </c>
-      <c r="D150" s="8" t="n"/>
-      <c r="E150" s="8" t="n"/>
-      <c r="F150" s="8" t="n"/>
-      <c r="G150" s="8" t="n"/>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано за месяц</t>
+          <t>Кредитная линия — долг на начало месяца</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>11000000</v>
+        <v>16545367</v>
       </c>
       <c r="D151" s="8" t="n"/>
       <c r="E151" s="8" t="n"/>
@@ -3142,34 +3142,38 @@
       <c r="H151" s="8" t="n"/>
       <c r="I151" s="10" t="inlineStr">
         <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на конец месяца</t>
+          <t>Кредитная линия — выбрано за месяц</t>
         </is>
       </c>
       <c r="C152" s="7" t="n">
-        <v>27545367</v>
+        <v>11000000</v>
       </c>
       <c r="D152" s="8" t="n"/>
       <c r="E152" s="8" t="n"/>
       <c r="F152" s="8" t="n"/>
       <c r="G152" s="8" t="n"/>
       <c r="H152" s="8" t="n"/>
-      <c r="I152" s="8" t="n"/>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t>Кредитная линия — долг на конец месяца</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>30000000</v>
+        <v>27545367</v>
       </c>
       <c r="D153" s="8" t="n"/>
       <c r="E153" s="8" t="n"/>
@@ -3181,11 +3185,11 @@
     <row r="154">
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C154" s="7" t="n">
-        <v>2454633</v>
+        <v>30000000</v>
       </c>
       <c r="D154" s="8" t="n"/>
       <c r="E154" s="8" t="n"/>
@@ -3197,101 +3201,97 @@
     <row r="155">
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Проценты по кредиту, уплачено</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>204388.93</v>
+        <v>2454633</v>
       </c>
       <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
       <c r="G155" s="8" t="n"/>
       <c r="H155" s="8" t="n"/>
-      <c r="I155" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
-        </is>
-      </c>
+      <c r="I155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Проценты по кредиту, уплачено</t>
         </is>
       </c>
       <c r="C156" s="7" t="n">
-        <v>396337.24</v>
+        <v>204388.93</v>
       </c>
       <c r="D156" s="8" t="n"/>
       <c r="E156" s="8" t="n"/>
       <c r="F156" s="8" t="n"/>
       <c r="G156" s="8" t="n"/>
       <c r="H156" s="8" t="n"/>
-      <c r="I156" s="8" t="n"/>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C157" s="7" t="n"/>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D157" s="8" t="n"/>
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="8" t="n"/>
       <c r="G157" s="8" t="n"/>
       <c r="H157" s="8" t="n"/>
-      <c r="I157" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I157" s="8" t="n"/>
     </row>
     <row r="158">
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="n">
-        <v>373487.16</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n"/>
       <c r="D158" s="8" t="n"/>
       <c r="E158" s="8" t="n"/>
       <c r="F158" s="8" t="n"/>
       <c r="G158" s="8" t="n"/>
       <c r="H158" s="8" t="n"/>
-      <c r="I158" s="8" t="n"/>
+      <c r="I158" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+          <t>Комиссия эквайринга</t>
         </is>
       </c>
       <c r="C159" s="7" t="n">
-        <v>3284000</v>
+        <v>373487.16</v>
       </c>
       <c r="D159" s="8" t="n"/>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n"/>
       <c r="G159" s="8" t="n"/>
       <c r="H159" s="8" t="n"/>
-      <c r="I159" s="10" t="inlineStr">
-        <is>
-          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
-        </is>
-      </c>
+      <c r="I159" s="8" t="n"/>
     </row>
     <row r="160">
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Авансы арендодателям на конец месяца</t>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
         </is>
       </c>
       <c r="C160" s="7" t="n">
-        <v>31195343.31</v>
+        <v>3284000</v>
       </c>
       <c r="D160" s="8" t="n"/>
       <c r="E160" s="8" t="n"/>
@@ -3299,6 +3299,26 @@
       <c r="G160" s="8" t="n"/>
       <c r="H160" s="8" t="n"/>
       <c r="I160" s="10" t="inlineStr">
+        <is>
+          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Авансы арендодателям на конец месяца</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>31195343.31</v>
+      </c>
+      <c r="D161" s="8" t="n"/>
+      <c r="E161" s="8" t="n"/>
+      <c r="F161" s="8" t="n"/>
+      <c r="G161" s="8" t="n"/>
+      <c r="H161" s="8" t="n"/>
+      <c r="I161" s="10" t="inlineStr">
         <is>
           <t>дебетовое сальдо счёта 60: Паритет (стр.12) работает июльскую предоплату, поэтому коммунальных платежей в августе нет</t>
         </is>
@@ -5338,9 +5358,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="9">
-        <f> Пробито по банку</f>
-        <v/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Пробито по банку</t>
+        </is>
       </c>
       <c r="C9" s="21" t="n">
         <v>97726711.3</v>
@@ -5397,9 +5418,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="9">
-        <f> Поступления от пациентов за август</f>
-        <v/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Поступления от пациентов за август</t>
+        </is>
       </c>
       <c r="C12" s="21" t="n">
         <v>97301854</v>
@@ -6885,7 +6907,7 @@
         </is>
       </c>
       <c r="C10" s="26" t="n">
-        <v>1615200</v>
+        <v>1255200</v>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>

--- a/out/Расчёт-Август-2026.xlsx
+++ b/out/Расчёт-Август-2026.xlsx
@@ -74,11 +74,11 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="008A7350"/>
+      <color rgb="00807A70"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00807A70"/>
+      <color rgb="008A7350"/>
       <sz val="11"/>
     </font>
     <font>
@@ -164,22 +164,22 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I161"/>
+  <dimension ref="B1:I162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1121,19 +1121,19 @@
         <v/>
       </c>
       <c r="D35" s="15" t="n">
-        <v>4180781.46</v>
+        <v>4229901.79</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>13054662.21</v>
+        <v>13039550.06</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>76485706.81999999</v>
+        <v>76010267.98999999</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>261238.64</v>
+        <v>261913.99</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>2959464.86</v>
+        <v>2958609.32</v>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
@@ -1141,218 +1141,236 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        наличными</t>
+        </is>
+      </c>
+      <c r="C36" s="19">
+        <f>SUM(D36:H36)</f>
+        <v/>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>41946.83</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>3838920.69</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>30259592.24</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>55303.87</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>786136.38</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>касса клиники</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        безналичными</t>
+        </is>
+      </c>
+      <c r="C37" s="19">
+        <f>SUM(D37:H37)</f>
+        <v/>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>4187954.96</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>9200629.369999999</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>45750675.75</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>206610.12</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>2172472.94</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>карты и онлайн-оплаты, за вычетом возвратов</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>В том числе по каналам поступления</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Наличными</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>34981900</v>
-      </c>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>01–10.08: 10 688 500; 11–31.08: 24 293 400</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Безналичными (карты и онлайн-оплаты)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>61959954</v>
-      </c>
+      <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>01–10.08: 20 555 014, из них онлайн-оплаты через сайт 1 035 500; 11–31.08: 41 764 940; за вычетом возвратов пациентам 360 000</t>
-        </is>
-      </c>
+      <c r="I39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Наличными</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>34981900</v>
+      </c>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>01–10.08: 10 688 500; 11–31.08: 24 293 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Безналичными (карты и онлайн-оплаты)</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>61518343.14</v>
+      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>эквайринг, зачисленный банком на расчётный счёт: 61 983 343, за вычетом возвратов пациентам 465 000 — комиссия банка уже удержана</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Итого по каналам</t>
         </is>
       </c>
-      <c r="C40" s="12">
-        <f>SUM(C38:C39)</f>
+      <c r="C42" s="12">
+        <f>SUM(C40:C41)</f>
         <v/>
       </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>должно совпасть с итогом выручки выше</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="19" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Справочно: оказано услуг за месяц</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C44" s="22" t="n">
         <v>94366672</v>
       </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>01–10.08: 29 476 382; 11–31.08: 64 890 290</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="19" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Справочно: авансы под будущие операции</t>
         </is>
       </c>
-      <c r="C43" s="20" t="n">
-        <v>2575181.99</v>
-      </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 2,7% выручки месяца</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="C45" s="22" t="n">
+        <v>2133571.15</v>
+      </c>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>выручка минус оказанные услуги: деньги получены, операция ещё впереди — 2,2% выручки месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>3. РАСХОДЫ (оплаченные)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>делятся между учредителями 50/50</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="B46" s="5" t="inlineStr">
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>6135792.28</v>
-      </c>
-      <c r="D47" s="7">
-        <f>C47/2</f>
-        <v/>
-      </c>
-      <c r="E47" s="7">
-        <f>C47/2</f>
-        <v/>
-      </c>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Зарплата по банку</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>12490831.85</v>
-      </c>
-      <c r="D48" s="7">
-        <f>C48/2</f>
-        <v/>
-      </c>
-      <c r="E48" s="7">
-        <f>C48/2</f>
-        <v/>
-      </c>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (общие)</t>
+          <t>Налоги с ФОТ (счета 68.90 и 69)</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>142409.63</v>
+        <v>6135792.28</v>
       </c>
       <c r="D49" s="7">
         <f>C49/2</f>
@@ -1370,11 +1388,11 @@
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Услуги банка (эквайринг)</t>
+          <t>Зарплата по банку</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>373487.16</v>
+        <v>12490831.85</v>
       </c>
       <c r="D50" s="7">
         <f>C50/2</f>
@@ -1392,11 +1410,11 @@
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Алименты (удержание из зарплаты)</t>
+          <t>Услуги банка (общие)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>38726.66</v>
+        <v>142409.63</v>
       </c>
       <c r="D51" s="7">
         <f>C51/2</f>
@@ -1414,11 +1432,11 @@
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Проценты по кредиту</t>
+          <t>Алименты (удержание из зарплаты)</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>204388.93</v>
+        <v>38726.66</v>
       </c>
       <c r="D52" s="7">
         <f>C52/2</f>
@@ -1434,48 +1452,54 @@
       <c r="I52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики и подрядчики (счёт 60)</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="n">
-        <v>69792829.48999999</v>
-      </c>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>204388.93</v>
+      </c>
+      <c r="D53" s="7">
+        <f>C53/2</f>
+        <v/>
+      </c>
+      <c r="E53" s="7">
+        <f>C53/2</f>
+        <v/>
+      </c>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>без оплаченного за счёт кредитной линии</t>
-        </is>
-      </c>
+      <c r="I53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики и подрядчики (счёт 60)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>69792829.48999999</v>
+      </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>без оплаченного за счёт кредитной линии</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Гонорары ИП хирургов</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>39819623</v>
-      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе медицинские и гонорары:</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
@@ -1486,11 +1510,11 @@
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Импланты</t>
+          <t xml:space="preserve">            Гонорары ИП хирургов</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>4728500</v>
+        <v>39819623</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
@@ -1502,11 +1526,11 @@
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медицинские материалы</t>
+          <t xml:space="preserve">            Импланты</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>3298432.06</v>
+        <v>4728500</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
@@ -1518,11 +1542,11 @@
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Завиркин А.В.</t>
+          <t xml:space="preserve">            Медицинские материалы</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>2887658</v>
+        <v>3298432.06</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
@@ -1534,11 +1558,11 @@
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходка</t>
+          <t xml:space="preserve">            ИП Завиркин А.В.</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>2250790.16</v>
+        <v>2887658</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
@@ -1550,11 +1574,11 @@
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Лекарства</t>
+          <t xml:space="preserve">            Расходка</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>827352.65</v>
+        <v>2250790.16</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
@@ -1566,11 +1590,11 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
+          <t xml:space="preserve">            Лекарства</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>570005</v>
+        <v>827352.65</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
@@ -1582,11 +1606,11 @@
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование и расходники</t>
+          <t xml:space="preserve">            ИП Чугуевская (ЗП Заведягин ОН)</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>515528</v>
+        <v>570005</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
@@ -1598,11 +1622,11 @@
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Питание</t>
+          <t xml:space="preserve">            Медоборудование и расходники</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>376950</v>
+        <v>515528</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
@@ -1614,11 +1638,11 @@
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Белье</t>
+          <t xml:space="preserve">            Питание</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>345200</v>
+        <v>376950</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
@@ -1630,11 +1654,11 @@
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Inmode</t>
+          <t xml:space="preserve">            Белье</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>210000</v>
+        <v>345200</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
@@ -1646,11 +1670,11 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Кровь</t>
+          <t xml:space="preserve">            Аренда Inmode</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>181735.9</v>
+        <v>210000</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
@@ -1662,11 +1686,11 @@
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Медоборудование</t>
+          <t xml:space="preserve">            Кровь</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>173834.16</v>
+        <v>181735.9</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
@@ -1678,11 +1702,11 @@
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Анализы</t>
+          <t xml:space="preserve">            Медоборудование</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>102102</v>
+        <v>173834.16</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
@@ -1694,11 +1718,11 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Бланки, мед.журналы, мед.книжки</t>
+          <t xml:space="preserve">            Анализы</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>63600</v>
+        <v>102102</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
@@ -1710,11 +1734,11 @@
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Вывоз ТКО и мед отходов</t>
+          <t xml:space="preserve">            Бланки, мед.журналы, мед.книжки</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>52136.72</v>
+        <v>63600</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -1726,11 +1750,11 @@
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Утилизация медотходов</t>
+          <t xml:space="preserve">            Вывоз ТКО и мед отходов</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>23625</v>
+        <v>52136.72</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
@@ -1742,11 +1766,11 @@
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Наркотики</t>
+          <t xml:space="preserve">            Утилизация медотходов</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>12760</v>
+        <v>23625</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
@@ -1756,12 +1780,14 @@
       <c r="I72" s="8" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        в том числе управленческие:</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="n"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Наркотики</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>12760</v>
+      </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
@@ -1770,14 +1796,12 @@
       <c r="I73" s="8" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Урегулирование досудебного спора</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>4692500</v>
-      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        в том числе управленческие:</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
@@ -1788,11 +1812,11 @@
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Маркетинговые услуги</t>
+          <t xml:space="preserve">            Урегулирование досудебного спора</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>2505800</v>
+        <v>4692500</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
@@ -1804,11 +1828,11 @@
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
+          <t xml:space="preserve">            Маркетинговые услуги</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>1155000</v>
+        <v>2505800</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
@@ -1820,11 +1844,11 @@
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Ремонт</t>
+          <t xml:space="preserve">            Аренда Самокатная 1 стр1</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>516000</v>
+        <v>1155000</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
@@ -1836,11 +1860,11 @@
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание 1СУправление</t>
+          <t xml:space="preserve">            Ремонт</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>441570</v>
+        <v>516000</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
@@ -1852,11 +1876,11 @@
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Фото видео</t>
+          <t xml:space="preserve">            Обслуживание 1СУправление</t>
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>337440</v>
+        <v>441570</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
@@ -1868,11 +1892,11 @@
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги юриста</t>
+          <t xml:space="preserve">            Фото видео</t>
         </is>
       </c>
       <c r="C80" s="7" t="n">
-        <v>330000</v>
+        <v>337440</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
@@ -1884,11 +1908,11 @@
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Складской учет</t>
+          <t xml:space="preserve">            Услуги юриста</t>
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
@@ -1900,11 +1924,11 @@
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ПО и IT-сервисы</t>
+          <t xml:space="preserve">            Складской учет</t>
         </is>
       </c>
       <c r="C82" s="7" t="n">
-        <v>279349.86</v>
+        <v>320000</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
@@ -1916,11 +1940,11 @@
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Битрикс 24</t>
+          <t xml:space="preserve">            ПО и IT-сервисы</t>
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>264850</v>
+        <v>279349.86</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
@@ -1932,11 +1956,11 @@
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Сайт</t>
+          <t xml:space="preserve">            Битрикс 24</t>
         </is>
       </c>
       <c r="C84" s="7" t="n">
-        <v>254000</v>
+        <v>264850</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
@@ -1948,11 +1972,11 @@
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            IT услуги</t>
+          <t xml:space="preserve">            Сайт</t>
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>247935.06</v>
+        <v>254000</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
@@ -1964,11 +1988,11 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Реклама</t>
+          <t xml:space="preserve">            IT услуги</t>
         </is>
       </c>
       <c r="C86" s="7" t="n">
-        <v>227800</v>
+        <v>247935.06</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
@@ -1980,11 +2004,11 @@
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Светильники и оборудование</t>
+          <t xml:space="preserve">            Реклама</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>179400</v>
+        <v>227800</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
@@ -1996,11 +2020,11 @@
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Услуги инженера</t>
+          <t xml:space="preserve">            Светильники и оборудование</t>
         </is>
       </c>
       <c r="C88" s="7" t="n">
-        <v>159575</v>
+        <v>179400</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
@@ -2012,11 +2036,11 @@
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Канц и хоз расходы</t>
+          <t xml:space="preserve">            Услуги инженера</t>
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>157671.72</v>
+        <v>159575</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
@@ -2028,11 +2052,11 @@
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Сервис речевой аналитики</t>
+          <t xml:space="preserve">            Канц и хоз расходы</t>
         </is>
       </c>
       <c r="C90" s="7" t="n">
-        <v>152250</v>
+        <v>157671.72</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
@@ -2044,11 +2068,11 @@
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Общехозяйственные</t>
+          <t xml:space="preserve">            Сервис речевой аналитики</t>
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>137116</v>
+        <v>152250</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
@@ -2060,11 +2084,11 @@
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Косметология</t>
+          <t xml:space="preserve">            Общехозяйственные</t>
         </is>
       </c>
       <c r="C92" s="7" t="n">
-        <v>114858</v>
+        <v>137116</v>
       </c>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
@@ -2076,11 +2100,11 @@
     <row r="93">
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Такси</t>
+          <t xml:space="preserve">            Косметология</t>
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>100000</v>
+        <v>114858</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
@@ -2092,11 +2116,11 @@
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Внедрение финансового учёта</t>
+          <t xml:space="preserve">            Такси</t>
         </is>
       </c>
       <c r="C94" s="7" t="n">
-        <v>85000</v>
+        <v>100000</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="8" t="n"/>
@@ -2108,11 +2132,11 @@
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Краснодар</t>
+          <t xml:space="preserve">            Внедрение финансового учёта</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>81075</v>
+        <v>85000</v>
       </c>
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
@@ -2124,11 +2148,11 @@
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Хоз расходы</t>
+          <t xml:space="preserve">            Краснодар</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>77247</v>
+        <v>81075</v>
       </c>
       <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
@@ -2140,11 +2164,11 @@
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Связь</t>
+          <t xml:space="preserve">            Хоз расходы</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>53760</v>
+        <v>77247</v>
       </c>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
@@ -2156,11 +2180,11 @@
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Кофе</t>
+          <t xml:space="preserve">            Связь</t>
         </is>
       </c>
       <c r="C98" s="7" t="n">
-        <v>48301.44</v>
+        <v>53760</v>
       </c>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
@@ -2172,11 +2196,11 @@
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Цветы</t>
+          <t xml:space="preserve">            Кофе</t>
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>40000</v>
+        <v>48301.44</v>
       </c>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
@@ -2188,11 +2212,11 @@
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Программное обнспечение</t>
+          <t xml:space="preserve">            Цветы</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>39200</v>
+        <v>40000</v>
       </c>
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
@@ -2204,11 +2228,11 @@
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Средства гигиены</t>
+          <t xml:space="preserve">            Программное обнспечение</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>37568</v>
+        <v>39200</v>
       </c>
       <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
@@ -2220,11 +2244,11 @@
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Доктор Дискаунт (назначение уточняется)</t>
+          <t xml:space="preserve">            Средства гигиены</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>35920.61</v>
+        <v>37568</v>
       </c>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
@@ -2236,11 +2260,11 @@
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Капвложения и работы</t>
+          <t xml:space="preserve">            Доктор Дискаунт (назначение уточняется)</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>29800</v>
+        <v>35920.61</v>
       </c>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
@@ -2252,11 +2276,11 @@
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Подбор персонала</t>
+          <t xml:space="preserve">            Капвложения и работы</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>27629</v>
+        <v>29800</v>
       </c>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
@@ -2268,11 +2292,11 @@
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Охрана</t>
+          <t xml:space="preserve">            Подбор персонала</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>26600</v>
+        <v>27629</v>
       </c>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
@@ -2284,11 +2308,11 @@
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Мебель, инвентарь</t>
+          <t xml:space="preserve">            Охрана</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>22130</v>
+        <v>26600</v>
       </c>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
@@ -2300,11 +2324,11 @@
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Вода</t>
+          <t xml:space="preserve">            Мебель, инвентарь</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>20000</v>
+        <v>22130</v>
       </c>
       <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
@@ -2316,11 +2340,11 @@
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Техподдержка ККТ</t>
+          <t xml:space="preserve">            Вода</t>
         </is>
       </c>
       <c r="C108" s="7" t="n">
-        <v>17900</v>
+        <v>20000</v>
       </c>
       <c r="D108" s="8" t="n"/>
       <c r="E108" s="8" t="n"/>
@@ -2332,11 +2356,11 @@
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Электрооборудование</t>
+          <t xml:space="preserve">            Техподдержка ККТ</t>
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>17740</v>
+        <v>17900</v>
       </c>
       <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
@@ -2348,11 +2372,11 @@
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Дизайн-услуги</t>
+          <t xml:space="preserve">            Электрооборудование</t>
         </is>
       </c>
       <c r="C110" s="7" t="n">
-        <v>17060</v>
+        <v>17740</v>
       </c>
       <c r="D110" s="8" t="n"/>
       <c r="E110" s="8" t="n"/>
@@ -2364,11 +2388,11 @@
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Интернет</t>
+          <t xml:space="preserve">            Дизайн-услуги</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>16235.15</v>
+        <v>17060</v>
       </c>
       <c r="D111" s="8" t="n"/>
       <c r="E111" s="8" t="n"/>
@@ -2380,11 +2404,11 @@
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Расходник</t>
+          <t xml:space="preserve">            Интернет</t>
         </is>
       </c>
       <c r="C112" s="7" t="n">
-        <v>15120</v>
+        <v>16235.15</v>
       </c>
       <c r="D112" s="8" t="n"/>
       <c r="E112" s="8" t="n"/>
@@ -2396,11 +2420,11 @@
     <row r="113">
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Аренда кофемашины</t>
+          <t xml:space="preserve">            Расходник</t>
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>15000</v>
+        <v>15120</v>
       </c>
       <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
@@ -2412,11 +2436,11 @@
     <row r="114">
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обучение персонала</t>
+          <t xml:space="preserve">            Аренда кофемашины</t>
         </is>
       </c>
       <c r="C114" s="7" t="n">
-        <v>10900</v>
+        <v>15000</v>
       </c>
       <c r="D114" s="8" t="n"/>
       <c r="E114" s="8" t="n"/>
@@ -2428,11 +2452,11 @@
     <row r="115">
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Общехоз.расходы прочие</t>
+          <t xml:space="preserve">            Обучение персонала</t>
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>10000</v>
+        <v>10900</v>
       </c>
       <c r="D115" s="8" t="n"/>
       <c r="E115" s="8" t="n"/>
@@ -2444,7 +2468,7 @@
     <row r="116">
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ПроДокторов</t>
+          <t xml:space="preserve">            Общехоз.расходы прочие</t>
         </is>
       </c>
       <c r="C116" s="7" t="n">
@@ -2460,11 +2484,11 @@
     <row r="117">
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Доставка</t>
+          <t xml:space="preserve">            ПроДокторов</t>
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>7495</v>
+        <v>10000</v>
       </c>
       <c r="D117" s="8" t="n"/>
       <c r="E117" s="8" t="n"/>
@@ -2476,11 +2500,11 @@
     <row r="118">
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ТО СКУД, пожарной сигнализации</t>
+          <t xml:space="preserve">            Доставка</t>
         </is>
       </c>
       <c r="C118" s="7" t="n">
-        <v>7000</v>
+        <v>7495</v>
       </c>
       <c r="D118" s="8" t="n"/>
       <c r="E118" s="8" t="n"/>
@@ -2492,11 +2516,11 @@
     <row r="119">
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Оргтехника</t>
+          <t xml:space="preserve">            ТО СКУД, пожарной сигнализации</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>5100</v>
+        <v>7000</v>
       </c>
       <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
@@ -2508,11 +2532,11 @@
     <row r="120">
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Обслуживание аквариума</t>
+          <t xml:space="preserve">            Оргтехника</t>
         </is>
       </c>
       <c r="C120" s="7" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="D120" s="8" t="n"/>
       <c r="E120" s="8" t="n"/>
@@ -2524,11 +2548,11 @@
     <row r="121">
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Консультационные услуги</t>
+          <t xml:space="preserve">            Обслуживание аквариума</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>1100</v>
+        <v>5000</v>
       </c>
       <c r="D121" s="8" t="n"/>
       <c r="E121" s="8" t="n"/>
@@ -2538,33 +2562,29 @@
       <c r="I121" s="8" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        − личные расходы Маланичева, они внутри счёта 60</t>
-        </is>
-      </c>
-      <c r="C122" s="24" t="n">
-        <v>-170861.64</v>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Консультационные услуги</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>1100</v>
       </c>
       <c r="D122" s="8" t="n"/>
       <c r="E122" s="8" t="n"/>
       <c r="F122" s="8" t="n"/>
       <c r="G122" s="8" t="n"/>
       <c r="H122" s="8" t="n"/>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>заказано лично под врача — пополам не делится</t>
-        </is>
-      </c>
+      <c r="I122" s="8" t="n"/>
     </row>
     <row r="123">
-      <c r="B123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        − личные расходы Погосяна, они внутри счёта 60</t>
-        </is>
-      </c>
-      <c r="C123" s="24" t="n">
-        <v>-1487162.05</v>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        − личные расходы Маланичева, они внутри счёта 60</t>
+        </is>
+      </c>
+      <c r="C123" s="25" t="n">
+        <v>-170861.64</v>
       </c>
       <c r="D123" s="8" t="n"/>
       <c r="E123" s="8" t="n"/>
@@ -2578,116 +2598,115 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>Поставщики к делению пополам</t>
-        </is>
-      </c>
-      <c r="C124" s="21">
-        <f>C53+C122+C123</f>
-        <v/>
-      </c>
-      <c r="D124" s="21">
-        <f>C124/2</f>
-        <v/>
-      </c>
-      <c r="E124" s="21">
-        <f>C124/2</f>
-        <v/>
-      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        − личные расходы Погосяна, они внутри счёта 60</t>
+        </is>
+      </c>
+      <c r="C124" s="25" t="n">
+        <v>-1487162.05</v>
+      </c>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
       <c r="F124" s="8" t="n"/>
       <c r="G124" s="8" t="n"/>
       <c r="H124" s="8" t="n"/>
-      <c r="I124" s="8" t="n"/>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>заказано лично под врача — пополам не делится</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="B125" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДЫ К ДЕЛЕНИЮ ПОПОЛАМ</t>
-        </is>
-      </c>
-      <c r="C125" s="15">
-        <f>SUM(C47:C52)+C124</f>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Поставщики к делению пополам</t>
+        </is>
+      </c>
+      <c r="C125" s="23">
+        <f>C54+C123+C124</f>
         <v/>
       </c>
-      <c r="D125" s="15">
+      <c r="D125" s="23">
         <f>C125/2</f>
         <v/>
       </c>
-      <c r="E125" s="15">
+      <c r="E125" s="23">
         <f>C125/2</f>
         <v/>
       </c>
-      <c r="F125" s="16" t="n"/>
-      <c r="G125" s="16" t="n"/>
-      <c r="H125" s="16" t="n"/>
-      <c r="I125" s="17" t="inlineStr">
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="8" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДЫ К ДЕЛЕНИЮ ПОПОЛАМ</t>
+        </is>
+      </c>
+      <c r="C126" s="15">
+        <f>SUM(C49:C53)+C125</f>
+        <v/>
+      </c>
+      <c r="D126" s="15">
+        <f>C126/2</f>
+        <v/>
+      </c>
+      <c r="E126" s="15">
+        <f>C126/2</f>
+        <v/>
+      </c>
+      <c r="F126" s="16" t="n"/>
+      <c r="G126" s="16" t="n"/>
+      <c r="H126" s="16" t="n"/>
+      <c r="I126" s="17" t="inlineStr">
         <is>
           <t>строки «в том числе» в сумму не входят</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="6" t="inlineStr">
+    <row r="127">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>+ Личные расходы, каждому свои</t>
         </is>
       </c>
-      <c r="C126" s="7">
-        <f>D126+E126</f>
-        <v/>
-      </c>
-      <c r="D126" s="7" t="n">
-        <v>170861.64</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>1487162.05</v>
-      </c>
-      <c r="F126" s="8" t="n"/>
-      <c r="G126" s="8" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>те самые суммы, что вычтены из счёта 60 выше</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Анализы</t>
-        </is>
-      </c>
-      <c r="C127" s="25">
+      <c r="C127" s="7">
         <f>D127+E127</f>
         <v/>
       </c>
-      <c r="D127" s="25" t="n">
-        <v>30620</v>
-      </c>
-      <c r="E127" s="25" t="n">
-        <v>12248</v>
+      <c r="D127" s="7" t="n">
+        <v>170861.64</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>1487162.05</v>
       </c>
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="8" t="n"/>
       <c r="H127" s="8" t="n"/>
-      <c r="I127" s="8" t="n"/>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>те самые суммы, что вычтены из счёта 60 выше</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="B128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Материалы за операции</t>
-        </is>
-      </c>
-      <c r="C128" s="25">
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Анализы</t>
+        </is>
+      </c>
+      <c r="C128" s="19">
         <f>D128+E128</f>
         <v/>
       </c>
-      <c r="D128" s="25" t="n">
-        <v>140241.64</v>
-      </c>
-      <c r="E128" s="25" t="n">
-        <v>1474914.05</v>
+      <c r="D128" s="19" t="n">
+        <v>30620</v>
+      </c>
+      <c r="E128" s="19" t="n">
+        <v>12248</v>
       </c>
       <c r="F128" s="8" t="n"/>
       <c r="G128" s="8" t="n"/>
@@ -2695,163 +2714,161 @@
       <c r="I128" s="8" t="n"/>
     </row>
     <row r="129">
-      <c r="B129" s="14" t="inlineStr">
-        <is>
-          <t>ДОЛЯ РАСХОДОВ КАЖДОГО</t>
-        </is>
-      </c>
-      <c r="C129" s="15">
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Материалы за операции</t>
+        </is>
+      </c>
+      <c r="C129" s="19">
         <f>D129+E129</f>
         <v/>
       </c>
-      <c r="D129" s="15">
-        <f>D125+D126</f>
+      <c r="D129" s="19" t="n">
+        <v>140241.64</v>
+      </c>
+      <c r="E129" s="19" t="n">
+        <v>1474914.05</v>
+      </c>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="8" t="n"/>
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="8" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>ДОЛЯ РАСХОДОВ КАЖДОГО</t>
+        </is>
+      </c>
+      <c r="C130" s="15">
+        <f>D130+E130</f>
         <v/>
       </c>
-      <c r="E129" s="15">
-        <f>E125+E126</f>
+      <c r="D130" s="15">
+        <f>D126+D127</f>
         <v/>
       </c>
-      <c r="F129" s="16" t="n"/>
-      <c r="G129" s="16" t="n"/>
-      <c r="H129" s="16" t="n"/>
-      <c r="I129" s="17" t="inlineStr">
+      <c r="E130" s="15">
+        <f>E126+E127</f>
+        <v/>
+      </c>
+      <c r="F130" s="16" t="n"/>
+      <c r="G130" s="16" t="n"/>
+      <c r="H130" s="16" t="n"/>
+      <c r="I130" s="17" t="inlineStr">
         <is>
           <t>к делению пополам плюс свои личные</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="B130" s="19" t="inlineStr">
+    <row r="131">
+      <c r="B131" s="21" t="inlineStr">
         <is>
           <t>Справочно: ремонт за счёт кредитной линии</t>
         </is>
       </c>
-      <c r="C130" s="20" t="n">
+      <c r="C131" s="22" t="n">
         <v>11000000</v>
       </c>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="8" t="n"/>
-      <c r="G130" s="8" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="10" t="inlineStr">
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="8" t="n"/>
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="10" t="inlineStr">
         <is>
           <t>в расходы учредителей не входит — стройка идёт на заёмные</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="B132" s="3" t="inlineStr">
+    <row r="133" ht="22" customHeight="1">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>4. РАСЧЁТ ДОХОДА УЧРЕДИТЕЛЕЙ</t>
         </is>
       </c>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="n"/>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="n"/>
-      <c r="G132" s="4" t="n"/>
-      <c r="H132" s="4" t="n"/>
-      <c r="I132" s="4" t="inlineStr">
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="inlineStr">
         <is>
           <t>методика 50/50</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="26" customHeight="1">
-      <c r="B133" s="5" t="inlineStr">
+    <row r="134" ht="26" customHeight="1">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Как считается</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" s="6" t="inlineStr">
+    <row r="135">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>1. Личная выручка (свои операции)</t>
         </is>
       </c>
-      <c r="C134" s="7">
-        <f>D134+E134</f>
+      <c r="C135" s="7">
+        <f>D135+E135</f>
         <v/>
       </c>
-      <c r="D134" s="7">
+      <c r="D135" s="7">
         <f>D35</f>
         <v/>
       </c>
-      <c r="E134" s="7">
+      <c r="E135" s="7">
         <f>E35</f>
-        <v/>
-      </c>
-      <c r="F134" s="8" t="n"/>
-      <c r="G134" s="8" t="n"/>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>своя строка из блока «Выручка»</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>2. Половина выручки других хирургов</t>
-        </is>
-      </c>
-      <c r="C135" s="7">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="D135" s="7">
-        <f>F35/2</f>
-        <v/>
-      </c>
-      <c r="E135" s="7">
-        <f>F35/2</f>
         <v/>
       </c>
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="8" t="n"/>
       <c r="H135" s="8" t="n"/>
-      <c r="I135" s="8" t="n"/>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>своя строка из блока «Выручка»</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>3. Половина выручки косметологии</t>
+          <t>2. Половина выручки других хирургов</t>
         </is>
       </c>
       <c r="C136" s="7">
-        <f>H35</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>H35/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="E136" s="7">
-        <f>H35/2</f>
+        <f>F35/2</f>
         <v/>
       </c>
       <c r="F136" s="8" t="n"/>
@@ -2862,19 +2879,19 @@
     <row r="137">
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>4. Половина прочих доходов</t>
+          <t>3. Половина выручки косметологии</t>
         </is>
       </c>
       <c r="C137" s="7">
-        <f>G35</f>
+        <f>H35</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>G35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="E137" s="7">
-        <f>G35/2</f>
+        <f>H35/2</f>
         <v/>
       </c>
       <c r="F137" s="8" t="n"/>
@@ -2885,45 +2902,41 @@
     <row r="138">
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>5. Половина процентов по депозитам</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="n">
-        <v>396337.24</v>
+          <t>4. Половина прочих доходов</t>
+        </is>
+      </c>
+      <c r="C138" s="7">
+        <f>G35</f>
+        <v/>
       </c>
       <c r="D138" s="7">
-        <f>C138/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="E138" s="7">
-        <f>C138/2</f>
+        <f>G35/2</f>
         <v/>
       </c>
       <c r="F138" s="8" t="n"/>
       <c r="G138" s="8" t="n"/>
       <c r="H138" s="8" t="n"/>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>начислены банком на остатки</t>
-        </is>
-      </c>
+      <c r="I138" s="8" t="n"/>
     </row>
     <row r="139">
-      <c r="B139" s="23" t="inlineStr">
-        <is>
-          <t>6. Минус доля расходов</t>
-        </is>
-      </c>
-      <c r="C139" s="24">
-        <f>-C129</f>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>5. Половина процентов по депозитам</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>396337.24</v>
+      </c>
+      <c r="D139" s="7">
+        <f>C139/2</f>
         <v/>
       </c>
-      <c r="D139" s="24">
-        <f>-D129</f>
-        <v/>
-      </c>
-      <c r="E139" s="24">
-        <f>-E129</f>
+      <c r="E139" s="7">
+        <f>C139/2</f>
         <v/>
       </c>
       <c r="F139" s="8" t="n"/>
@@ -2931,229 +2944,236 @@
       <c r="H139" s="8" t="n"/>
       <c r="I139" s="10" t="inlineStr">
         <is>
+          <t>начислены банком на остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>6. Минус доля расходов</t>
+        </is>
+      </c>
+      <c r="C140" s="25">
+        <f>-C130</f>
+        <v/>
+      </c>
+      <c r="D140" s="25">
+        <f>-D130</f>
+        <v/>
+      </c>
+      <c r="E140" s="25">
+        <f>-E130</f>
+        <v/>
+      </c>
+      <c r="F140" s="8" t="n"/>
+      <c r="G140" s="8" t="n"/>
+      <c r="H140" s="8" t="n"/>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
           <t>строка «Доля расходов каждого» блока 3</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="B140" s="14" t="inlineStr">
+    <row r="141">
+      <c r="B141" s="14" t="inlineStr">
         <is>
           <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
-      <c r="C140" s="15">
-        <f>SUM(C134:C139)</f>
+      <c r="C141" s="15">
+        <f>SUM(C135:C140)</f>
         <v/>
       </c>
-      <c r="D140" s="15">
-        <f>SUM(D134:D139)</f>
+      <c r="D141" s="15">
+        <f>SUM(D135:D140)</f>
         <v/>
       </c>
-      <c r="E140" s="15">
-        <f>SUM(E134:E139)</f>
+      <c r="E141" s="15">
+        <f>SUM(E135:E140)</f>
         <v/>
       </c>
-      <c r="F140" s="16" t="n"/>
-      <c r="G140" s="16" t="n"/>
-      <c r="H140" s="16" t="n"/>
-      <c r="I140" s="16" t="n"/>
-    </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="B142" s="3" t="inlineStr">
+      <c r="F141" s="16" t="n"/>
+      <c r="G141" s="16" t="n"/>
+      <c r="H141" s="16" t="n"/>
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>5. К ВЫПЛАТЕ УЧРЕДИТЕЛЯМ</t>
         </is>
       </c>
-      <c r="C142" s="4" t="n"/>
-      <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="n"/>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="4" t="n"/>
-      <c r="H142" s="4" t="n"/>
-      <c r="I142" s="4" t="inlineStr"/>
-    </row>
-    <row r="143" ht="26" customHeight="1">
-      <c r="B143" s="5" t="inlineStr">
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144" ht="26" customHeight="1">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>Маланичев</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>Погосян</t>
         </is>
       </c>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="I144" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>Доход за месяц</t>
-        </is>
-      </c>
-      <c r="C144" s="7">
-        <f>C140</f>
-        <v/>
-      </c>
-      <c r="D144" s="7">
-        <f>D140</f>
-        <v/>
-      </c>
-      <c r="E144" s="7">
-        <f>E140</f>
-        <v/>
-      </c>
-      <c r="F144" s="8" t="n"/>
-      <c r="G144" s="8" t="n"/>
-      <c r="H144" s="8" t="n"/>
-      <c r="I144" s="8" t="n"/>
     </row>
     <row r="145">
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Остаток с прошлого месяца</t>
+          <t>Доход за месяц</t>
         </is>
       </c>
       <c r="C145" s="7">
-        <f>D145+E145</f>
+        <f>C141</f>
         <v/>
       </c>
-      <c r="D145" s="7" t="n">
-        <v>30658896.02</v>
-      </c>
-      <c r="E145" s="7" t="n">
-        <v>45275972.21</v>
+      <c r="D145" s="7">
+        <f>D141</f>
+        <v/>
+      </c>
+      <c r="E145" s="7">
+        <f>E141</f>
+        <v/>
       </c>
       <c r="F145" s="8" t="n"/>
       <c r="G145" s="8" t="n"/>
       <c r="H145" s="8" t="n"/>
-      <c r="I145" s="10" t="inlineStr">
-        <is>
-          <t>ручной ввод бухгалтерии</t>
-        </is>
-      </c>
+      <c r="I145" s="8" t="n"/>
     </row>
     <row r="146">
-      <c r="B146" s="23" t="inlineStr">
-        <is>
-          <t>Выплачены дивиденды</t>
-        </is>
-      </c>
-      <c r="C146" s="24">
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Остаток с прошлого месяца</t>
+        </is>
+      </c>
+      <c r="C146" s="7">
         <f>D146+E146</f>
         <v/>
       </c>
-      <c r="D146" s="24" t="n">
-        <v>-5882353</v>
-      </c>
-      <c r="E146" s="24" t="n">
-        <v>-5882353</v>
+      <c r="D146" s="7" t="n">
+        <v>30658896.02</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>45275972.21</v>
       </c>
       <c r="F146" s="8" t="n"/>
       <c r="G146" s="8" t="n"/>
       <c r="H146" s="8" t="n"/>
       <c r="I146" s="10" t="inlineStr">
         <is>
+          <t>ручной ввод бухгалтерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>Выплачены дивиденды</t>
+        </is>
+      </c>
+      <c r="C147" s="25">
+        <f>D147+E147</f>
+        <v/>
+      </c>
+      <c r="D147" s="25" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="E147" s="25" t="n">
+        <v>-5882353</v>
+      </c>
+      <c r="F147" s="8" t="n"/>
+      <c r="G147" s="8" t="n"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
           <t>начислено с НДФЛ</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="B147" s="14" t="inlineStr">
+    <row r="148">
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t>ИТОГО К ВЫПЛАТЕ НА 31.08.2026</t>
         </is>
       </c>
-      <c r="C147" s="15">
-        <f>SUM(C144:C146)</f>
+      <c r="C148" s="15">
+        <f>SUM(C145:C147)</f>
         <v/>
       </c>
-      <c r="D147" s="15">
-        <f>SUM(D144:D146)</f>
+      <c r="D148" s="15">
+        <f>SUM(D145:D147)</f>
         <v/>
       </c>
-      <c r="E147" s="15">
-        <f>SUM(E144:E146)</f>
+      <c r="E148" s="15">
+        <f>SUM(E145:E147)</f>
         <v/>
       </c>
-      <c r="F147" s="16" t="n"/>
-      <c r="G147" s="16" t="n"/>
-      <c r="H147" s="16" t="n"/>
-      <c r="I147" s="16" t="n"/>
-    </row>
-    <row r="149" ht="22" customHeight="1">
-      <c r="B149" s="3" t="inlineStr">
+      <c r="F148" s="16" t="n"/>
+      <c r="G148" s="16" t="n"/>
+      <c r="H148" s="16" t="n"/>
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>6. СПРАВОЧНО</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="4" t="n"/>
-      <c r="H149" s="4" t="n"/>
-      <c r="I149" s="4" t="inlineStr"/>
-    </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="B150" s="5" t="inlineStr">
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="inlineStr"/>
+    </row>
+    <row r="151" ht="26" customHeight="1">
+      <c r="B151" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C151" s="5" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="I150" s="5" t="inlineStr">
+      <c r="I151" s="5" t="inlineStr">
         <is>
           <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>Кредитная линия — долг на начало месяца</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="n">
-        <v>16545367</v>
-      </c>
-      <c r="D151" s="8" t="n"/>
-      <c r="E151" s="8" t="n"/>
-      <c r="F151" s="8" t="n"/>
-      <c r="G151" s="8" t="n"/>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — выбрано за месяц</t>
+          <t>Кредитная линия — долг на начало месяца</t>
         </is>
       </c>
       <c r="C152" s="7" t="n">
-        <v>11000000</v>
+        <v>16545367</v>
       </c>
       <c r="D152" s="8" t="n"/>
       <c r="E152" s="8" t="n"/>
@@ -3162,34 +3182,38 @@
       <c r="H152" s="8" t="n"/>
       <c r="I152" s="10" t="inlineStr">
         <is>
-          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+          <t>счёт 67, контрагент «ОМЕГА ООО»</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — долг на конец месяца</t>
+          <t>Кредитная линия — выбрано за месяц</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>27545367</v>
+        <v>11000000</v>
       </c>
       <c r="D153" s="8" t="n"/>
       <c r="E153" s="8" t="n"/>
       <c r="F153" s="8" t="n"/>
       <c r="G153" s="8" t="n"/>
       <c r="H153" s="8" t="n"/>
-      <c r="I153" s="8" t="n"/>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>9 000 000 + 2 000 000, оба ушли Квалитету</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — лимит</t>
+          <t>Кредитная линия — долг на конец месяца</t>
         </is>
       </c>
       <c r="C154" s="7" t="n">
-        <v>30000000</v>
+        <v>27545367</v>
       </c>
       <c r="D154" s="8" t="n"/>
       <c r="E154" s="8" t="n"/>
@@ -3201,11 +3225,11 @@
     <row r="155">
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Кредитная линия — свободный остаток</t>
+          <t>Кредитная линия — лимит</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>2454633</v>
+        <v>30000000</v>
       </c>
       <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
@@ -3217,81 +3241,81 @@
     <row r="156">
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Проценты по кредиту, уплачено</t>
+          <t>Кредитная линия — свободный остаток</t>
         </is>
       </c>
       <c r="C156" s="7" t="n">
-        <v>204388.93</v>
+        <v>2454633</v>
       </c>
       <c r="D156" s="8" t="n"/>
       <c r="E156" s="8" t="n"/>
       <c r="F156" s="8" t="n"/>
       <c r="G156" s="8" t="n"/>
       <c r="H156" s="8" t="n"/>
-      <c r="I156" s="10" t="inlineStr">
-        <is>
-          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
-        </is>
-      </c>
+      <c r="I156" s="8" t="n"/>
     </row>
     <row r="157">
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Проценты по депозитам за месяц</t>
+          <t>Проценты по кредиту, уплачено</t>
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>396337.24</v>
+        <v>204388.93</v>
       </c>
       <c r="D157" s="8" t="n"/>
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="8" t="n"/>
       <c r="G157" s="8" t="n"/>
       <c r="H157" s="8" t="n"/>
-      <c r="I157" s="8" t="n"/>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>счёт 67, контрагент «Филиал „Центральный“ Банка ВТБ»; в июле было 151 764,47</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Остаток наличных в кассе</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="n"/>
+          <t>Проценты по депозитам за месяц</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>396337.24</v>
+      </c>
       <c r="D158" s="8" t="n"/>
       <c r="E158" s="8" t="n"/>
       <c r="F158" s="8" t="n"/>
       <c r="G158" s="8" t="n"/>
       <c r="H158" s="8" t="n"/>
-      <c r="I158" s="10" t="inlineStr">
-        <is>
-          <t>не проставлен</t>
-        </is>
-      </c>
+      <c r="I158" s="8" t="n"/>
     </row>
     <row r="159">
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Комиссия эквайринга</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="n">
-        <v>373487.16</v>
-      </c>
+          <t>Остаток наличных в кассе</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n"/>
       <c r="D159" s="8" t="n"/>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n"/>
       <c r="G159" s="8" t="n"/>
       <c r="H159" s="8" t="n"/>
-      <c r="I159" s="8" t="n"/>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>не проставлен</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
+          <t>Комиссия эквайринга, удержана банком</t>
         </is>
       </c>
       <c r="C160" s="7" t="n">
-        <v>3284000</v>
+        <v>373487.16</v>
       </c>
       <c r="D160" s="8" t="n"/>
       <c r="E160" s="8" t="n"/>
@@ -3300,18 +3324,18 @@
       <c r="H160" s="8" t="n"/>
       <c r="I160" s="10" t="inlineStr">
         <is>
-          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+          <t>в расходы не ставится: безнал в выручке взят уже за вычетом комиссии</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Авансы арендодателям на конец месяца</t>
+          <t>Онлайн-оплаты через сайт (интернет-эквайринг)</t>
         </is>
       </c>
       <c r="C161" s="7" t="n">
-        <v>31195343.31</v>
+        <v>3284000</v>
       </c>
       <c r="D161" s="8" t="n"/>
       <c r="E161" s="8" t="n"/>
@@ -3319,6 +3343,26 @@
       <c r="G161" s="8" t="n"/>
       <c r="H161" s="8" t="n"/>
       <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>счёт 62.01; отдельной строкой не добавляется — уже внутри безналичных поступлений</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Авансы арендодателям на конец месяца</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>31195343.31</v>
+      </c>
+      <c r="D162" s="8" t="n"/>
+      <c r="E162" s="8" t="n"/>
+      <c r="F162" s="8" t="n"/>
+      <c r="G162" s="8" t="n"/>
+      <c r="H162" s="8" t="n"/>
+      <c r="I162" s="10" t="inlineStr">
         <is>
           <t>дебетовое сальдо счёта 60: Паритет (стр.12) работает июльскую предоплату, поэтому коммунальных платежей в августе нет</t>
         </is>
@@ -5220,7 +5264,7 @@
       <c r="F127" s="13" t="n"/>
       <c r="G127" s="13" t="n"/>
       <c r="H127" s="13" t="n"/>
-      <c r="I127" s="18" t="inlineStr">
+      <c r="I127" s="20" t="inlineStr">
         <is>
           <t>в т.ч. за счёт кредитной линии — см. справочную строку основного листа</t>
         </is>
@@ -5283,7 +5327,7 @@
           <t>Поступило на р/с через счёт 57 (нетто)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="23" t="n">
         <v>97353224.14</v>
       </c>
       <c r="D5" s="8" t="n"/>
@@ -5363,7 +5407,7 @@
           <t>Пробито по банку</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="23" t="n">
         <v>97726711.3</v>
       </c>
       <c r="D9" s="8" t="n"/>
@@ -5378,12 +5422,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>− Инкассация больше пробитой налички</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <v>-388100</v>
       </c>
       <c r="D10" s="8" t="n"/>
@@ -5398,13 +5442,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>− Эквайринг конца июля, зачисленный в августе</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n">
-        <v>-36757.29999999702</v>
+      <c r="C11" s="25" t="n">
+        <v>-373368.1599999964</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
@@ -5413,7 +5457,7 @@
       <c r="H11" s="8" t="n"/>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>по банку 62 356 711.30 против 62 319 954.00 по картам</t>
+          <t>по банку 62 356 711.30 против 61 983 343.14 по картам</t>
         </is>
       </c>
     </row>
@@ -5423,8 +5467,8 @@
           <t>Поступления от пациентов за август</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
-        <v>97301854</v>
+      <c r="C12" s="23" t="n">
+        <v>96965243.14</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
@@ -5438,13 +5482,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>− Возвраты пациентам</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n">
-        <v>-360000</v>
+      <c r="C13" s="25" t="n">
+        <v>-465000</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
@@ -5464,14 +5508,14 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>96941853.98999999</v>
+        <v>96500243.15000001</v>
       </c>
       <c r="D14" s="13" t="n"/>
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n"/>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>сходится до копейки</t>
         </is>
@@ -5540,7 +5584,7 @@
           <t>Медицинские — итого</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="23" t="n">
         <v>56439832.64999999</v>
       </c>
       <c r="D5" s="8" t="n"/>
@@ -5880,7 +5924,7 @@
           <t>Управленческие — итого</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="23" t="n">
         <v>13352996.84</v>
       </c>
       <c r="D24" s="8" t="n"/>
@@ -6768,7 +6812,7 @@
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="13" t="n"/>
       <c r="H73" s="13" t="n"/>
-      <c r="I73" s="18" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>совпадает со строкой «Поставщики и подрядчики» основного листа</t>
         </is>
